--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C41F88-0E42-4D4B-BA19-558696AB4EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB5393F-02DE-483A-A45E-E0BCA2B12E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="10" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="11" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="42">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -180,6 +180,9 @@
   <si>
     <t>Shakoor</t>
   </si>
+  <si>
+    <t>CTNS</t>
+  </si>
 </sst>
 </file>
 
@@ -286,7 +289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -626,11 +629,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -764,6 +798,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -799,6 +836,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1145,57 +1191,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="B2" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1203,18 +1249,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1564,95 +1610,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1660,33 +1706,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2413,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB8BBA6-E6CB-45EB-B741-EF1A3D434FE9}">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -2432,7 +2478,7 @@
     <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2452,123 +2498,124 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="59" t="s">
+      <c r="M2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="M3" s="63"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-    </row>
-    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="68" t="s">
+      <c r="O6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="69" t="s">
+      <c r="P6" s="70"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="S6" s="73"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -2618,7 +2665,7 @@
         <v>11</v>
       </c>
       <c r="Q7" s="45" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R7" s="45" t="s">
         <v>13</v>
@@ -2630,13 +2677,16 @@
         <v>12</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="W7" s="59" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -2660,19 +2710,12 @@
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="28">
-        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8">
-        <f>SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -2710,22 +2753,37 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="N9" s="12">
+        <v>42</v>
+      </c>
+      <c r="O9" s="12">
+        <v>54</v>
+      </c>
+      <c r="P9" s="12">
+        <v>20</v>
+      </c>
       <c r="Q9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>58</v>
+      </c>
+      <c r="S9" s="12">
+        <v>34</v>
+      </c>
       <c r="T9" s="12"/>
-      <c r="U9">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U9" s="59">
+        <v>50</v>
+      </c>
+      <c r="V9">
+        <f>SUM(N9:U9)/40</f>
+        <v>6.45</v>
+      </c>
+      <c r="W9" s="44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>39</v>
@@ -2760,19 +2818,16 @@
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q10" s="28"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="V10">
+        <f t="shared" ref="V10:V13" si="0">SUM(N10:U10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>33</v>
@@ -2808,22 +2863,37 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="N11" s="12">
+        <v>198</v>
+      </c>
+      <c r="O11" s="12">
+        <v>40</v>
+      </c>
+      <c r="P11" s="12">
+        <v>40</v>
+      </c>
       <c r="Q11" s="28">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>52</v>
+      </c>
+      <c r="S11" s="12">
+        <v>60</v>
+      </c>
+      <c r="T11" s="12"/>
+      <c r="U11" s="59">
+        <v>60</v>
+      </c>
+      <c r="V11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+        <v>11.25</v>
+      </c>
+      <c r="W11" s="44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -2847,19 +2917,16 @@
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="V12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -2874,15 +2941,16 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="V13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
@@ -2921,15 +2989,15 @@
       <c r="M14" s="10"/>
       <c r="N14" s="14">
         <f t="shared" ref="N14:T14" si="2">SUM(N8:N13)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="2"/>
@@ -2937,22 +3005,19 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U14" s="35" t="e">
-        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U14" s="35"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -2989,27 +3054,27 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="4">P14/20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="5">R14/20</f>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -3048,24 +3113,24 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="7">O15+O14</f>
-        <v>0</v>
+        <v>98.7</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>0</v>
+        <v>115.5</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>98.7</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="8"/>
@@ -3115,24 +3180,24 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="10">O14/40</f>
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="11">R14/40</f>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="11"/>
@@ -3140,7 +3205,7 @@
       </c>
       <c r="U17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
@@ -3164,7 +3229,7 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="M2:T5"/>
     <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3172,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52CB744-359B-4545-85D0-01C9D0099EAF}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -3183,13 +3248,12 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3202,7 +3266,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -3212,99 +3276,94 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3312,33 +3371,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="O6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="P6" s="70"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3369,48 +3427,45 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
+      <c r="R7" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
       <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
         <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="U7" s="12" t="s">
         <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3426,35 +3481,28 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
+      <c r="U8" s="28"/>
+      <c r="V8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -3463,42 +3511,52 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="C9" s="12">
+        <v>153</v>
+      </c>
+      <c r="D9" s="12">
+        <v>85</v>
+      </c>
+      <c r="E9" s="12">
+        <v>85</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>168</v>
+      </c>
+      <c r="H9" s="12">
+        <v>108</v>
+      </c>
+      <c r="I9" s="12">
+        <v>246</v>
+      </c>
+      <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+        <v>21.125</v>
+      </c>
+      <c r="K9" s="44">
+        <v>18</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="Q9" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
+      <c r="U9" s="28"/>
+      <c r="V9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -3507,42 +3565,52 @@
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="C10" s="12">
+        <v>100</v>
+      </c>
+      <c r="D10" s="12">
+        <v>40</v>
+      </c>
+      <c r="E10" s="12">
+        <v>40</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>99</v>
+      </c>
+      <c r="H10" s="12">
+        <v>54</v>
+      </c>
+      <c r="I10" s="12">
+        <v>181</v>
+      </c>
+      <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>12.85</v>
+      </c>
+      <c r="K10" s="44">
+        <v>11</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
+      <c r="U10" s="28"/>
+      <c r="V10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -3551,42 +3619,50 @@
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="C11" s="12">
+        <v>192</v>
+      </c>
+      <c r="D11" s="12">
+        <v>102</v>
+      </c>
+      <c r="E11" s="12">
+        <v>102</v>
+      </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="G11" s="12">
+        <v>38</v>
+      </c>
+      <c r="H11" s="12">
+        <v>88</v>
+      </c>
+      <c r="I11" s="12">
+        <v>82</v>
+      </c>
+      <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>15.1</v>
+      </c>
+      <c r="K11" s="44">
+        <v>8</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
+      <c r="U11" s="28"/>
+      <c r="V11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -3602,41 +3678,36 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>0</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
+      <c r="U12" s="28"/>
+      <c r="V12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="B13" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -3644,103 +3715,101 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="J13">
+        <v>95</v>
+      </c>
+      <c r="K13" s="74">
+        <v>7</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11" t="str">
+        <f>B13</f>
+        <v xml:space="preserve">Shakoor </v>
+      </c>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="U13" s="28"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>445</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>227</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>227</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>305</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="1"/>
+        <v>509</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>1963</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:T14" si="2">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="14"/>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
+      </c>
+      <c r="X14">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
@@ -3751,56 +3820,58 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>11.35</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>11.35</v>
       </c>
       <c r="F15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="3"/>
+        <v>15.25</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>12.5</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>25.45</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="T15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="X15">
+        <v>126</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
@@ -3809,141 +3880,153 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>238.35</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="6"/>
+        <v>238.35</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="6"/>
+        <v>320.25</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="6"/>
+        <v>262.5</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="6"/>
+        <v>534.45000000000005</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
+      <c r="T16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U16" s="36"/>
+      <c r="X16">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>11.125</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>5.6749999999999998</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="9"/>
+        <v>5.6749999999999998</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="9"/>
+        <v>7.625</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="9"/>
+        <v>6.25</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="9"/>
+        <v>12.725</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>49.075000000000003</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
+      <c r="T17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <f>400*5</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X18">
+        <f>Y18*40</f>
+        <v>1600</v>
+      </c>
+      <c r="Y18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -3953,16 +4036,25 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="X19">
+        <f>SUM(X14:X18)</f>
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="X20">
+        <f>X19/40</f>
+        <v>95.25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4017,95 +4109,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4113,33 +4205,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4818,95 +4910,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4914,33 +5006,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5632,95 +5724,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5728,33 +5820,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6430,95 +6522,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6526,33 +6618,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7227,95 +7319,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7323,33 +7415,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8033,95 +8125,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8129,33 +8221,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8845,95 +8937,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8941,33 +9033,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9669,58 +9761,58 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="59" t="s">
+      <c r="O2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
       <c r="AB2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
       <c r="AB3">
         <v>14</v>
       </c>
@@ -9733,51 +9825,51 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
     </row>
     <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="68"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9785,35 +9877,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="69" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10706,95 +10798,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10802,33 +10894,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11513,95 +11605,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11609,33 +11701,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12337,95 +12429,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12433,33 +12525,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13135,95 +13227,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13231,33 +13323,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13959,95 +14051,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14055,33 +14147,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14781,95 +14873,95 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14877,33 +14969,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15632,95 +15724,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15728,33 +15820,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -16430,95 +16522,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -16526,33 +16618,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -17231,95 +17323,95 @@
     </row>
     <row r="2" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -17327,33 +17419,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -18081,95 +18173,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -18177,33 +18269,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -18896,103 +18988,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="59" t="s">
+      <c r="O2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="68"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -19000,35 +19092,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="69" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -19981,95 +20073,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -20077,33 +20169,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -20779,95 +20871,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -20875,33 +20967,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -21578,95 +21670,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="65"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -21674,33 +21766,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="69" t="s">
+      <c r="Q6" s="70"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="71"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -22378,103 +22470,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="59" t="s">
+      <c r="O2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="68"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -22482,35 +22574,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="69" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -23422,103 +23514,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="59" t="s">
+      <c r="O2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="68"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -23526,35 +23618,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="69" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -24489,103 +24581,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="59" t="s">
+      <c r="O2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
     </row>
     <row r="4" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
     </row>
     <row r="5" spans="1:26" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="68"/>
     </row>
     <row r="6" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -24593,35 +24685,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="69" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -25259,103 +25351,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="59" t="s">
+      <c r="O2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="68"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -25363,35 +25455,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="69" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -26132,103 +26224,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="59" t="s">
+      <c r="O2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="62"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="65"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="65"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="66"/>
-      <c r="W5" s="66"/>
-      <c r="X5" s="67"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="68"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -26236,35 +26328,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="69" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="70"/>
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -27107,91 +27199,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="62"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="59" t="s">
+      <c r="M2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="62"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="65"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="64"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="65"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="64"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="65"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="64"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="65"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="68"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="66"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="67"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="68"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -27199,30 +27291,30 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="71"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="68" t="s">
+      <c r="O6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="69" t="s">
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="70"/>
+      <c r="U6" s="71"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB5393F-02DE-483A-A45E-E0BCA2B12E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9972EFC9-D0DA-48F0-B06B-C06714CF8D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="11" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="13" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="42">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -664,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -842,9 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3448,7 +3445,7 @@
         <v>11</v>
       </c>
       <c r="Q7" s="45" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R7" s="45" t="s">
         <v>13</v>
@@ -3487,16 +3484,13 @@
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="10" t="str">
-        <f>B8</f>
+        <f t="shared" ref="M8:M13" si="0">B8</f>
         <v>Furqan</v>
       </c>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="28">
-        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
@@ -3541,23 +3535,37 @@
       </c>
       <c r="L9" s="27"/>
       <c r="M9" s="10" t="str">
-        <f>B9</f>
+        <f t="shared" si="0"/>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="N9" s="12">
+        <v>124</v>
+      </c>
+      <c r="O9" s="12">
+        <v>82</v>
+      </c>
+      <c r="P9" s="12">
+        <v>82</v>
+      </c>
       <c r="Q9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>138</v>
+      </c>
+      <c r="S9" s="12">
+        <v>83</v>
+      </c>
       <c r="T9" s="12"/>
-      <c r="U9" s="28"/>
+      <c r="U9" s="28">
+        <v>190</v>
+      </c>
       <c r="V9">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
+        <f>SUM(N9:U9)/40</f>
+        <v>17.475000000000001</v>
+      </c>
+      <c r="W9" s="44">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
@@ -3595,23 +3603,37 @@
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="10" t="str">
-        <f>B10</f>
+        <f t="shared" si="0"/>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
+      <c r="N10" s="12">
+        <v>100</v>
+      </c>
+      <c r="O10" s="12">
+        <v>40</v>
+      </c>
+      <c r="P10" s="12">
+        <v>40</v>
+      </c>
       <c r="Q10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>19</v>
+      </c>
+      <c r="S10" s="12">
+        <v>14</v>
+      </c>
       <c r="T10" s="12"/>
-      <c r="U10" s="28"/>
+      <c r="U10" s="28">
+        <v>61</v>
+      </c>
       <c r="V10">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
+        <f t="shared" ref="V10:V12" si="1">SUM(N10:U10)/40</f>
+        <v>6.85</v>
+      </c>
+      <c r="W10" s="44">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
@@ -3647,23 +3669,37 @@
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
-        <f>B11</f>
+        <f t="shared" si="0"/>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="N11" s="12">
+        <v>140</v>
+      </c>
+      <c r="O11" s="12">
+        <v>102</v>
+      </c>
+      <c r="P11" s="12">
+        <v>102</v>
+      </c>
       <c r="Q11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>32</v>
+      </c>
+      <c r="S11" s="12">
+        <v>82</v>
+      </c>
       <c r="T11" s="12"/>
-      <c r="U11" s="28"/>
+      <c r="U11" s="28">
+        <v>82</v>
+      </c>
       <c r="V11">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>13.5</v>
+      </c>
+      <c r="W11" s="44">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
@@ -3684,22 +3720,19 @@
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
-        <f>B12</f>
+        <f t="shared" si="0"/>
         <v>Mubeen</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
       <c r="U12" s="28"/>
       <c r="V12">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -3718,21 +3751,18 @@
       <c r="J13">
         <v>95</v>
       </c>
-      <c r="K13" s="74">
+      <c r="K13" s="41">
         <v>7</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" s="11" t="str">
-        <f>B13</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
@@ -3742,31 +3772,31 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
         <v>445</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>227</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>227</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>305</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>509</v>
       </c>
       <c r="J14" s="35">
@@ -3776,31 +3806,31 @@
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:T14" si="2">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:T14" si="3">SUM(N8:N13)</f>
+        <v>364</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>224</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>224</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>189</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>179</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14" s="14"/>
@@ -3823,23 +3853,23 @@
         <v>11.35</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
         <v>11.35</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>15.25</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12.5</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25.45</v>
       </c>
       <c r="L15" s="13"/>
@@ -3849,23 +3879,23 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="4">P14/20</f>
-        <v>0</v>
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>11.2</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="5">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>9.4499999999999993</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>8.9499999999999993</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -3883,27 +3913,27 @@
         <v>445</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
         <v>238.35</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>238.35</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>320.25</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>262.5</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>534.45000000000005</v>
       </c>
       <c r="L16" s="13"/>
@@ -3912,27 +3942,27 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>235.2</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>235.2</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>198.45</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>187.95</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -3950,27 +3980,27 @@
         <v>11.125</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
         <v>5.6749999999999998</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.6749999999999998</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.625</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.25</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12.725</v>
       </c>
       <c r="J17" s="35">
@@ -3983,33 +4013,33 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="10">O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>5.6</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5.6</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="11">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>4.7249999999999996</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>4.4749999999999996</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="X17">
         <f>400*5</f>
@@ -4867,7 +4897,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400FD42A-C002-41E3-80E9-BA0AAA04C4EB}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -4878,15 +4908,14 @@
     <col min="6" max="6" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4896,7 +4925,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -4906,9 +4935,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="60" t="s">
         <v>36</v>
@@ -4920,21 +4948,20 @@
       <c r="G2" s="61"/>
       <c r="H2" s="61"/>
       <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="60" t="s">
         <v>37</v>
       </c>
+      <c r="N2" s="61"/>
       <c r="O2" s="61"/>
       <c r="P2" s="61"/>
       <c r="Q2" s="61"/>
       <c r="R2" s="61"/>
       <c r="S2" s="61"/>
       <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="62"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="63"/>
       <c r="C3" s="64"/>
@@ -4944,19 +4971,18 @@
       <c r="G3" s="64"/>
       <c r="H3" s="64"/>
       <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="64"/>
       <c r="O3" s="64"/>
       <c r="P3" s="64"/>
       <c r="Q3" s="64"/>
       <c r="R3" s="64"/>
       <c r="S3" s="64"/>
       <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="65"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="63"/>
       <c r="C4" s="64"/>
@@ -4966,19 +4992,18 @@
       <c r="G4" s="64"/>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="64"/>
       <c r="O4" s="64"/>
       <c r="P4" s="64"/>
       <c r="Q4" s="64"/>
       <c r="R4" s="64"/>
       <c r="S4" s="64"/>
       <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="65"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="66"/>
       <c r="C5" s="67"/>
@@ -4988,19 +5013,18 @@
       <c r="G5" s="67"/>
       <c r="H5" s="67"/>
       <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
       <c r="O5" s="67"/>
       <c r="P5" s="67"/>
       <c r="Q5" s="67"/>
       <c r="R5" s="67"/>
       <c r="S5" s="67"/>
       <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="68"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -5016,25 +5040,24 @@
       </c>
       <c r="H6" s="70"/>
       <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="O6" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="P6" s="70"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="70" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="70"/>
       <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="71"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -5063,52 +5086,49 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="12" t="s">
         <v>26</v>
       </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O7" s="58" t="s">
+      <c r="N7" s="58" t="s">
         <v>6</v>
       </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
       <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
       <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
         <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="U7" s="12" t="s">
         <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -5120,39 +5140,29 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28"/>
+      <c r="V8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -5164,171 +5174,179 @@
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
         <v>0</v>
       </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28"/>
+      <c r="V9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="C10" s="12">
+        <v>155</v>
+      </c>
+      <c r="D10" s="12">
+        <v>70</v>
+      </c>
+      <c r="E10" s="12">
+        <v>30</v>
+      </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="G10" s="12">
+        <v>200</v>
+      </c>
+      <c r="H10" s="12">
+        <v>100</v>
+      </c>
+      <c r="I10" s="12">
+        <v>290</v>
+      </c>
+      <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>21.125</v>
+      </c>
+      <c r="K10" s="44">
+        <v>8</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10" s="28"/>
+      <c r="V10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+      <c r="C11" s="12">
+        <v>172</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>100</v>
+      </c>
+      <c r="H11" s="12">
+        <v>105</v>
+      </c>
+      <c r="I11" s="12">
+        <v>115</v>
+      </c>
+      <c r="J11">
+        <f t="shared" ref="J11:J12" si="0">SUM(C11:F11,G11,H11,I11)/40</f>
+        <v>14.6</v>
+      </c>
+      <c r="K11" s="44">
+        <v>8</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11" s="28"/>
+      <c r="V11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>120</v>
+      </c>
+      <c r="E12" s="12">
+        <v>120</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="G12" s="12">
+        <f>120+80+40</f>
+        <v>240</v>
+      </c>
+      <c r="H12" s="12">
+        <f>120+80+40</f>
+        <v>240</v>
+      </c>
+      <c r="I12" s="12">
+        <f>200+160+160+80</f>
+        <v>600</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="K12" s="44">
+        <v>3</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
-      </c>
+        <v>Shakoor</v>
+      </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12" s="28"/>
+      <c r="V12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -5338,116 +5356,105 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="42" t="s">
+      <c r="J13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11">
+        <f>B13</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="42" t="s">
+      <c r="U13" s="28"/>
+      <c r="V13" s="42" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>327</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>236</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>196</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>540</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>445</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="1"/>
+        <v>1005</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10" t="s">
+        <v>2749</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -5455,205 +5462,202 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>22.25</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>50.25</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="T15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="D16" s="38">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>247.8</v>
       </c>
       <c r="E16" s="38">
+        <f t="shared" si="6"/>
+        <v>205.8</v>
+      </c>
+      <c r="F16" s="38">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38">
+        <f t="shared" si="6"/>
+        <v>567</v>
+      </c>
+      <c r="H16" s="38">
+        <f t="shared" si="6"/>
+        <v>467.25</v>
+      </c>
+      <c r="I16" s="38">
+        <f t="shared" si="6"/>
+        <v>1055.25</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="38">
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="38">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="38">
+      <c r="T16" s="38">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G16" s="38">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="38">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="38">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="K16" s="42" t="s">
+      <c r="U16" s="36"/>
+      <c r="V16" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="38">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="38">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="38">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="38">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-      <c r="W16" s="42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>8.1750000000000007</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>5.9</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="9"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="9"/>
+        <v>13.5</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="9"/>
+        <v>11.125</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="9"/>
+        <v>25.125</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>68.724999999999994</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
+      <c r="T17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -5663,16 +5667,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9972EFC9-D0DA-48F0-B06B-C06714CF8D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E780B-F4E9-490E-A6F8-E44BF88AD8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="13" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="14" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="42">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -664,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -801,6 +801,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -842,6 +845,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1188,57 +1194,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="B2" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1246,18 +1252,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1607,95 +1613,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1703,33 +1709,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2497,87 +2503,87 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2585,32 +2591,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="69" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="73"/>
-      <c r="T6" s="73"/>
-      <c r="U6" s="73"/>
+      <c r="S6" s="74"/>
+      <c r="T6" s="74"/>
+      <c r="U6" s="74"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3276,91 +3282,91 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="65"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="65"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="68"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3368,32 +3374,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="69" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="70" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3767,6 +3773,12 @@
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="28"/>
+      <c r="V13">
+        <v>74</v>
+      </c>
+      <c r="W13" s="41">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
@@ -4139,95 +4151,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4235,33 +4247,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4897,7 +4909,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400FD42A-C002-41E3-80E9-BA0AAA04C4EB}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -4912,6 +4924,852 @@
     <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="63"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="66"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="66"/>
+    </row>
+    <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="69"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="R7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" s="27"/>
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8">
+        <f>SUM(C8:F8,G8,H8,I8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
+        <f t="shared" ref="M8:M13" si="0">B8</f>
+        <v>Furqan</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8">
+        <f>SUM(N8:T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" s="27"/>
+      <c r="B9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9">
+        <f>SUM(C9:F9,G9,H9,I9)/40</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Salman</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9">
+        <f>SUM(N9:T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" s="27"/>
+      <c r="B10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="12">
+        <v>155</v>
+      </c>
+      <c r="D10" s="12">
+        <v>70</v>
+      </c>
+      <c r="E10" s="12">
+        <v>30</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12">
+        <v>200</v>
+      </c>
+      <c r="H10" s="12">
+        <v>100</v>
+      </c>
+      <c r="I10" s="12">
+        <v>290</v>
+      </c>
+      <c r="J10">
+        <f>SUM(C10:F10,G10,H10,I10)/40</f>
+        <v>21.125</v>
+      </c>
+      <c r="K10" s="44">
+        <v>8</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Zesahn</v>
+      </c>
+      <c r="N10" s="12">
+        <v>155</v>
+      </c>
+      <c r="O10" s="12">
+        <v>53</v>
+      </c>
+      <c r="P10" s="12">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>200</v>
+      </c>
+      <c r="R10" s="12">
+        <v>100</v>
+      </c>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12">
+        <v>290</v>
+      </c>
+      <c r="U10">
+        <f>SUM(N10:T10)/40</f>
+        <v>20.7</v>
+      </c>
+      <c r="V10" s="44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="12">
+        <v>172</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>100</v>
+      </c>
+      <c r="H11" s="12">
+        <v>105</v>
+      </c>
+      <c r="I11" s="12">
+        <v>115</v>
+      </c>
+      <c r="J11">
+        <f t="shared" ref="J11:J12" si="1">SUM(C11:F11,G11,H11,I11)/40</f>
+        <v>14.6</v>
+      </c>
+      <c r="K11" s="44">
+        <v>8</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Umair</v>
+      </c>
+      <c r="N11" s="12">
+        <v>182</v>
+      </c>
+      <c r="O11" s="12">
+        <v>46</v>
+      </c>
+      <c r="P11" s="12">
+        <v>46</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>115</v>
+      </c>
+      <c r="R11" s="12">
+        <v>115</v>
+      </c>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12">
+        <v>130</v>
+      </c>
+      <c r="U11">
+        <f>SUM(N11:T11)/40</f>
+        <v>15.85</v>
+      </c>
+      <c r="V11" s="44">
+        <v>9</v>
+      </c>
+      <c r="X11">
+        <v>660</v>
+      </c>
+      <c r="Y11">
+        <v>1780</v>
+      </c>
+      <c r="Z11">
+        <f>Y11+X11</f>
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12">
+        <v>120</v>
+      </c>
+      <c r="E12" s="12">
+        <v>120</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12">
+        <f>120+80+40</f>
+        <v>240</v>
+      </c>
+      <c r="H12" s="12">
+        <f>120+80+40</f>
+        <v>240</v>
+      </c>
+      <c r="I12" s="12">
+        <f>200+160+160+80</f>
+        <v>600</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="K12" s="44">
+        <v>3</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Shakoor</v>
+      </c>
+      <c r="N12" s="12">
+        <v>240</v>
+      </c>
+      <c r="O12" s="12">
+        <v>140</v>
+      </c>
+      <c r="P12" s="12">
+        <v>280</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>500</v>
+      </c>
+      <c r="R12" s="12">
+        <v>320</v>
+      </c>
+      <c r="S12" s="12">
+        <v>480</v>
+      </c>
+      <c r="T12" s="12">
+        <v>480</v>
+      </c>
+      <c r="U12">
+        <v>49</v>
+      </c>
+      <c r="V12" s="44">
+        <v>6</v>
+      </c>
+      <c r="Z12">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="14">
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <v>327</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>236</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="2"/>
+        <v>196</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="2"/>
+        <v>540</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>445</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="2"/>
+        <v>1005</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>2749</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:T14" si="3">SUM(N8:N13)</f>
+        <v>577</v>
+      </c>
+      <c r="O14" s="14">
+        <f t="shared" si="3"/>
+        <v>239</v>
+      </c>
+      <c r="P14" s="14">
+        <f t="shared" si="3"/>
+        <v>356</v>
+      </c>
+      <c r="Q14" s="14">
+        <f t="shared" si="3"/>
+        <v>815</v>
+      </c>
+      <c r="R14" s="14">
+        <f t="shared" si="3"/>
+        <v>535</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="T14" s="36">
+        <f t="shared" si="3"/>
+        <v>900</v>
+      </c>
+      <c r="U14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+Q14+R14+S14</f>
+        <v>#REF!</v>
+      </c>
+      <c r="W14">
+        <v>2440</v>
+      </c>
+      <c r="X14">
+        <f>W14/40</f>
+        <v>61</v>
+      </c>
+      <c r="Z14">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13">
+        <f>D14/20</f>
+        <v>11.8</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F15" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="4"/>
+        <v>22.25</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="4"/>
+        <v>50.25</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>11.95</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>17.8</v>
+      </c>
+      <c r="Q15" s="13">
+        <f t="shared" ref="Q15:S15" si="6">Q14/20</f>
+        <v>40.75</v>
+      </c>
+      <c r="R15" s="13">
+        <f t="shared" si="6"/>
+        <v>26.75</v>
+      </c>
+      <c r="S15" s="13">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="T15" s="13"/>
+      <c r="Z15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="36">
+        <f>C15+C14</f>
+        <v>327</v>
+      </c>
+      <c r="D16" s="38">
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>247.8</v>
+      </c>
+      <c r="E16" s="38">
+        <f t="shared" si="7"/>
+        <v>205.8</v>
+      </c>
+      <c r="F16" s="38">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="38">
+        <f t="shared" si="7"/>
+        <v>567</v>
+      </c>
+      <c r="H16" s="38">
+        <f t="shared" si="7"/>
+        <v>467.25</v>
+      </c>
+      <c r="I16" s="38">
+        <f t="shared" si="7"/>
+        <v>1055.25</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>577</v>
+      </c>
+      <c r="O16" s="38">
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>250.95</v>
+      </c>
+      <c r="P16" s="38">
+        <f t="shared" si="8"/>
+        <v>373.8</v>
+      </c>
+      <c r="Q16" s="38">
+        <f t="shared" ref="Q16:S16" si="9">Q15+Q14</f>
+        <v>855.75</v>
+      </c>
+      <c r="R16" s="38">
+        <f t="shared" si="9"/>
+        <v>561.75</v>
+      </c>
+      <c r="S16" s="38">
+        <f t="shared" si="9"/>
+        <v>504</v>
+      </c>
+      <c r="T16" s="36"/>
+      <c r="U16" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z16">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A17" s="13"/>
+      <c r="B17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="36">
+        <f>C14/40</f>
+        <v>8.1750000000000007</v>
+      </c>
+      <c r="D17" s="36">
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>5.9</v>
+      </c>
+      <c r="E17" s="36">
+        <f t="shared" si="10"/>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="10"/>
+        <v>11.125</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="10"/>
+        <v>25.125</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>68.724999999999994</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>14.425000000000001</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>5.9749999999999996</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="11"/>
+        <v>8.9</v>
+      </c>
+      <c r="Q17" s="36">
+        <f t="shared" ref="Q17:S17" si="12">Q14/40</f>
+        <v>20.375</v>
+      </c>
+      <c r="R17" s="36">
+        <f t="shared" si="12"/>
+        <v>13.375</v>
+      </c>
+      <c r="S17" s="36">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="T17" s="36"/>
+      <c r="U17" s="35">
+        <f>SUM(N17:S17)</f>
+        <v>75.05</v>
+      </c>
+      <c r="Z17">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="C18" s="32"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:I5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:T5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:T6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE31C1E2-A8F9-4087-95F5-CC61C8293F6A}">
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4938,91 +5796,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="63"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="65"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="66"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="65"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="66"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="68"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="69"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5030,32 +5888,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="69" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="70" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="72"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5133,16 +5991,29 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="C8" s="12">
+        <v>142</v>
+      </c>
+      <c r="D8" s="12">
+        <v>12</v>
+      </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="G8" s="12">
+        <v>30</v>
+      </c>
+      <c r="H8" s="12">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12">
+        <v>60</v>
+      </c>
       <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="K8" s="44">
+        <v>9</v>
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="10" t="str">
@@ -5152,11 +6023,11 @@
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="28"/>
+      <c r="Q8" s="12"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="28"/>
+      <c r="U8" s="12"/>
       <c r="V8">
         <f>SUM(N8:P8,R8,S8,T8)/40</f>
         <v>0</v>
@@ -5167,16 +6038,29 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="C9" s="12">
+        <v>175</v>
+      </c>
+      <c r="D9" s="12">
+        <v>45</v>
+      </c>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="G9" s="12">
+        <v>77</v>
+      </c>
+      <c r="H9" s="12">
+        <v>16</v>
+      </c>
+      <c r="I9" s="12">
+        <v>127</v>
+      </c>
       <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="K9" s="44">
+        <v>7</v>
       </c>
       <c r="L9" s="27"/>
       <c r="M9" s="10" t="str">
@@ -5186,11 +6070,11 @@
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="28"/>
+      <c r="Q9" s="12"/>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="28"/>
+      <c r="U9" s="12"/>
       <c r="V9">
         <f>SUM(N9:P9,R9,S9,T9)/40</f>
         <v>0</v>
@@ -5202,30 +6086,30 @@
         <v>39</v>
       </c>
       <c r="C10" s="12">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="D10" s="12">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E10" s="12">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="H10" s="12">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I10" s="12">
-        <v>290</v>
+        <v>170</v>
       </c>
       <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>21.125</v>
+        <v>14.75</v>
       </c>
       <c r="K10" s="44">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="10" t="str">
@@ -5235,11 +6119,11 @@
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="28"/>
+      <c r="Q10" s="12"/>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="28"/>
+      <c r="U10" s="12"/>
       <c r="V10">
         <f>SUM(N10:P10,R10,S10,T10)/40</f>
         <v>0</v>
@@ -5251,7 +6135,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="12">
-        <v>172</v>
+        <v>308</v>
       </c>
       <c r="D11" s="12">
         <v>46</v>
@@ -5263,20 +6147,20 @@
         <v>0</v>
       </c>
       <c r="G11" s="12">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H11" s="12">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="I11" s="12">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="J11">
-        <f t="shared" ref="J11:J12" si="0">SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>14.6</v>
-      </c>
-      <c r="K11" s="44">
-        <v>8</v>
+        <f>SUM(C11:F11,G11,H11,I11)/40</f>
+        <v>12</v>
+      </c>
+      <c r="K11" s="75">
+        <v>14</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
@@ -5286,11 +6170,11 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="28"/>
+      <c r="Q11" s="12"/>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="28"/>
+      <c r="U11" s="12"/>
       <c r="V11">
         <f>SUM(N11:P11,R11,S11,T11)/40</f>
         <v>0</v>
@@ -5299,48 +6183,32 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12">
-        <v>120</v>
-      </c>
-      <c r="E12" s="12">
-        <v>120</v>
-      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="12"/>
-      <c r="G12" s="12">
-        <f>120+80+40</f>
-        <v>240</v>
-      </c>
-      <c r="H12" s="12">
-        <f>120+80+40</f>
-        <v>240</v>
-      </c>
-      <c r="I12" s="12">
-        <f>200+160+160+80</f>
-        <v>600</v>
-      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
       <c r="J12">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="K12" s="44">
-        <v>3</v>
+        <f>SUM(C12:F12,G12,H12,I12)/40</f>
+        <v>0</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Shakoor</v>
+        <v>Mubeen</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="28"/>
+      <c r="Q12" s="12"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="28"/>
+      <c r="U12" s="12"/>
       <c r="V12">
         <f>SUM(N12:P12,R12,S12,T12)/40</f>
         <v>0</v>
@@ -5356,100 +6224,84 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="42" t="s">
-        <v>24</v>
-      </c>
       <c r="L13" s="11"/>
-      <c r="M13" s="11">
-        <f>B13</f>
-        <v>0</v>
-      </c>
+      <c r="M13" s="11"/>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="28"/>
+      <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="42" t="s">
-        <v>24</v>
-      </c>
+      <c r="U13" s="12"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
-      <c r="B14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
-        <v>327</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="1"/>
-        <v>236</v>
-      </c>
-      <c r="E14" s="14">
-        <f t="shared" si="1"/>
-        <v>196</v>
-      </c>
-      <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
-      <c r="H14" s="14">
-        <f t="shared" si="1"/>
-        <v>445</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" si="1"/>
-        <v>1005</v>
+      <c r="B14" s="10"/>
+      <c r="C14" s="36">
+        <f t="shared" ref="C14:I14" si="0">SUM(C8:C13)</f>
+        <v>715</v>
+      </c>
+      <c r="D14" s="36">
+        <f t="shared" si="0"/>
+        <v>223</v>
+      </c>
+      <c r="E14" s="36">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="F14" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="36">
+        <f t="shared" si="0"/>
+        <v>197</v>
+      </c>
+      <c r="H14" s="36">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="I14" s="36">
+        <f t="shared" si="0"/>
+        <v>397</v>
       </c>
       <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>2749</v>
+        <v>1779</v>
       </c>
       <c r="L14" s="13"/>
-      <c r="M14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="35" t="e">
+      <c r="M14" s="10"/>
+      <c r="N14" s="36">
+        <f t="shared" ref="N14:T14" si="1">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="36"/>
+      <c r="V14" s="60" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
@@ -5462,27 +6314,27 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>11.8</v>
+        <v>11.15</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="3">E14/20</f>
-        <v>9.8000000000000007</v>
+        <f t="shared" ref="E15:I15" si="2">E14/20</f>
+        <v>6.3</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="3"/>
-        <v>27</v>
+        <f t="shared" si="2"/>
+        <v>9.85</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
-        <v>22.25</v>
+        <f t="shared" si="2"/>
+        <v>6.05</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
-        <v>50.25</v>
+        <f t="shared" si="2"/>
+        <v>19.850000000000001</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -5494,20 +6346,20 @@
         <v>0</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="4">P14/20</f>
+        <f t="shared" ref="P15" si="3">P14/20</f>
         <v>0</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <f t="shared" ref="R15:T15" si="4">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -5519,34 +6371,31 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>327</v>
-      </c>
-      <c r="D16" s="38">
-        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
-        <v>247.8</v>
-      </c>
-      <c r="E16" s="38">
-        <f t="shared" si="6"/>
-        <v>205.8</v>
-      </c>
-      <c r="F16" s="38">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="38">
-        <f t="shared" si="6"/>
-        <v>567</v>
-      </c>
-      <c r="H16" s="38">
-        <f t="shared" si="6"/>
-        <v>467.25</v>
-      </c>
-      <c r="I16" s="38">
-        <f t="shared" si="6"/>
-        <v>1055.25</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>25</v>
+        <v>715</v>
+      </c>
+      <c r="D16" s="36">
+        <f t="shared" ref="D16:I16" si="5">D15+D14</f>
+        <v>234.15</v>
+      </c>
+      <c r="E16" s="36">
+        <f t="shared" si="5"/>
+        <v>132.30000000000001</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="5"/>
+        <v>206.85</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="5"/>
+        <v>127.05</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="5"/>
+        <v>416.85</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -5556,31 +6405,28 @@
         <f>N15+N14</f>
         <v>0</v>
       </c>
-      <c r="O16" s="38">
-        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="38">
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="6">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="7">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="38">
-        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>0</v>
-      </c>
-      <c r="S16" s="38">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="38">
-        <f t="shared" si="8"/>
+      <c r="T16" s="36">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
-      <c r="V16" s="42" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
@@ -5589,35 +6435,35 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>8.1750000000000007</v>
+        <v>17.875</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="9">D14/40</f>
-        <v>5.9</v>
+        <f t="shared" ref="D17:I17" si="8">D14/40</f>
+        <v>5.5750000000000002</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="9"/>
-        <v>4.9000000000000004</v>
+        <f t="shared" si="8"/>
+        <v>3.15</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="9"/>
-        <v>13.5</v>
+        <f t="shared" si="8"/>
+        <v>4.9249999999999998</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="9"/>
-        <v>11.125</v>
+        <f t="shared" si="8"/>
+        <v>3.0249999999999999</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="9"/>
-        <v>25.125</v>
+        <f t="shared" si="8"/>
+        <v>9.9250000000000007</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>68.724999999999994</v>
+        <v>44.474999999999994</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">
@@ -5628,24 +6474,24 @@
         <v>0</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <f t="shared" ref="O17:P17" si="9">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <f t="shared" ref="R17:T17" si="10">R14/40</f>
         <v>0</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
@@ -5676,804 +6522,6 @@
     <mergeCell ref="M2:U5"/>
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="R6:U6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE31C1E2-A8F9-4087-95F5-CC61C8293F6A}">
-  <dimension ref="A1:X19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08984375" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="69" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="69" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
-        <v>3</v>
-      </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="43" t="str">
-        <f>B8</f>
-        <v>Furqan</v>
-      </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
-      <c r="B9" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="43" t="str">
-        <f>B9</f>
-        <v>Salman</v>
-      </c>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
-      <c r="B10" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="43" t="str">
-        <f>B10</f>
-        <v>Zesahn</v>
-      </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="43" t="str">
-        <f>B11</f>
-        <v>Umair</v>
-      </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="43" t="str">
-        <f>B12</f>
-        <v>Mubeen</v>
-      </c>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13">
-        <f>D14/20</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="36">
-        <f>C15+C14</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="36">
-        <f>C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6525,95 +6573,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6621,33 +6669,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7322,95 +7370,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7418,33 +7466,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8128,95 +8176,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8224,33 +8272,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8940,95 +8988,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9036,33 +9084,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9764,58 +9812,58 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="63"/>
       <c r="AB2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
       <c r="AB3">
         <v>14</v>
       </c>
@@ -9828,51 +9876,51 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="68"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="69"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9880,35 +9928,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="70" t="s">
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10801,95 +10849,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10897,33 +10945,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11608,95 +11656,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11704,33 +11752,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12432,95 +12480,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12528,33 +12576,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13230,95 +13278,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13326,33 +13374,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14054,95 +14102,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14150,33 +14198,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14876,95 +14924,95 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14972,33 +15020,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15727,95 +15775,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15823,33 +15871,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -16525,95 +16573,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -16621,33 +16669,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -17326,95 +17374,95 @@
     </row>
     <row r="2" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -17422,33 +17470,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -18176,95 +18224,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -18272,33 +18320,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -18991,103 +19039,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="63"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="68"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="69"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -19095,35 +19143,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="70" t="s">
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -20076,95 +20124,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -20172,33 +20220,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -20874,95 +20922,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -20970,33 +21018,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -21673,95 +21721,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="65"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="68"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -21769,33 +21817,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="70" t="s">
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -22473,103 +22521,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="63"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="68"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="69"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -22577,35 +22625,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="70" t="s">
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -23517,103 +23565,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="63"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="68"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="69"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -23621,35 +23669,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="70" t="s">
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -24584,103 +24632,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="63"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
     </row>
     <row r="4" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:26" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="68"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="69"/>
     </row>
     <row r="6" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -24688,35 +24736,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="70" t="s">
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -25354,103 +25402,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="63"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="68"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="69"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -25458,35 +25506,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="70" t="s">
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -26227,103 +26275,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="63"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="63"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="66"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="65"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="66"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="65"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="66"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="69"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="68"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="69"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -26331,35 +26379,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="70" t="s">
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="72"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="70" t="s">
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -27202,91 +27250,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="63"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="65"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="66"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="65"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="66"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="68"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="69"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -27294,30 +27342,30 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="69" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="72"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E780B-F4E9-490E-A6F8-E44BF88AD8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978EC407-5827-4C82-8FAC-F0C4F294DCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="14" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="42">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -846,7 +846,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5754,7 +5754,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE31C1E2-A8F9-4087-95F5-CC61C8293F6A}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -5770,6 +5770,825 @@
     <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="63"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="66"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="66"/>
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="69"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A8" s="27"/>
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="12">
+        <v>142</v>
+      </c>
+      <c r="D8" s="12">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12">
+        <v>30</v>
+      </c>
+      <c r="H8" s="12">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12">
+        <v>60</v>
+      </c>
+      <c r="J8">
+        <f>SUM(C8:F8,G8,H8,I8)/40</f>
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="K8" s="44">
+        <v>9</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
+        <f>B8</f>
+        <v>Furqan</v>
+      </c>
+      <c r="N8" s="12">
+        <v>142</v>
+      </c>
+      <c r="O8" s="12">
+        <v>12</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>30</v>
+      </c>
+      <c r="S8" s="12">
+        <v>25</v>
+      </c>
+      <c r="T8" s="12">
+        <v>60</v>
+      </c>
+      <c r="U8">
+        <f>SUM(N8:T8)/40</f>
+        <v>6.7249999999999996</v>
+      </c>
+      <c r="V8" s="44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A9" s="27"/>
+      <c r="B9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="12">
+        <v>175</v>
+      </c>
+      <c r="D9" s="12">
+        <v>45</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12">
+        <v>77</v>
+      </c>
+      <c r="H9" s="12">
+        <v>16</v>
+      </c>
+      <c r="I9" s="12">
+        <v>127</v>
+      </c>
+      <c r="J9">
+        <f>SUM(C9:F9,G9,H9,I9)/40</f>
+        <v>11</v>
+      </c>
+      <c r="K9" s="44">
+        <v>7</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
+        <f>B9</f>
+        <v>Salman</v>
+      </c>
+      <c r="N9" s="12">
+        <v>174</v>
+      </c>
+      <c r="O9" s="12">
+        <v>41</v>
+      </c>
+      <c r="P9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>57</v>
+      </c>
+      <c r="S9" s="12">
+        <v>16</v>
+      </c>
+      <c r="T9" s="12">
+        <v>104</v>
+      </c>
+      <c r="U9">
+        <f t="shared" ref="U9:U12" si="0">SUM(N9:T9)/40</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="V9" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A10" s="27"/>
+      <c r="B10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="12">
+        <v>90</v>
+      </c>
+      <c r="D10" s="12">
+        <v>120</v>
+      </c>
+      <c r="E10" s="12">
+        <v>80</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12">
+        <v>70</v>
+      </c>
+      <c r="H10" s="12">
+        <v>60</v>
+      </c>
+      <c r="I10" s="12">
+        <v>170</v>
+      </c>
+      <c r="J10">
+        <f>SUM(C10:F10,G10,H10,I10)/40</f>
+        <v>14.75</v>
+      </c>
+      <c r="K10" s="44">
+        <v>14</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
+        <f>B10</f>
+        <v>Zesahn</v>
+      </c>
+      <c r="N10" s="12">
+        <v>80</v>
+      </c>
+      <c r="O10" s="12">
+        <v>120</v>
+      </c>
+      <c r="P10" s="12">
+        <v>80</v>
+      </c>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12">
+        <v>70</v>
+      </c>
+      <c r="S10" s="12">
+        <v>60</v>
+      </c>
+      <c r="T10" s="12">
+        <v>170</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="V10" s="44">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="12">
+        <v>308</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>20</v>
+      </c>
+      <c r="H11" s="12">
+        <v>20</v>
+      </c>
+      <c r="I11" s="12">
+        <v>40</v>
+      </c>
+      <c r="J11">
+        <f>SUM(C11:F11,G11,H11,I11)/40</f>
+        <v>12</v>
+      </c>
+      <c r="K11" s="41">
+        <v>14</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
+        <f>B11</f>
+        <v>Umair</v>
+      </c>
+      <c r="N11" s="12">
+        <v>307</v>
+      </c>
+      <c r="O11" s="12">
+        <v>46</v>
+      </c>
+      <c r="P11" s="12">
+        <v>46</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>20</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <v>40</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="0"/>
+        <v>11.475</v>
+      </c>
+      <c r="V11" s="44">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12">
+        <f>SUM(C12:F12,G12,H12,I12)/40</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12">
+        <v>120</v>
+      </c>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12">
+        <v>360</v>
+      </c>
+      <c r="S12" s="12">
+        <v>600</v>
+      </c>
+      <c r="T12" s="12">
+        <v>320</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="V12" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="36">
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>715</v>
+      </c>
+      <c r="D14" s="36">
+        <f t="shared" si="1"/>
+        <v>223</v>
+      </c>
+      <c r="E14" s="36">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="F14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="36">
+        <f t="shared" si="1"/>
+        <v>197</v>
+      </c>
+      <c r="H14" s="36">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="I14" s="36">
+        <f t="shared" si="1"/>
+        <v>397</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>1779</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="36">
+        <f t="shared" ref="N14:S14" si="2">SUM(N8:N13)</f>
+        <v>703</v>
+      </c>
+      <c r="O14" s="36">
+        <f t="shared" si="2"/>
+        <v>339</v>
+      </c>
+      <c r="P14" s="36">
+        <f t="shared" si="2"/>
+        <v>126</v>
+      </c>
+      <c r="Q14" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="36">
+        <f t="shared" si="2"/>
+        <v>537</v>
+      </c>
+      <c r="S14" s="36">
+        <f t="shared" si="2"/>
+        <v>701</v>
+      </c>
+      <c r="T14" s="36"/>
+      <c r="U14" s="60" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13">
+        <f>D14/20</f>
+        <v>11.15</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>6.3</v>
+      </c>
+      <c r="F15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="3"/>
+        <v>9.85</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>6.05</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>19.850000000000001</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>16.95</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>6.3</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:S15" si="5">R14/20</f>
+        <v>26.85</v>
+      </c>
+      <c r="S15" s="13">
+        <f t="shared" si="5"/>
+        <v>35.049999999999997</v>
+      </c>
+      <c r="T15" s="13"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="36">
+        <f>C15+C14</f>
+        <v>715</v>
+      </c>
+      <c r="D16" s="36">
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>234.15</v>
+      </c>
+      <c r="E16" s="36">
+        <f t="shared" si="6"/>
+        <v>132.30000000000001</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="6"/>
+        <v>206.85</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="6"/>
+        <v>127.05</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="6"/>
+        <v>416.85</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>703</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>355.95</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="7"/>
+        <v>132.30000000000001</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:S16" si="8">R15+R14</f>
+        <v>563.85</v>
+      </c>
+      <c r="S16" s="36">
+        <f t="shared" si="8"/>
+        <v>736.05</v>
+      </c>
+      <c r="T16" s="36"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A17" s="13"/>
+      <c r="B17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="36">
+        <f>C14/40</f>
+        <v>17.875</v>
+      </c>
+      <c r="D17" s="36">
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>5.5750000000000002</v>
+      </c>
+      <c r="E17" s="36">
+        <f t="shared" si="9"/>
+        <v>3.15</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="9"/>
+        <v>4.9249999999999998</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="9"/>
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="9"/>
+        <v>9.9250000000000007</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>44.474999999999994</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>17.574999999999999</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>8.4749999999999996</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="10"/>
+        <v>3.15</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:S17" si="11">R14/40</f>
+        <v>13.425000000000001</v>
+      </c>
+      <c r="S17" s="36">
+        <f t="shared" si="11"/>
+        <v>17.524999999999999</v>
+      </c>
+      <c r="T17" s="36"/>
+      <c r="U17" s="35">
+        <f>SUM(N17:S17)</f>
+        <v>60.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="C18" s="32"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:I5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:T5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:T6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6570164-B7E7-4177-A35A-60E2B49B6F1E}">
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5965,7 +6784,7 @@
         <v>11</v>
       </c>
       <c r="Q7" s="45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R7" s="45" t="s">
         <v>13</v>
@@ -5977,7 +6796,7 @@
         <v>12</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V7" s="12" t="s">
         <v>27</v>
@@ -5992,28 +6811,32 @@
         <v>17</v>
       </c>
       <c r="C8" s="12">
+        <v>40</v>
+      </c>
+      <c r="D8" s="12">
+        <v>40</v>
+      </c>
+      <c r="E8" s="12">
+        <v>40</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>86</v>
+      </c>
+      <c r="H8" s="12">
+        <v>92</v>
+      </c>
+      <c r="I8" s="12">
         <v>142</v>
-      </c>
-      <c r="D8" s="12">
-        <v>12</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12">
-        <v>30</v>
-      </c>
-      <c r="H8" s="12">
-        <v>25</v>
-      </c>
-      <c r="I8" s="12">
-        <v>60</v>
       </c>
       <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>6.7249999999999996</v>
+        <v>11</v>
       </c>
       <c r="K8" s="44">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="10" t="str">
@@ -6023,11 +6846,17 @@
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>0</v>
+      </c>
       <c r="V8">
         <f>SUM(N8:P8,R8,S8,T8)/40</f>
         <v>0</v>
@@ -6039,28 +6868,32 @@
         <v>14</v>
       </c>
       <c r="C9" s="12">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="D9" s="12">
-        <v>45</v>
-      </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+        <v>112</v>
+      </c>
+      <c r="E9" s="12">
+        <v>106</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
       <c r="G9" s="12">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="H9" s="12">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="I9" s="12">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>11</v>
+        <v>14.75</v>
       </c>
       <c r="K9" s="44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="27"/>
       <c r="M9" s="10" t="str">
@@ -6070,11 +6903,17 @@
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
+      <c r="Q9" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U13" si="1">SUM(R9:T9)/20</f>
+        <v>0</v>
+      </c>
       <c r="V9">
         <f>SUM(N9:P9,R9,S9,T9)/40</f>
         <v>0</v>
@@ -6086,30 +6925,30 @@
         <v>39</v>
       </c>
       <c r="C10" s="12">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="D10" s="12">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="E10" s="12">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="H10" s="12">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="I10" s="12">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>14.75</v>
-      </c>
-      <c r="K10" s="44">
-        <v>14</v>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K10" s="75">
+        <v>12</v>
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="10" t="str">
@@ -6119,11 +6958,17 @@
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
+      <c r="Q10" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
+      <c r="U10" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="V10">
         <f>SUM(N10:P10,R10,S10,T10)/40</f>
         <v>0</v>
@@ -6135,32 +6980,32 @@
         <v>33</v>
       </c>
       <c r="C11" s="12">
-        <v>308</v>
+        <v>72</v>
       </c>
       <c r="D11" s="12">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E11" s="12">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="F11" s="12">
         <v>0</v>
       </c>
       <c r="G11" s="12">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H11" s="12">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I11" s="12">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>12</v>
+        <v>5.35</v>
       </c>
       <c r="K11" s="75">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
@@ -6170,11 +7015,17 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
+      <c r="Q11" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
+      <c r="U11" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="V11">
         <f>SUM(N11:P11,R11,S11,T11)/40</f>
         <v>0</v>
@@ -6183,7 +7034,7 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -6193,22 +7044,30 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
+        <v>150</v>
+      </c>
+      <c r="K12" s="75">
+        <v>1</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
+        <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
+      <c r="Q12" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
+      <c r="U12" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="V12">
         <f>SUM(N12:P12,R12,S12,T12)/40</f>
         <v>0</v>
@@ -6229,79 +7088,88 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
+      <c r="Q13" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
+      <c r="U13" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="36">
-        <f t="shared" ref="C14:I14" si="0">SUM(C8:C13)</f>
-        <v>715</v>
-      </c>
-      <c r="D14" s="36">
-        <f t="shared" si="0"/>
-        <v>223</v>
-      </c>
-      <c r="E14" s="36">
-        <f t="shared" si="0"/>
-        <v>126</v>
-      </c>
-      <c r="F14" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="36">
-        <f t="shared" si="0"/>
-        <v>197</v>
-      </c>
-      <c r="H14" s="36">
-        <f t="shared" si="0"/>
-        <v>121</v>
-      </c>
-      <c r="I14" s="36">
-        <f t="shared" si="0"/>
-        <v>397</v>
+      <c r="C14" s="14">
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <v>456</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>207</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="2"/>
+        <v>201</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="2"/>
+        <v>245</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>233</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="2"/>
+        <v>254</v>
       </c>
       <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>1779</v>
+        <v>1596</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="36">
-        <f t="shared" ref="N14:T14" si="1">SUM(N8:N13)</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="36"/>
-      <c r="V14" s="60" t="e">
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
@@ -6314,27 +7182,27 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>11.15</v>
+        <v>10.35</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="2">E14/20</f>
-        <v>6.3</v>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>10.050000000000001</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="2"/>
-        <v>9.85</v>
+        <f t="shared" si="4"/>
+        <v>12.25</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
-        <v>6.05</v>
+        <f t="shared" si="4"/>
+        <v>11.65</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
-        <v>19.850000000000001</v>
+        <f t="shared" si="4"/>
+        <v>12.7</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -6346,20 +7214,20 @@
         <v>0</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="3">P14/20</f>
+        <f t="shared" ref="P15" si="5">P14/20</f>
         <v>0</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="4">R14/20</f>
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -6371,31 +7239,31 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>715</v>
+        <v>456</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="5">D15+D14</f>
-        <v>234.15</v>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>217.35</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="5"/>
-        <v>132.30000000000001</v>
+        <f t="shared" si="7"/>
+        <v>211.05</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="5"/>
-        <v>206.85</v>
+        <f t="shared" si="7"/>
+        <v>257.25</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="5"/>
-        <v>127.05</v>
+        <f t="shared" si="7"/>
+        <v>244.65</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="5"/>
-        <v>416.85</v>
+        <f t="shared" si="7"/>
+        <v>266.7</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -6406,24 +7274,24 @@
         <v>0</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="6">O15+O14</f>
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="7">R15+R14</f>
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
         <v>0</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -6435,35 +7303,35 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>17.875</v>
+        <v>11.4</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="8">D14/40</f>
-        <v>5.5750000000000002</v>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>5.1749999999999998</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="8"/>
-        <v>3.15</v>
+        <f t="shared" si="10"/>
+        <v>5.0250000000000004</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="8"/>
-        <v>4.9249999999999998</v>
+        <f t="shared" si="10"/>
+        <v>6.125</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="8"/>
-        <v>3.0249999999999999</v>
+        <f t="shared" si="10"/>
+        <v>5.8250000000000002</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="8"/>
-        <v>9.9250000000000007</v>
+        <f t="shared" si="10"/>
+        <v>6.35</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>44.474999999999994</v>
+        <v>39.900000000000006</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">
@@ -6474,24 +7342,24 @@
         <v>0</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="9">O14/40</f>
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="10">R14/40</f>
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
         <v>0</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
@@ -6522,804 +7390,6 @@
     <mergeCell ref="M2:U5"/>
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="R6:U6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6570164-B7E7-4177-A35A-60E2B49B6F1E}">
-  <dimension ref="A1:X19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08984375" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
-        <f>B8</f>
-        <v>Furqan</v>
-      </c>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
-      <c r="B9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
-        <f>B9</f>
-        <v>Salman</v>
-      </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
-      <c r="B10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
-        <f>B10</f>
-        <v>Zesahn</v>
-      </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
-        <f>B11</f>
-        <v>Umair</v>
-      </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
-        <f>B12</f>
-        <v>Mubeen</v>
-      </c>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13">
-        <f>D14/20</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="36">
-        <f>C15+C14</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="36">
-        <f>C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978EC407-5827-4C82-8FAC-F0C4F294DCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A94082E-F69E-442C-84DB-DCB835B0D627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="14" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="7" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -664,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -845,9 +845,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6947,7 +6944,7 @@
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="K10" s="75">
+      <c r="K10" s="44">
         <v>12</v>
       </c>
       <c r="L10" s="27"/>
@@ -7004,7 +7001,7 @@
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
         <v>5.35</v>
       </c>
-      <c r="K11" s="75">
+      <c r="K11" s="44">
         <v>8</v>
       </c>
       <c r="L11" s="11"/>
@@ -7046,7 +7043,7 @@
       <c r="J12">
         <v>150</v>
       </c>
-      <c r="K12" s="75">
+      <c r="K12" s="44">
         <v>1</v>
       </c>
       <c r="L12" s="11"/>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A94082E-F69E-442C-84DB-DCB835B0D627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9B581F-7ABA-47A2-93B6-5F396ABFE310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="7" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="16" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -6771,7 +6771,7 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="58" t="s">
+      <c r="N7" s="37" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="56" t="s">
@@ -6780,8 +6780,8 @@
       <c r="P7" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="45" t="s">
-        <v>8</v>
+      <c r="Q7" s="56" t="s">
+        <v>12</v>
       </c>
       <c r="R7" s="45" t="s">
         <v>13</v>
@@ -6789,11 +6789,11 @@
       <c r="S7" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="T7" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="U7" s="12" t="s">
-        <v>8</v>
+      <c r="U7" s="45" t="s">
+        <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
         <v>27</v>
@@ -6840,23 +6840,34 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
+      <c r="N8" s="12">
+        <v>40</v>
+      </c>
+      <c r="O8" s="12">
+        <v>39</v>
+      </c>
+      <c r="P8" s="12">
+        <v>40</v>
+      </c>
       <c r="Q8" s="28">
-        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>86</v>
+      </c>
+      <c r="S8" s="12">
+        <v>92</v>
+      </c>
       <c r="T8" s="12"/>
       <c r="U8" s="28">
-        <f>SUM(R8:T8)/20</f>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="V8">
-        <f>SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
+        <f>SUM(N8:U8)/40</f>
+        <v>10.975</v>
+      </c>
+      <c r="W8" s="44">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
@@ -6897,23 +6908,34 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="N9" s="12">
+        <v>102</v>
+      </c>
+      <c r="O9" s="12">
+        <v>112</v>
+      </c>
+      <c r="P9" s="12">
+        <v>106</v>
+      </c>
       <c r="Q9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>92</v>
+      </c>
+      <c r="S9" s="12">
+        <v>96</v>
+      </c>
       <c r="T9" s="12"/>
       <c r="U9" s="28">
-        <f t="shared" ref="U9:U13" si="1">SUM(R9:T9)/20</f>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="V9">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="V9:V12" si="0">SUM(N9:U9)/40</f>
+        <v>14.75</v>
+      </c>
+      <c r="W9" s="44">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
@@ -6952,23 +6974,34 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
+      <c r="N10" s="12">
+        <v>162</v>
+      </c>
+      <c r="O10" s="12">
+        <v>35</v>
+      </c>
+      <c r="P10" s="12">
+        <v>35</v>
+      </c>
       <c r="Q10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>13</v>
+      </c>
+      <c r="S10" s="12">
+        <v>11</v>
+      </c>
       <c r="T10" s="12"/>
       <c r="U10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>6.55</v>
+      </c>
+      <c r="W10" s="44">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
@@ -7009,23 +7042,34 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="N11" s="12">
+        <v>72</v>
+      </c>
+      <c r="O11" s="12">
+        <v>20</v>
+      </c>
+      <c r="P11" s="12">
+        <v>20</v>
+      </c>
       <c r="Q11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>44</v>
+      </c>
+      <c r="S11" s="12">
+        <v>34</v>
+      </c>
       <c r="T11" s="12"/>
       <c r="U11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.35</v>
+      </c>
+      <c r="W11" s="44">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
@@ -7034,14 +7078,25 @@
         <v>34</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1000</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H12" s="12">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1000</v>
+      </c>
       <c r="J12">
-        <v>150</v>
+        <f>SUM(C12:F12,G12,H12,I12)/40</f>
+        <v>125</v>
       </c>
       <c r="K12" s="44">
         <v>1</v>
@@ -7052,22 +7107,29 @@
         <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
+      <c r="O12" s="12">
+        <v>1000</v>
+      </c>
+      <c r="P12" s="12">
+        <v>1000</v>
+      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12">
+        <v>1000</v>
+      </c>
+      <c r="S12" s="12">
+        <v>880</v>
+      </c>
       <c r="T12" s="12"/>
       <c r="U12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V12">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>122</v>
+      </c>
+      <c r="W12" s="44">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
@@ -7085,90 +7147,87 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="U13" s="28"/>
+      <c r="W13" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
         <v>456</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
-        <v>207</v>
+        <f t="shared" si="1"/>
+        <v>1207</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
-        <v>201</v>
+        <f t="shared" si="1"/>
+        <v>1201</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
-        <v>245</v>
+        <f t="shared" si="1"/>
+        <v>1245</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
-        <v>233</v>
+        <f t="shared" si="1"/>
+        <v>1233</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
-        <v>254</v>
+        <f t="shared" si="1"/>
+        <v>1254</v>
       </c>
       <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>1596</v>
+        <v>6596</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
+        <v>376</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1206</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1201</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1235</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1113</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="35" t="e">
-        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>1254</v>
+      </c>
+      <c r="V14" s="35">
+        <f>SUM(N14:U14)</f>
+        <v>6385</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.35">
@@ -7179,27 +7238,27 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>10.35</v>
+        <v>60.35</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="4">E14/20</f>
-        <v>10.050000000000001</v>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>60.05</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="4"/>
-        <v>12.25</v>
+        <f t="shared" si="3"/>
+        <v>62.25</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="4"/>
-        <v>11.65</v>
+        <f t="shared" si="3"/>
+        <v>61.65</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="4"/>
-        <v>12.7</v>
+        <f t="shared" si="3"/>
+        <v>62.7</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -7208,23 +7267,23 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>60.3</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="5">P14/20</f>
-        <v>0</v>
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>60.05</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="6">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>61.75</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>55.65</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -7239,28 +7298,28 @@
         <v>456</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
-        <v>217.35</v>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>1267.3499999999999</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="7"/>
-        <v>211.05</v>
+        <f t="shared" si="6"/>
+        <v>1261.05</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="7"/>
-        <v>257.25</v>
+        <f t="shared" si="6"/>
+        <v>1307.25</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="7"/>
-        <v>244.65</v>
+        <f t="shared" si="6"/>
+        <v>1294.6500000000001</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="7"/>
-        <v>266.7</v>
+        <f t="shared" si="6"/>
+        <v>1316.7</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -7268,27 +7327,27 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>1266.3</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1261.05</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>1296.75</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1168.6500000000001</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -7303,32 +7362,32 @@
         <v>11.4</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="10">D14/40</f>
-        <v>5.1749999999999998</v>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>30.175000000000001</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="10"/>
-        <v>5.0250000000000004</v>
+        <f t="shared" si="9"/>
+        <v>30.024999999999999</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="10"/>
-        <v>6.125</v>
+        <f t="shared" si="9"/>
+        <v>31.125</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="10"/>
-        <v>5.8250000000000002</v>
+        <f t="shared" si="9"/>
+        <v>30.824999999999999</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="10"/>
-        <v>6.35</v>
+        <f t="shared" si="9"/>
+        <v>31.35</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>39.900000000000006</v>
+        <v>164.89999999999998</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">
@@ -7336,33 +7395,33 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="11">O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>30.15</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>30.024999999999999</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="12">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>30.875</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>27.824999999999999</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>128.27499999999998</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -7394,7 +7453,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A2FBED-8856-42CC-977B-5977D4F16323}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -7405,15 +7464,14 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7423,7 +7481,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -7433,9 +7491,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>36</v>
@@ -7447,21 +7504,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>37</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -7471,19 +7527,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -7493,19 +7548,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -7515,19 +7569,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -7543,25 +7596,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -7590,193 +7642,200 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="44">
+      <c r="C8" s="12">
+        <v>40</v>
+      </c>
+      <c r="D8" s="12">
+        <v>40</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>135</v>
+      </c>
+      <c r="H8" s="12">
+        <v>70</v>
+      </c>
+      <c r="I8" s="12">
+        <v>75</v>
+      </c>
+      <c r="J8">
+        <f>SUM(C8:I8)/40</f>
+        <v>9</v>
+      </c>
+      <c r="K8" s="44">
         <v>5</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28"/>
+      <c r="V8">
+        <f>SUM(N8:U8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="44">
-        <v>9</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="D9" s="12">
+        <v>60</v>
+      </c>
+      <c r="E9" s="12">
+        <v>20</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>122</v>
+      </c>
+      <c r="H9" s="12">
+        <v>101</v>
+      </c>
+      <c r="I9" s="12">
+        <v>97</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
+        <v>10</v>
+      </c>
+      <c r="K9" s="44">
+        <v>8</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28"/>
+      <c r="V9">
+        <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="44">
-        <v>6</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+      <c r="C10" s="12">
+        <v>150</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>40</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>76</v>
+      </c>
+      <c r="H10" s="12">
+        <v>86</v>
+      </c>
+      <c r="I10" s="12">
+        <v>96</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>11.2</v>
+      </c>
+      <c r="K10" s="44">
+        <v>12</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10" s="28"/>
+      <c r="V10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>33</v>
@@ -7788,39 +7847,29 @@
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11" s="28"/>
+      <c r="V11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -7832,39 +7881,29 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12" s="28"/>
+      <c r="V12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -7874,106 +7913,92 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U13" s="28"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <v>190</v>
       </c>
       <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="2"/>
+        <v>333</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>257</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="2"/>
+        <v>268</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>1208</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E14" s="14">
+      <c r="P14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F14" s="14">
+      <c r="Q14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="R14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="S14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="T14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J14" s="14">
+      <c r="U14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -7981,199 +8006,196 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>3</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>16.649999999999999</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>12.85</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <f t="shared" si="4"/>
+        <v>13.4</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>105</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="7"/>
+        <v>63</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="7"/>
+        <v>349.65</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="7"/>
+        <v>269.85000000000002</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="7"/>
+        <v>281.39999999999998</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>2.5</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="10"/>
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="10"/>
+        <v>8.3249999999999993</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="10"/>
+        <v>6.4249999999999998</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="10"/>
+        <v>6.7</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>30.2</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -8183,16 +8205,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9B581F-7ABA-47A2-93B6-5F396ABFE310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94501647-FA30-43B8-929F-5A3C83248F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="16" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="42">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -664,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -845,6 +845,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7722,17 +7728,34 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+      <c r="N8" s="12">
+        <v>40</v>
+      </c>
+      <c r="O8" s="12">
+        <v>40</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="28">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>95</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
       <c r="T8" s="12"/>
-      <c r="U8" s="28"/>
+      <c r="U8" s="28">
+        <v>35</v>
+      </c>
       <c r="V8">
         <f>SUM(N8:U8)/40</f>
-        <v>0</v>
+        <v>5.25</v>
+      </c>
+      <c r="W8" s="44">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
@@ -7772,16 +7795,31 @@
         <v>Salman</v>
       </c>
       <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+      <c r="O9" s="12">
+        <v>60</v>
+      </c>
+      <c r="P9" s="12">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>109</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
       <c r="T9" s="12"/>
-      <c r="U9" s="28"/>
+      <c r="U9" s="28">
+        <v>83</v>
+      </c>
       <c r="V9">
         <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
-        <v>0</v>
+        <v>6.8</v>
+      </c>
+      <c r="W9" s="75">
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
@@ -7822,17 +7860,34 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="N10" s="12">
+        <v>20</v>
+      </c>
+      <c r="O10" s="12">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="28">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>76</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
       <c r="T10" s="12"/>
-      <c r="U10" s="28"/>
+      <c r="U10" s="28">
+        <v>86</v>
+      </c>
       <c r="V10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.55</v>
+      </c>
+      <c r="W10" s="75">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
@@ -7963,15 +8018,15 @@
       <c r="M14" s="10"/>
       <c r="N14" s="14">
         <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="3"/>
@@ -7979,7 +8034,7 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="3"/>
@@ -7991,7 +8046,7 @@
       </c>
       <c r="U14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -8035,16 +8090,16 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="5">P14/20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="6">R14/20</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="6"/>
@@ -8095,20 +8150,20 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="8">O15+O14</f>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="9">R15+R14</f>
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="9"/>
@@ -8163,20 +8218,20 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="11">O14/40</f>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="12">R14/40</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="12"/>
@@ -8189,7 +8244,7 @@
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -8221,7 +8276,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257F4DF8-C865-4EAB-87FC-B54CA70AD20E}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -8229,18 +8284,17 @@
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.08984375" customWidth="1"/>
     <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8250,7 +8304,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -8260,9 +8314,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>36</v>
@@ -8274,21 +8327,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>37</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -8298,19 +8350,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -8320,19 +8371,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -8342,19 +8392,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -8370,25 +8419,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -8417,283 +8465,330 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="45">
+      <c r="C8" s="12">
+        <v>44</v>
+      </c>
+      <c r="D8" s="12">
+        <v>42</v>
+      </c>
+      <c r="E8" s="12">
+        <v>42</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>66</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>66</v>
+      </c>
+      <c r="J8" s="76">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="45">
-        <v>7</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+        <v>6.5</v>
+      </c>
+      <c r="K8" s="76">
+        <v>6</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="45">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="45">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="45">
+      <c r="C9" s="12">
+        <v>92</v>
+      </c>
+      <c r="D9" s="12">
+        <v>60</v>
+      </c>
+      <c r="E9" s="12">
+        <v>60</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>72</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12">
+        <v>92</v>
+      </c>
+      <c r="J9" s="76">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="45">
-        <v>9</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+        <v>9.4</v>
+      </c>
+      <c r="K9" s="76">
+        <v>4</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="Q9" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="45">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U13" si="1">SUM(R9:T9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="45">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="C10" s="12">
+        <v>222</v>
+      </c>
+      <c r="D10" s="12">
+        <v>90</v>
+      </c>
+      <c r="E10" s="12">
+        <v>90</v>
+      </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="45">
+      <c r="G10" s="12">
+        <v>152</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>160</v>
+      </c>
+      <c r="J10" s="76">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="45">
-        <v>17</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="K10" s="76">
+        <v>20</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="45">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="45">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="40">
+      <c r="C11" s="12">
+        <v>460</v>
+      </c>
+      <c r="D11" s="12">
+        <v>40</v>
+      </c>
+      <c r="E11" s="12">
+        <v>40</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>146</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>100</v>
+      </c>
+      <c r="J11" s="76">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="40"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>19.649999999999999</v>
+      </c>
+      <c r="K11" s="76">
+        <v>11</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="40">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="40">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="40">
+      <c r="D12" s="12">
+        <v>960</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1480</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>1240</v>
+      </c>
+      <c r="H12" s="12">
+        <v>1320</v>
+      </c>
+      <c r="I12" s="12">
+        <v>2080</v>
+      </c>
+      <c r="J12" s="76">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="40"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+        <v>177</v>
+      </c>
+      <c r="K12" s="76">
+        <v>11</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
-      </c>
+        <v xml:space="preserve">Shakoor </v>
+      </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="40">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V12" s="40">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -8703,109 +8798,100 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="J13" s="40"/>
       <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W13" s="40"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U13" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="40"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <v>818</v>
       </c>
       <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>1192</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="2"/>
+        <v>1712</v>
+      </c>
+      <c r="F14" s="14">
+        <v>1960</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="2"/>
+        <v>1676</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>1320</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="2"/>
+        <v>2498</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>11176</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E14" s="14">
+      <c r="P14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F14" s="14">
+      <c r="Q14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="R14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="S14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="T14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J14" s="14">
+      <c r="U14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -8813,199 +8899,196 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>59.6</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>85.6</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>98</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>83.8</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>66</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <f t="shared" si="4"/>
+        <v>124.9</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>1251.5999999999999</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="7"/>
+        <v>1797.6</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="7"/>
+        <v>2058</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="7"/>
+        <v>1759.8</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="7"/>
+        <v>1386</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="7"/>
+        <v>2622.9</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>20.45</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>29.8</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="10"/>
+        <v>42.8</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="10"/>
+        <v>49</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="10"/>
+        <v>41.9</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="10"/>
+        <v>33</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="10"/>
+        <v>62.45</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>279.40000000000003</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -9015,16 +9098,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94501647-FA30-43B8-929F-5A3C83248F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34033E70-8B84-42E3-B880-F6EBC8F85915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="16" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="17" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="41">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -146,9 +146,6 @@
   </si>
   <si>
     <t>ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Executed </t>
   </si>
   <si>
     <t>Executed</t>
@@ -664,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -845,12 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1532,12 +1523,12 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -1552,12 +1543,12 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1617,7 +1608,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -1629,7 +1620,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -1958,7 +1949,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>140</v>
@@ -2030,7 +2021,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>172</v>
@@ -2507,7 +2498,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -2518,7 +2509,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -2686,7 +2677,7 @@
         <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W7" s="59" t="s">
         <v>26</v>
@@ -2792,7 +2783,7 @@
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12">
@@ -2836,7 +2827,7 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>210</v>
@@ -3286,7 +3277,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -3297,7 +3288,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -3580,7 +3571,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>100</v>
@@ -3648,7 +3639,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>192</v>
@@ -3748,7 +3739,7 @@
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -4155,7 +4146,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -4167,7 +4158,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -4443,7 +4434,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -4487,7 +4478,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -4953,7 +4944,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -4964,7 +4955,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -5203,7 +5194,7 @@
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>155</v>
@@ -5266,7 +5257,7 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>172</v>
@@ -5341,7 +5332,7 @@
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12">
@@ -5798,7 +5789,7 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -5809,7 +5800,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -6108,7 +6099,7 @@
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>90</v>
@@ -6171,7 +6162,7 @@
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>308</v>
@@ -6253,7 +6244,7 @@
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12">
@@ -6619,7 +6610,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -6630,7 +6621,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -6947,7 +6938,7 @@
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>242</v>
@@ -7013,7 +7004,7 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>72</v>
@@ -7081,7 +7072,7 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12">
@@ -7501,7 +7492,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -7512,7 +7503,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -7818,14 +7809,14 @@
         <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
         <v>6.8</v>
       </c>
-      <c r="W9" s="75">
+      <c r="W9" s="44">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>150</v>
@@ -7886,14 +7877,14 @@
         <f t="shared" si="1"/>
         <v>5.55</v>
       </c>
-      <c r="W10" s="75">
+      <c r="W10" s="44">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -8318,7 +8309,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -8329,7 +8320,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -8476,7 +8467,7 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="58" t="s">
+      <c r="N7" s="37" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="56" t="s">
@@ -8485,8 +8476,8 @@
       <c r="P7" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="45" t="s">
-        <v>8</v>
+      <c r="Q7" s="56" t="s">
+        <v>12</v>
       </c>
       <c r="R7" s="45" t="s">
         <v>13</v>
@@ -8494,11 +8485,11 @@
       <c r="S7" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="T7" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="U7" s="12" t="s">
-        <v>8</v>
+      <c r="U7" s="45" t="s">
+        <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
         <v>27</v>
@@ -8533,11 +8524,11 @@
       <c r="I8" s="12">
         <v>66</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="12">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>6.5</v>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="12">
         <v>6</v>
       </c>
       <c r="L8" s="27"/>
@@ -8546,22 +8537,31 @@
         <v>Furqan</v>
       </c>
       <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
+      <c r="O8" s="12">
+        <v>0</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
       <c r="Q8" s="28">
-        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>60</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
       <c r="T8" s="12"/>
       <c r="U8" s="28">
-        <f>SUM(R8:T8)/20</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V8" s="45">
-        <f>SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
+        <f>SUM(N8:U8)/40</f>
+        <v>3</v>
+      </c>
+      <c r="W8" s="59">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
@@ -8590,11 +8590,11 @@
       <c r="I9" s="12">
         <v>92</v>
       </c>
-      <c r="J9" s="76">
+      <c r="J9" s="12">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
         <v>9.4</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="12">
         <v>4</v>
       </c>
       <c r="L9" s="27"/>
@@ -8602,29 +8602,40 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="N9" s="12">
+        <v>92</v>
+      </c>
+      <c r="O9" s="12">
+        <v>40</v>
+      </c>
+      <c r="P9" s="12">
+        <v>40</v>
+      </c>
       <c r="Q9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>72</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
       <c r="T9" s="12"/>
       <c r="U9" s="28">
-        <f t="shared" ref="U9:U13" si="1">SUM(R9:T9)/20</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="V9" s="45">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="V9:V11" si="0">SUM(N9:U9)/40</f>
+        <v>8.4</v>
+      </c>
+      <c r="W9" s="59">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>222</v>
@@ -8645,11 +8656,11 @@
       <c r="I10" s="12">
         <v>160</v>
       </c>
-      <c r="J10" s="76">
+      <c r="J10" s="12">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
         <v>17.850000000000001</v>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="12">
         <v>20</v>
       </c>
       <c r="L10" s="27"/>
@@ -8657,29 +8668,40 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
+      <c r="N10" s="12">
+        <v>222</v>
+      </c>
+      <c r="O10" s="12">
+        <v>90</v>
+      </c>
+      <c r="P10" s="12">
+        <v>90</v>
+      </c>
       <c r="Q10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>152</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
       <c r="T10" s="12"/>
       <c r="U10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="V10" s="45">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>17.850000000000001</v>
+      </c>
+      <c r="W10" s="59">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>460</v>
@@ -8702,11 +8724,11 @@
       <c r="I11" s="12">
         <v>100</v>
       </c>
-      <c r="J11" s="76">
+      <c r="J11" s="12">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
         <v>19.649999999999999</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="12">
         <v>11</v>
       </c>
       <c r="L11" s="11"/>
@@ -8714,29 +8736,40 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="N11" s="12">
+        <v>460</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0</v>
+      </c>
       <c r="Q11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>86</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
       <c r="T11" s="12"/>
       <c r="U11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="40">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="V11" s="45">
+        <f t="shared" si="0"/>
+        <v>15.65</v>
+      </c>
+      <c r="W11" s="41">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12">
@@ -8757,11 +8790,11 @@
       <c r="I12" s="12">
         <v>2080</v>
       </c>
-      <c r="J12" s="76">
+      <c r="J12" s="12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>177</v>
       </c>
-      <c r="K12" s="76">
+      <c r="K12" s="12">
         <v>11</v>
       </c>
       <c r="L12" s="11"/>
@@ -8772,20 +8805,16 @@
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="40">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
-        <v>0</v>
+      <c r="U12" s="28"/>
+      <c r="V12" s="45">
+        <v>71</v>
+      </c>
+      <c r="W12" s="41">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
@@ -8805,47 +8834,41 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="U13" s="28"/>
       <c r="V13" s="40"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
         <v>818</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1192</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1712</v>
       </c>
       <c r="F14" s="14">
         <v>1960</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1676</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1320</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2498</v>
       </c>
       <c r="J14" s="35">
@@ -8855,36 +8878,36 @@
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
+        <v>774</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>130</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>130</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>370</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>392</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -8902,23 +8925,23 @@
         <v>59.6</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
         <v>85.6</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>83.8</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>66</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>124.9</v>
       </c>
       <c r="L15" s="13"/>
@@ -8928,23 +8951,23 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="5">P14/20</f>
-        <v>0</v>
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>6.5</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="6">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>18.5</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -8959,27 +8982,27 @@
         <v>818</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
         <v>1251.5999999999999</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1797.6</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2058</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1759.8</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1386</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2622.9</v>
       </c>
       <c r="L16" s="13"/>
@@ -8988,27 +9011,27 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>136.5</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>136.5</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>388.5</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -9023,27 +9046,27 @@
         <v>20.45</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
         <v>29.8</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>42.8</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>41.9</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>62.45</v>
       </c>
       <c r="J17" s="35">
@@ -9056,33 +9079,33 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="11">O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>3.25</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>3.25</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="12">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>9.25</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -9114,7 +9137,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48CE528A-B31C-4333-9BC5-136993154ACA}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -9125,16 +9148,15 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9144,7 +9166,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -9154,12 +9176,11 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -9168,21 +9189,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
-        <v>37</v>
-      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -9192,19 +9212,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -9214,19 +9233,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -9236,19 +9254,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -9264,25 +9281,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -9311,240 +9327,277 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="C8" s="12">
+        <v>76</v>
+      </c>
+      <c r="D8" s="12">
+        <v>26</v>
+      </c>
+      <c r="E8" s="12">
+        <v>20</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>38</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>26</v>
+      </c>
+      <c r="J8" s="44">
+        <f>SUM(C8:I8)/40</f>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K8" s="44">
+        <v>5</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="C9" s="12">
+        <v>155</v>
+      </c>
+      <c r="D9" s="12">
+        <v>20</v>
+      </c>
+      <c r="E9" s="12">
+        <v>70</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>70</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12">
+        <v>95</v>
+      </c>
+      <c r="J9" s="44">
+        <f t="shared" ref="J9:J12" si="1">SUM(C9:I9)/40</f>
+        <v>10.25</v>
+      </c>
+      <c r="K9" s="44">
+        <v>5</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="Q9" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U13" si="2">SUM(R9:T9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
+        <v>38</v>
+      </c>
+      <c r="C10" s="12">
+        <v>74</v>
+      </c>
+      <c r="D10" s="12">
+        <v>30</v>
+      </c>
+      <c r="E10" s="12">
+        <v>30</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>470</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>110</v>
+      </c>
+      <c r="J10" s="44">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="K10" s="44">
+        <v>14</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
+      <c r="U10" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
+        <v>32</v>
+      </c>
+      <c r="C11" s="12">
+        <v>180</v>
+      </c>
+      <c r="D11" s="12">
+        <v>60</v>
+      </c>
+      <c r="E11" s="12">
+        <v>60</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>90</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>50</v>
+      </c>
+      <c r="J11" s="44">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>11</v>
+      </c>
+      <c r="K11" s="44">
+        <v>8</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
+      <c r="U11" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -9556,42 +9609,35 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
+      <c r="J12" s="44">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
+      <c r="U12" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -9601,41 +9647,38 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="J13" s="44"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
+      <c r="U13" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
+        <v>485</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
@@ -9643,7 +9686,7 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
@@ -9651,20 +9694,20 @@
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <v>281</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>1750</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="4">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
@@ -9691,16 +9734,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -9708,11 +9747,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="5"/>
@@ -9720,7 +9759,7 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>33.4</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="5"/>
@@ -9728,56 +9767,55 @@
       </c>
       <c r="I15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="L15" t="s">
+        <v>14.05</v>
+      </c>
+      <c r="K15" t="s">
         <v>28</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="6">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="7">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="8"/>
@@ -9785,7 +9823,7 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>701.4</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="8"/>
@@ -9793,56 +9831,55 @@
       </c>
       <c r="I16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
+        <v>295.05</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
       <c r="O16" s="36">
-        <f>O15+O14</f>
+        <f t="shared" ref="O16:P16" si="9">O15+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="10">R15+R14</f>
+        <v>0</v>
+      </c>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>12.125</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="11"/>
@@ -9850,7 +9887,7 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="11"/>
@@ -9858,52 +9895,51 @@
       </c>
       <c r="I17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
+        <v>7.0250000000000004</v>
+      </c>
+      <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
+        <v>43.749999999999993</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
         <v>23</v>
       </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
       <c r="O17" s="36">
-        <f>O14/40</f>
+        <f t="shared" ref="O17:P17" si="12">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="13">R14/40</f>
+        <v>0</v>
+      </c>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -9913,16 +9949,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9983,7 +10018,7 @@
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -9996,7 +10031,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -10008,7 +10043,7 @@
       <c r="W2" s="62"/>
       <c r="X2" s="63"/>
       <c r="AB2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
@@ -10255,7 +10290,7 @@
         <v>46174</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P8" s="12">
         <v>284</v>
@@ -10421,7 +10456,7 @@
       </c>
       <c r="N10" s="27"/>
       <c r="O10" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P10" s="12">
         <v>86</v>
@@ -10539,7 +10574,7 @@
     <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12">
         <v>382</v>
@@ -11020,7 +11055,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -11032,7 +11067,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -11238,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="10" t="str">
@@ -11285,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="10" t="str">
@@ -11314,7 +11349,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -11332,7 +11367,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="10" t="str">
@@ -11361,7 +11396,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -11827,7 +11862,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -11839,7 +11874,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -12121,7 +12156,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -12168,7 +12203,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -12651,7 +12686,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -12663,7 +12698,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -12939,7 +12974,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="29"/>
       <c r="D10" s="29"/>
@@ -12983,7 +13018,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -13449,7 +13484,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -13461,7 +13496,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -13743,7 +13778,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -13790,7 +13825,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -14273,7 +14308,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -14285,7 +14320,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -14567,7 +14602,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -14614,7 +14649,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -15072,7 +15107,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -15084,7 +15119,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -15095,7 +15130,7 @@
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -15107,7 +15142,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -15406,7 +15441,7 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -15460,7 +15495,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -15946,7 +15981,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -15958,7 +15993,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -16234,7 +16269,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -16278,7 +16313,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -16744,7 +16779,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -16756,7 +16791,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -17032,7 +17067,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -17076,7 +17111,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -17545,7 +17580,7 @@
     <row r="2" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -17557,7 +17592,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -17856,7 +17891,7 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -17908,7 +17943,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -18395,7 +18430,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -18407,7 +18442,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -18689,7 +18724,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -18736,7 +18771,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -19210,7 +19245,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -19223,7 +19258,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -19602,7 +19637,7 @@
         <v>46175</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>60</v>
@@ -19687,7 +19722,7 @@
         <v>46175</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>276</v>
@@ -19847,7 +19882,7 @@
         <v>46175</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12">
@@ -20295,7 +20330,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -20307,7 +20342,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -20583,7 +20618,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -20627,7 +20662,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -21093,7 +21128,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -21105,7 +21140,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -21381,7 +21416,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -21425,7 +21460,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -21892,7 +21927,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -21904,7 +21939,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -22180,7 +22215,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -22224,7 +22259,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -22692,7 +22727,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -22705,7 +22740,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -23067,7 +23102,7 @@
         <v>46176</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>100</v>
@@ -23154,7 +23189,7 @@
         <v>46176</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>612</v>
@@ -23326,7 +23361,7 @@
         <v>46176</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P13" s="12"/>
       <c r="Q13" s="12">
@@ -23736,7 +23771,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -23749,7 +23784,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -24111,7 +24146,7 @@
         <v>46177</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>262</v>
@@ -24198,7 +24233,7 @@
         <v>46177</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>182</v>
@@ -24371,7 +24406,7 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12">
@@ -24803,7 +24838,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -24816,7 +24851,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -25573,7 +25608,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -25586,7 +25621,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -25920,7 +25955,7 @@
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>200</v>
@@ -25998,7 +26033,7 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>280</v>
@@ -26446,7 +26481,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -26459,7 +26494,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -26802,7 +26837,7 @@
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>40</v>
@@ -26876,7 +26911,7 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12">
         <v>242</v>
@@ -27421,7 +27456,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -27432,7 +27467,7 @@
       <c r="I2" s="63"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -27751,7 +27786,7 @@
         <v>46181</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="12">
         <v>40</v>
@@ -27855,7 +27890,7 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12">
         <v>254</v>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34033E70-8B84-42E3-B880-F6EBC8F85915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20EE2B2-BB6B-4049-AA62-B7B36C3F47CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="17" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="20" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="40">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>ok</t>
   </si>
   <si>
     <t>Executed</t>
@@ -661,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -842,6 +839,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1523,12 +1526,12 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -1543,12 +1546,12 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1611,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -1620,7 +1623,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -1949,7 +1952,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>140</v>
@@ -2021,7 +2024,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>172</v>
@@ -2498,7 +2501,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -2509,7 +2512,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -2677,7 +2680,7 @@
         <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W7" s="59" t="s">
         <v>26</v>
@@ -2783,7 +2786,7 @@
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12">
@@ -2827,7 +2830,7 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>210</v>
@@ -3277,7 +3280,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -3288,7 +3291,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -3571,7 +3574,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>100</v>
@@ -3639,7 +3642,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>192</v>
@@ -3739,7 +3742,7 @@
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -4146,7 +4149,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -4158,7 +4161,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -4434,7 +4437,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -4478,7 +4481,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -4944,7 +4947,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -4955,7 +4958,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -5194,7 +5197,7 @@
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>155</v>
@@ -5257,7 +5260,7 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>172</v>
@@ -5332,7 +5335,7 @@
     <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12">
@@ -5789,7 +5792,7 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -5800,7 +5803,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -6099,7 +6102,7 @@
     <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>90</v>
@@ -6162,7 +6165,7 @@
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>308</v>
@@ -6244,7 +6247,7 @@
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12">
@@ -6610,7 +6613,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -6621,7 +6624,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -6938,7 +6941,7 @@
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>242</v>
@@ -7004,7 +7007,7 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>72</v>
@@ -7072,7 +7075,7 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12">
@@ -7492,7 +7495,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -7503,7 +7506,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -7816,7 +7819,7 @@
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>150</v>
@@ -7884,7 +7887,7 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -8309,7 +8312,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -8320,7 +8323,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -8635,7 +8638,7 @@
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>222</v>
@@ -8701,7 +8704,7 @@
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>460</v>
@@ -8769,7 +8772,7 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12">
@@ -9180,7 +9183,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -9191,7 +9194,7 @@
       <c r="I2" s="62"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -9338,7 +9341,7 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="58" t="s">
+      <c r="N7" s="75" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="56" t="s">
@@ -9347,8 +9350,8 @@
       <c r="P7" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="45" t="s">
-        <v>8</v>
+      <c r="Q7" s="56" t="s">
+        <v>12</v>
       </c>
       <c r="R7" s="45" t="s">
         <v>13</v>
@@ -9356,11 +9359,11 @@
       <c r="S7" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="T7" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="U7" s="12" t="s">
-        <v>8</v>
+      <c r="U7" s="45" t="s">
+        <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
         <v>27</v>
@@ -9407,23 +9410,34 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
+      <c r="N8" s="12">
+        <v>76</v>
+      </c>
+      <c r="O8" s="12">
+        <v>26</v>
+      </c>
+      <c r="P8" s="12">
+        <v>20</v>
+      </c>
       <c r="Q8" s="28">
-        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>26</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
       <c r="T8" s="12"/>
       <c r="U8" s="28">
-        <f>SUM(R8:T8)/20</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V8">
-        <f>SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
+        <f>SUM(N8:U8)/40</f>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="W8" s="76">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
@@ -9453,7 +9467,7 @@
         <v>95</v>
       </c>
       <c r="J9" s="44">
-        <f t="shared" ref="J9:J12" si="1">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>10.25</v>
       </c>
       <c r="K9" s="44">
@@ -9464,29 +9478,40 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="N9" s="12">
+        <v>155</v>
+      </c>
+      <c r="O9" s="12">
+        <v>20</v>
+      </c>
+      <c r="P9" s="12">
+        <v>30</v>
+      </c>
       <c r="Q9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>65</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
       <c r="T9" s="12"/>
       <c r="U9" s="28">
-        <f t="shared" ref="U9:U13" si="2">SUM(R9:T9)/20</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V9">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
+        <v>8.75</v>
+      </c>
+      <c r="W9" s="76">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>74</v>
@@ -9510,7 +9535,7 @@
         <v>110</v>
       </c>
       <c r="J10" s="44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17.850000000000001</v>
       </c>
       <c r="K10" s="44">
@@ -9521,29 +9546,40 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
+      <c r="N10" s="12">
+        <v>74</v>
+      </c>
+      <c r="O10" s="12">
+        <v>30</v>
+      </c>
+      <c r="P10" s="12">
+        <v>30</v>
+      </c>
       <c r="Q10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>470</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
       <c r="T10" s="12"/>
       <c r="U10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="V10">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>17.850000000000001</v>
+      </c>
+      <c r="W10" s="76">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>180</v>
@@ -9567,7 +9603,7 @@
         <v>50</v>
       </c>
       <c r="J11" s="44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="K11" s="44">
@@ -9578,23 +9614,34 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="N11" s="12">
+        <v>60</v>
+      </c>
+      <c r="O11" s="12">
+        <v>20</v>
+      </c>
+      <c r="P11" s="12">
+        <v>20</v>
+      </c>
       <c r="Q11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>30</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
       <c r="T11" s="12"/>
       <c r="U11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V11">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="W11" s="76">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
@@ -9610,7 +9657,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L12" s="11"/>
@@ -9621,19 +9668,13 @@
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="U12" s="28"/>
       <c r="V12">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9653,47 +9694,41 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="U13" s="28"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
         <v>485</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>668</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>281</v>
       </c>
       <c r="J14" s="35">
@@ -9703,36 +9738,36 @@
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="4">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>365</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>96</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>591</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>246</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -9750,23 +9785,23 @@
         <v>6.8</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
         <v>9</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>33.4</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>14.05</v>
       </c>
       <c r="K15" t="s">
@@ -9779,23 +9814,23 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="6">P14/20</f>
-        <v>0</v>
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>5</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="7">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>29.55</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -9810,27 +9845,27 @@
         <v>485</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
         <v>142.80000000000001</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>189</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>701.4</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>295.05</v>
       </c>
       <c r="L16" s="13"/>
@@ -9839,27 +9874,27 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="9">O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>100.8</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>105</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="10">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>620.54999999999995</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -9874,27 +9909,27 @@
         <v>12.125</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
         <v>3.4</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4.5</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>16.7</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>7.0250000000000004</v>
       </c>
       <c r="J17" s="35">
@@ -9907,33 +9942,33 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>9.125</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="12">O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>2.4</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2.5</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="13">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>14.775</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -10018,7 +10053,7 @@
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -10031,7 +10066,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -10043,7 +10078,7 @@
       <c r="W2" s="62"/>
       <c r="X2" s="63"/>
       <c r="AB2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
@@ -10290,7 +10325,7 @@
         <v>46174</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P8" s="12">
         <v>284</v>
@@ -10456,7 +10491,7 @@
       </c>
       <c r="N10" s="27"/>
       <c r="O10" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P10" s="12">
         <v>86</v>
@@ -10574,7 +10609,7 @@
     <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="12">
         <v>382</v>
@@ -11055,7 +11090,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -11067,7 +11102,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -11257,13 +11292,13 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
       <c r="J8" s="28">
         <f>SUM(G8:I8)/20</f>
         <v>0</v>
@@ -11273,22 +11308,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29">
         <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
         <v>0</v>
       </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
       <c r="U8" s="12"/>
       <c r="V8" s="28">
         <f>SUM(S8:U8)/20</f>
@@ -11304,13 +11339,13 @@
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="28">
         <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
         <v>0</v>
@@ -11320,22 +11355,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
       <c r="U9" s="12"/>
       <c r="V9" s="28">
         <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
@@ -11349,15 +11384,15 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+        <v>37</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
       <c r="J10" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -11367,22 +11402,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
       <c r="U10" s="12"/>
       <c r="V10" s="28">
         <f t="shared" si="2"/>
@@ -11396,15 +11431,15 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+        <v>31</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
       <c r="J11" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -11418,15 +11453,15 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
       <c r="U11" s="12"/>
       <c r="V11" s="28">
         <f t="shared" si="2"/>
@@ -11442,13 +11477,13 @@
       <c r="B12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -11462,15 +11497,15 @@
         <f>B12</f>
         <v>Mubeen</v>
       </c>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
       <c r="U12" s="12"/>
       <c r="V12" s="28">
         <f t="shared" si="2"/>
@@ -11817,7 +11852,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C45487-B908-4B5C-9BA4-6B5B2A14CAC7}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -11828,16 +11863,15 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11847,7 +11881,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -11857,12 +11891,11 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -11871,21 +11904,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
-        <v>36</v>
-      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -11895,19 +11927,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -11917,19 +11948,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -11939,19 +11969,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -11967,25 +11996,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -12014,52 +12042,49 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -12071,183 +12096,183 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f t="shared" ref="K8:K13" si="0">SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="J8">
+        <f>SUM(C8:F8,G8,H8,I8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="1">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f t="shared" ref="W8:W13" si="2">SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28"/>
+      <c r="V8">
+        <f t="shared" ref="V8:V13" si="0">SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="3">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="C9" s="12">
+        <v>132</v>
+      </c>
+      <c r="D9" s="12">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>12</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>77</v>
+      </c>
+      <c r="H9" s="12">
+        <v>30</v>
+      </c>
+      <c r="I9" s="12">
+        <v>77</v>
+      </c>
+      <c r="J9">
+        <f>SUM(C9:F9,G9,H9,I9)/40</f>
+        <v>8.5</v>
+      </c>
+      <c r="K9" s="44">
+        <v>7</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="4">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28"/>
+      <c r="V9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12">
+        <v>202</v>
+      </c>
+      <c r="D10" s="12">
+        <v>66</v>
+      </c>
+      <c r="E10" s="12">
+        <v>66</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>126</v>
+      </c>
+      <c r="H10" s="12">
+        <v>126</v>
+      </c>
+      <c r="I10" s="12">
+        <v>212</v>
+      </c>
+      <c r="J10">
+        <f>SUM(C10:F10,G10,H10,I10)/40</f>
+        <v>19.95</v>
+      </c>
+      <c r="K10" s="44">
+        <v>16</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10" s="28"/>
+      <c r="V10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>31</v>
+      </c>
+      <c r="C11" s="12">
+        <v>420</v>
+      </c>
+      <c r="D11" s="12">
+        <v>86</v>
+      </c>
+      <c r="E11" s="12">
+        <v>86</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>160</v>
+      </c>
+      <c r="H11" s="12">
+        <v>80</v>
+      </c>
+      <c r="I11" s="12">
+        <v>80</v>
+      </c>
+      <c r="J11">
+        <f>SUM(C11:F11,G11,H11,I11)/40</f>
+        <v>22.8</v>
+      </c>
+      <c r="K11" s="41">
+        <v>10</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11" s="28"/>
+      <c r="V11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -12259,42 +12284,30 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="J12">
+        <f>SUM(C12:F12,G12,H12,I12)/40</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12" s="28"/>
+      <c r="V12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -12304,117 +12317,101 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="J13">
+        <f>SUM(C13:F13,G13,H13,I13)/40</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="41"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U13" s="28"/>
+      <c r="V13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="5">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>754</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>164</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>164</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>363</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>236</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="1"/>
+        <v>369</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>2050</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="6">SUM(O8:O13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -12422,199 +12419,196 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="7">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>18.149999999999999</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>11.8</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <f t="shared" si="3"/>
+        <v>18.45</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="8">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="9">S14/20</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>754</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="10">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>172.2</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>172.2</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>381.15</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>247.8</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
+        <f t="shared" si="6"/>
+        <v>387.45</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
       <c r="O16" s="36">
-        <f>O15+O14</f>
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="11">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>0</v>
+      </c>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="12">S15+S14</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="13">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>9.0749999999999993</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>5.9</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
+        <f t="shared" si="9"/>
+        <v>9.2249999999999996</v>
+      </c>
+      <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
+        <v>51.25</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
         <v>23</v>
       </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
       <c r="O17" s="36">
-        <f>O14/40</f>
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="14">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>0</v>
+      </c>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="15">S14/40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -12624,16 +12618,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12686,7 +12679,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -12698,7 +12691,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -12974,7 +12967,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="29"/>
       <c r="D10" s="29"/>
@@ -13018,7 +13011,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -13484,7 +13477,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -13496,7 +13489,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -13778,7 +13771,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -13825,7 +13818,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -14308,7 +14301,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -14320,7 +14313,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -14602,7 +14595,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -14649,7 +14642,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -15107,7 +15100,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -15119,7 +15112,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -15130,7 +15123,7 @@
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -15142,7 +15135,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -15441,7 +15434,7 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -15495,7 +15488,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -15981,7 +15974,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -15993,7 +15986,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -16269,7 +16262,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -16313,7 +16306,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -16779,7 +16772,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -16791,7 +16784,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -17067,7 +17060,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -17111,7 +17104,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -17580,7 +17573,7 @@
     <row r="2" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -17592,7 +17585,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -17891,7 +17884,7 @@
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -17943,7 +17936,7 @@
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -18430,7 +18423,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -18442,7 +18435,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -18724,7 +18717,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -18771,7 +18764,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -19245,7 +19238,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -19258,7 +19251,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -19637,7 +19630,7 @@
         <v>46175</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>60</v>
@@ -19722,7 +19715,7 @@
         <v>46175</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>276</v>
@@ -19882,7 +19875,7 @@
         <v>46175</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12">
@@ -20330,7 +20323,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -20342,7 +20335,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -20618,7 +20611,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -20662,7 +20655,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -21128,7 +21121,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -21140,7 +21133,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -21416,7 +21409,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -21460,7 +21453,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -21927,7 +21920,7 @@
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -21939,7 +21932,7 @@
       <c r="J2" s="63"/>
       <c r="M2" s="1"/>
       <c r="N2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
@@ -22215,7 +22208,7 @@
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -22259,7 +22252,7 @@
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -22727,7 +22720,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -22740,7 +22733,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -23102,7 +23095,7 @@
         <v>46176</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>100</v>
@@ -23189,7 +23182,7 @@
         <v>46176</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>612</v>
@@ -23361,7 +23354,7 @@
         <v>46176</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P13" s="12"/>
       <c r="Q13" s="12">
@@ -23771,7 +23764,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -23784,7 +23777,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -24146,7 +24139,7 @@
         <v>46177</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>262</v>
@@ -24233,7 +24226,7 @@
         <v>46177</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>182</v>
@@ -24406,7 +24399,7 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12">
@@ -24838,7 +24831,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -24851,7 +24844,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -25608,7 +25601,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -25621,7 +25614,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -25955,7 +25948,7 @@
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>200</v>
@@ -26033,7 +26026,7 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>280</v>
@@ -26481,7 +26474,7 @@
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -26494,7 +26487,7 @@
       <c r="K2" s="63"/>
       <c r="N2" s="1"/>
       <c r="O2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
@@ -26837,7 +26830,7 @@
     <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>40</v>
@@ -26911,7 +26904,7 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12">
         <v>242</v>
@@ -27456,7 +27449,7 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -27467,7 +27460,7 @@
       <c r="I2" s="63"/>
       <c r="L2" s="1"/>
       <c r="M2" s="61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="62"/>
       <c r="O2" s="62"/>
@@ -27786,7 +27779,7 @@
         <v>46181</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="12">
         <v>40</v>
@@ -27890,7 +27883,7 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="12">
         <v>254</v>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20EE2B2-BB6B-4049-AA62-B7B36C3F47CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54507373-020E-4835-B38F-BBF9C46AA3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="20" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="21" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="43">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -176,6 +176,15 @@
   </si>
   <si>
     <t>CTNS</t>
+  </si>
+  <si>
+    <t>70meat</t>
+  </si>
+  <si>
+    <t>70lem</t>
+  </si>
+  <si>
+    <t>120lem</t>
   </si>
 </sst>
 </file>
@@ -841,10 +850,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9341,7 +9350,7 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="75" t="s">
+      <c r="N7" s="37" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="56" t="s">
@@ -9436,7 +9445,7 @@
         <f>SUM(N8:U8)/40</f>
         <v>4.3499999999999996</v>
       </c>
-      <c r="W8" s="76">
+      <c r="W8" s="44">
         <v>4</v>
       </c>
     </row>
@@ -9504,7 +9513,7 @@
         <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
         <v>8.75</v>
       </c>
-      <c r="W9" s="76">
+      <c r="W9" s="44">
         <v>5</v>
       </c>
     </row>
@@ -9572,7 +9581,7 @@
         <f t="shared" si="1"/>
         <v>17.850000000000001</v>
       </c>
-      <c r="W10" s="76">
+      <c r="W10" s="44">
         <v>14</v>
       </c>
     </row>
@@ -9640,7 +9649,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="W11" s="76">
+      <c r="W11" s="44">
         <v>5</v>
       </c>
     </row>
@@ -12053,7 +12062,7 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="75" t="s">
+      <c r="N7" s="37" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="56" t="s">
@@ -12097,7 +12106,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
+        <f t="shared" ref="J8:J13" si="0">SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
       <c r="K8" s="44"/>
@@ -12106,16 +12115,16 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="N8" s="12"/>
+      <c r="N8" s="28"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="28"/>
+      <c r="Q8" s="75"/>
+      <c r="R8" s="75"/>
+      <c r="S8" s="75"/>
+      <c r="T8" s="75"/>
+      <c r="U8" s="75"/>
       <c r="V8">
-        <f t="shared" ref="V8:V13" si="0">SUM(N8:P8,R8,S8,T8)/40</f>
+        <f t="shared" ref="V8:V13" si="1">SUM(N8:P8,R8,S8,T8)/40</f>
         <v>0</v>
       </c>
     </row>
@@ -12146,7 +12155,7 @@
         <v>77</v>
       </c>
       <c r="J9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
+        <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
       <c r="K9" s="44">
@@ -12157,16 +12166,16 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
+      <c r="N9" s="28"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="28"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="75"/>
       <c r="V9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -12197,7 +12206,7 @@
         <v>212</v>
       </c>
       <c r="J10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
+        <f t="shared" si="0"/>
         <v>19.95</v>
       </c>
       <c r="K10" s="44">
@@ -12208,16 +12217,16 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
+      <c r="N10" s="28"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="28"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
       <c r="V10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -12248,7 +12257,7 @@
         <v>80</v>
       </c>
       <c r="J11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
+        <f t="shared" si="0"/>
         <v>22.8</v>
       </c>
       <c r="K11" s="41">
@@ -12259,16 +12268,16 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
+      <c r="N11" s="28"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="28"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="75"/>
+      <c r="T11" s="75"/>
+      <c r="U11" s="75"/>
       <c r="V11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -12285,7 +12294,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12" s="41"/>
@@ -12294,16 +12303,16 @@
         <f>B12</f>
         <v>Mubeen</v>
       </c>
-      <c r="N12" s="12"/>
+      <c r="N12" s="28"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="28"/>
+      <c r="Q12" s="75"/>
+      <c r="R12" s="75"/>
+      <c r="S12" s="75"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="75"/>
       <c r="V12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -12318,7 +12327,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13">
-        <f>SUM(C13:F13,G13,H13,I13)/40</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="41"/>
@@ -12327,13 +12336,13 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="28"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
       <c r="V13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -12341,31 +12350,31 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
         <v>754</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>363</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>236</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>369</v>
       </c>
       <c r="J14" s="35">
@@ -12375,35 +12384,35 @@
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
         <v>0</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V14" s="35" t="e">
@@ -12422,23 +12431,23 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
         <v>8.1999999999999993</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18.149999999999999</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11.8</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18.45</v>
       </c>
       <c r="L15" s="13"/>
@@ -12451,20 +12460,20 @@
         <v>0</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="4">P14/20</f>
+        <f t="shared" ref="P15" si="5">P14/20</f>
         <v>0</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -12479,27 +12488,27 @@
         <v>754</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
         <v>172.2</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>172.2</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>381.15</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>247.8</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>387.45</v>
       </c>
       <c r="L16" s="13"/>
@@ -12511,24 +12520,24 @@
         <v>0</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
         <v>0</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -12543,27 +12552,27 @@
         <v>18.850000000000001</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
         <v>4.0999999999999996</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.0749999999999993</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.9</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9.2249999999999996</v>
       </c>
       <c r="J17" s="35">
@@ -12579,24 +12588,24 @@
         <v>0</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
         <v>0</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
@@ -12634,7 +12643,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA54328-BFA5-404C-870B-9E32B69390E2}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -12645,16 +12654,15 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12664,7 +12672,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -12674,9 +12682,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -12688,21 +12695,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -12712,19 +12718,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -12734,19 +12739,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -12756,19 +12760,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -12784,25 +12787,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -12831,381 +12833,402 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8" s="27"/>
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="28">
+        <v>95</v>
+      </c>
+      <c r="D8" s="12">
+        <v>34</v>
+      </c>
+      <c r="E8" s="12">
+        <v>39</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>43</v>
+      </c>
+      <c r="H8" s="12">
+        <v>48</v>
+      </c>
+      <c r="I8" s="12">
+        <v>53</v>
+      </c>
+      <c r="J8">
+        <f>SUM(C8:F8,G8,H8,I8)/40</f>
+        <v>7.8</v>
+      </c>
+      <c r="K8" s="44">
         <v>7</v>
       </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="43" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="N8" s="28"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8">
+        <f>SUM(N8:U8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="C9" s="28">
+        <v>40</v>
+      </c>
+      <c r="D9" s="12">
+        <v>40</v>
+      </c>
+      <c r="E9" s="12">
+        <v>40</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>85</v>
+      </c>
+      <c r="H9" s="12">
+        <v>60</v>
+      </c>
+      <c r="I9" s="12">
+        <v>135</v>
+      </c>
+      <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="43" t="str">
+        <v>10</v>
+      </c>
+      <c r="K9" s="44">
+        <v>3</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="N9" s="28"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9">
+        <f t="shared" ref="V9:V13" si="0">SUM(N9:U9)/40</f>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>300</v>
+      </c>
+      <c r="Z9">
+        <v>200</v>
+      </c>
+      <c r="AA9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="C10" s="28">
+        <v>80</v>
+      </c>
+      <c r="D10" s="12">
+        <v>40</v>
+      </c>
+      <c r="E10" s="12">
+        <v>40</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12">
+        <v>85</v>
+      </c>
+      <c r="H10" s="12">
+        <v>90</v>
+      </c>
+      <c r="I10" s="12">
+        <v>64</v>
+      </c>
+      <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="43" t="str">
+        <v>9.9749999999999996</v>
+      </c>
+      <c r="K10" s="44">
+        <v>14</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="28">
+      <c r="N10" s="28"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="C11" s="28">
+        <v>262</v>
+      </c>
+      <c r="D11" s="12">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12">
+        <v>10</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>20</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>20</v>
+      </c>
+      <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="43" t="str">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="K11" s="44">
+        <v>8</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="28"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
       <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>0</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="43" t="str">
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="28"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="28"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>477</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>129</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>233</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>198</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="1"/>
+        <v>272</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>1433</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -13213,199 +13236,196 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>6.45</v>
       </c>
       <c r="F15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="3"/>
+        <v>11.65</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>9.9</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>13.6</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="T15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>130.19999999999999</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="6"/>
+        <v>135.44999999999999</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="6"/>
+        <v>244.65</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="6"/>
+        <v>207.9</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="6"/>
+        <v>285.60000000000002</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
+      <c r="T16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>11.925000000000001</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>3.1</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="9"/>
+        <v>3.2250000000000001</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="9"/>
+        <v>5.8250000000000002</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="9"/>
+        <v>4.95</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="9"/>
+        <v>6.8</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>35.824999999999996</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
+      <c r="T17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -13415,16 +13435,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13432,7 +13451,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F16114E-0AD8-4652-8B31-88E6EC8B6522}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -13443,16 +13462,15 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13462,7 +13480,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -13472,9 +13490,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -13486,21 +13503,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -13510,19 +13526,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -13532,19 +13547,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -13554,19 +13568,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -13582,25 +13595,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -13629,396 +13641,333 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="76" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="L8" s="46">
+      <c r="K8" s="46">
         <v>6</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="28"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Q8" s="75"/>
+      <c r="R8" s="75"/>
+      <c r="S8" s="75"/>
+      <c r="T8" s="75"/>
+      <c r="U8" s="75"/>
+      <c r="V8">
+        <f>SUM(N8:U8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
         <v>0</v>
       </c>
-      <c r="L9" s="46">
+      <c r="K9" s="46">
         <v>8</v>
       </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="28"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="75"/>
+      <c r="V9">
+        <f t="shared" ref="V9:V13" si="0">SUM(N9:U9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
         <v>0</v>
       </c>
-      <c r="L10" s="46">
+      <c r="K10" s="46">
         <v>3</v>
       </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="28"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
+      <c r="V10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
         <v>0</v>
       </c>
-      <c r="L11" s="46">
+      <c r="K11" s="46">
         <v>8</v>
       </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="28"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="75"/>
+      <c r="T11" s="75"/>
+      <c r="U11" s="75"/>
+      <c r="V11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>0</v>
       </c>
-      <c r="L12" s="46">
+      <c r="K12" s="46">
         <v>4</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="28"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="75"/>
+      <c r="R12" s="75"/>
+      <c r="S12" s="75"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="75"/>
+      <c r="V12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="28"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
+      <c r="V13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
         <v>0</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -14029,55 +13978,54 @@
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
         <v>0</v>
       </c>
       <c r="F15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="T15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -14087,62 +14035,61 @@
         <v>0</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
+      <c r="T16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
@@ -14152,73 +14099,72 @@
         <v>0</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
         <v>0</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
+      <c r="T17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -14228,16 +14174,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -14247,7 +14192,7 @@
           <x14:formula1>
             <xm:f>'last month'!$B$22:$B$28</xm:f>
           </x14:formula1>
-          <xm:sqref>B8:B12 N8:N12</xm:sqref>
+          <xm:sqref>B8:B12 M8:M12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54507373-020E-4835-B38F-BBF9C46AA3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA09A7B3-4048-45C7-8033-884E8473E2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="21" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="44">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>120lem</t>
+  </si>
+  <si>
+    <t>No EXC</t>
   </si>
 </sst>
 </file>
@@ -667,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -849,11 +852,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11861,7 +11861,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C45487-B908-4B5C-9BA4-6B5B2A14CAC7}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -11877,10 +11877,9 @@
     <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11899,9 +11898,8 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -11923,10 +11921,9 @@
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="T2" s="63"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -11944,10 +11941,9 @@
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="T3" s="66"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -11965,10 +11961,9 @@
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
-    </row>
-    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T4" s="66"/>
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -11986,10 +11981,9 @@
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="T5" s="69"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -12019,10 +12013,9 @@
         <v>3</v>
       </c>
       <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="T6" s="72"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -12081,19 +12074,16 @@
         <v>7</v>
       </c>
       <c r="T7" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="U7" s="45" t="s">
         <v>8</v>
       </c>
+      <c r="U7" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="V7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -12118,17 +12108,16 @@
       <c r="N8" s="28"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="75"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="75"/>
-      <c r="T8" s="75"/>
-      <c r="U8" s="75"/>
-      <c r="V8">
-        <f t="shared" ref="V8:V13" si="1">SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8">
+        <f t="shared" ref="U8:U9" si="1">SUM(N8:T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -12166,20 +12155,22 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="28"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="75"/>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
-      <c r="V9">
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V9" s="42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
@@ -12217,20 +12208,36 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="28"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="75"/>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="75"/>
-      <c r="U10" s="75"/>
-      <c r="V10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="N10" s="28">
+        <v>202</v>
+      </c>
+      <c r="O10" s="12">
+        <v>66</v>
+      </c>
+      <c r="P10" s="12">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>126</v>
+      </c>
+      <c r="S10" s="12">
+        <v>126</v>
+      </c>
+      <c r="T10" s="12">
+        <v>212</v>
+      </c>
+      <c r="U10">
+        <f>SUM(N10:T10)/40</f>
+        <v>19.95</v>
+      </c>
+      <c r="V10" s="44">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
@@ -12268,55 +12275,100 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="28"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="75"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="75"/>
-      <c r="T11" s="75"/>
-      <c r="U11" s="75"/>
-      <c r="V11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="N11" s="28">
+        <v>420</v>
+      </c>
+      <c r="O11" s="12">
+        <v>80</v>
+      </c>
+      <c r="P11" s="12">
+        <v>80</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>120</v>
+      </c>
+      <c r="S11" s="12">
+        <v>40</v>
+      </c>
+      <c r="T11" s="12">
+        <v>40</v>
+      </c>
+      <c r="U11">
+        <f>SUM(N11:T11)/40</f>
+        <v>19.5</v>
+      </c>
+      <c r="V11" s="44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>1189</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1395</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="12">
+        <v>2398</v>
+      </c>
+      <c r="H12" s="12">
+        <v>2397</v>
+      </c>
+      <c r="I12" s="12">
+        <v>4800</v>
+      </c>
       <c r="J12">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="41"/>
+        <v>304.47500000000002</v>
+      </c>
+      <c r="K12" s="41">
+        <v>1</v>
+      </c>
       <c r="L12" s="11"/>
-      <c r="M12" s="10" t="str">
-        <f>B12</f>
-        <v>Mubeen</v>
+      <c r="M12" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="N12" s="28"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="75"/>
-      <c r="V12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="O12" s="12">
+        <f>1189+40</f>
+        <v>1229</v>
+      </c>
+      <c r="P12" s="12">
+        <f>1395+40</f>
+        <v>1435</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
+        <f>2398+40</f>
+        <v>2438</v>
+      </c>
+      <c r="S12" s="12">
+        <v>2397</v>
+      </c>
+      <c r="T12" s="12">
+        <f>4800+40</f>
+        <v>4840</v>
+      </c>
+      <c r="U12">
+        <f>SUM(N12:T12)/40</f>
+        <v>308.47500000000002</v>
+      </c>
+      <c r="V12" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -12336,17 +12388,16 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13">
+        <f>SUM(N13:T13)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
@@ -12355,11 +12406,11 @@
       </c>
       <c r="D14" s="14">
         <f t="shared" si="2"/>
-        <v>164</v>
+        <v>1353</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="2"/>
-        <v>164</v>
+        <v>1559</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="2"/>
@@ -12367,33 +12418,33 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="2"/>
-        <v>363</v>
+        <v>2761</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="2"/>
-        <v>236</v>
+        <v>2633</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="2"/>
-        <v>369</v>
+        <v>5169</v>
       </c>
       <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>2050</v>
+        <v>14229</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:T14" si="3">SUM(N8:N13)</f>
+        <v>622</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="3"/>
@@ -12401,26 +12452,22 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2684</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2563</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="35" t="e">
-        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
+        <v>5092</v>
+      </c>
+      <c r="U14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -12428,11 +12475,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>8.1999999999999993</v>
+        <v>67.650000000000006</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="4">E14/20</f>
-        <v>8.1999999999999993</v>
+        <v>77.95</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
@@ -12440,15 +12487,15 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="4"/>
-        <v>18.149999999999999</v>
+        <v>138.05000000000001</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>11.8</v>
+        <v>131.65</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>18.45</v>
+        <v>258.45</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -12457,28 +12504,24 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="5">P14/20</f>
-        <v>0</v>
+        <v>79.05</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="6">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:S15" si="6">R14/20</f>
+        <v>134.19999999999999</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+        <v>128.15</v>
+      </c>
+      <c r="T15" s="13"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -12489,11 +12532,11 @@
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="7">D15+D14</f>
-        <v>172.2</v>
+        <v>1420.65</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="7"/>
-        <v>172.2</v>
+        <v>1636.95</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="7"/>
@@ -12501,15 +12544,15 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="7"/>
-        <v>381.15</v>
+        <v>2899.05</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="7"/>
-        <v>247.8</v>
+        <v>2764.65</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="7"/>
-        <v>387.45</v>
+        <v>5427.45</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -12517,32 +12560,28 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="8">O15+O14</f>
-        <v>0</v>
+        <v>1443.75</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1660.05</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:S16" si="9">R15+R14</f>
+        <v>2818.2</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+        <v>2691.15</v>
+      </c>
+      <c r="T16" s="36"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
@@ -12553,11 +12592,11 @@
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="10">D14/40</f>
-        <v>4.0999999999999996</v>
+        <v>33.825000000000003</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="10"/>
-        <v>4.0999999999999996</v>
+        <v>38.975000000000001</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="10"/>
@@ -12565,19 +12604,19 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="10"/>
-        <v>9.0749999999999993</v>
+        <v>69.025000000000006</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="10"/>
-        <v>5.9</v>
+        <v>65.825000000000003</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="10"/>
-        <v>9.2249999999999996</v>
+        <v>129.22499999999999</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>51.25</v>
+        <v>355.72500000000002</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">
@@ -12585,39 +12624,35 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>15.55</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="11">O14/40</f>
-        <v>0</v>
+        <v>34.375</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>39.524999999999999</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="12">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:S17" si="12">R14/40</f>
+        <v>67.099999999999994</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36"/>
-      <c r="V17" s="35">
-        <f>SUM(N17:T17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+        <v>64.075000000000003</v>
+      </c>
+      <c r="T17" s="36"/>
+      <c r="U17" s="35">
+        <f>SUM(N17:S17)</f>
+        <v>220.625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -12633,9 +12668,9 @@
     <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:I6"/>
-    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="M2:T5"/>
     <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="R6:T6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13001,30 +13036,32 @@
         <v>37</v>
       </c>
       <c r="C10" s="28">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="D10" s="12">
         <v>40</v>
       </c>
       <c r="E10" s="12">
-        <v>40</v>
-      </c>
-      <c r="F10" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
       <c r="G10" s="12">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="H10" s="12">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I10" s="12">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>9.9749999999999996</v>
+        <v>12.1</v>
       </c>
       <c r="K10" s="44">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="10" t="str">
@@ -13098,23 +13135,36 @@
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="28"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>800</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1280</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="12">
+        <v>1040</v>
+      </c>
+      <c r="H12" s="12">
+        <v>1280</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1520</v>
+      </c>
       <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
+        <v>148</v>
+      </c>
+      <c r="K12" s="75">
+        <v>7</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
+        <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="N12" s="28"/>
       <c r="O12" s="12"/>
@@ -13159,15 +13209,15 @@
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
-        <v>477</v>
+        <v>641</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="1"/>
-        <v>124</v>
+        <v>924</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="1"/>
-        <v>129</v>
+        <v>1369</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="1"/>
@@ -13175,19 +13225,19 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="1"/>
-        <v>233</v>
+        <v>1293</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="1"/>
-        <v>198</v>
+        <v>1448</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="1"/>
-        <v>272</v>
+        <v>1763</v>
       </c>
       <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>1433</v>
+        <v>7438</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
@@ -13236,11 +13286,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>6.2</v>
+        <v>46.2</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="3">E14/20</f>
-        <v>6.45</v>
+        <v>68.45</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="3"/>
@@ -13248,15 +13298,15 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="3"/>
-        <v>11.65</v>
+        <v>64.650000000000006</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="3"/>
-        <v>9.9</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="3"/>
-        <v>13.6</v>
+        <v>88.15</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -13293,15 +13343,15 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>477</v>
+        <v>641</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="6">D15+D14</f>
-        <v>130.19999999999999</v>
+        <v>970.2</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="6"/>
-        <v>135.44999999999999</v>
+        <v>1437.45</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="6"/>
@@ -13309,15 +13359,15 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="6"/>
-        <v>244.65</v>
+        <v>1357.65</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="6"/>
-        <v>207.9</v>
+        <v>1520.4</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="6"/>
-        <v>285.60000000000002</v>
+        <v>1851.15</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -13357,15 +13407,15 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>11.925000000000001</v>
+        <v>16.024999999999999</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="9">D14/40</f>
-        <v>3.1</v>
+        <v>23.1</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="9"/>
-        <v>3.2250000000000001</v>
+        <v>34.225000000000001</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="9"/>
@@ -13373,19 +13423,19 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="9"/>
-        <v>5.8250000000000002</v>
+        <v>32.325000000000003</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="9"/>
-        <v>4.95</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="9"/>
-        <v>6.8</v>
+        <v>44.075000000000003</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>35.824999999999996</v>
+        <v>185.95</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">
@@ -13652,7 +13702,7 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="76" t="s">
+      <c r="N7" s="37" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="56" t="s">
@@ -13710,11 +13760,11 @@
       <c r="N8" s="28"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="75"/>
-      <c r="R8" s="75"/>
-      <c r="S8" s="75"/>
-      <c r="T8" s="75"/>
-      <c r="U8" s="75"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
       <c r="V8">
         <f>SUM(N8:U8)/40</f>
         <v>0</v>
@@ -13747,11 +13797,11 @@
       <c r="N9" s="28"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="75"/>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
       <c r="V9">
         <f t="shared" ref="V9:V13" si="0">SUM(N9:U9)/40</f>
         <v>0</v>
@@ -13784,11 +13834,11 @@
       <c r="N10" s="28"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="75"/>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="75"/>
-      <c r="U10" s="75"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
       <c r="V10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13821,11 +13871,11 @@
       <c r="N11" s="28"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="75"/>
-      <c r="R11" s="75"/>
-      <c r="S11" s="75"/>
-      <c r="T11" s="75"/>
-      <c r="U11" s="75"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
       <c r="V11">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13858,11 +13908,11 @@
       <c r="N12" s="28"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="75"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
       <c r="V12">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13883,11 +13933,11 @@
       <c r="N13" s="28"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
       <c r="V13">
         <f t="shared" si="0"/>
         <v>0</v>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA09A7B3-4048-45C7-8033-884E8473E2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8083F8D1-497D-4C5F-8BB4-335A99E6BA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="21" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="22" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -670,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -851,9 +851,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12948,17 +12945,34 @@
         <f>B8</f>
         <v>Furqan</v>
       </c>
-      <c r="N8" s="28"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+      <c r="N8" s="28">
+        <v>95</v>
+      </c>
+      <c r="O8" s="12">
+        <v>34</v>
+      </c>
+      <c r="P8" s="12">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>43</v>
+      </c>
+      <c r="S8" s="12">
+        <v>48</v>
+      </c>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
+      <c r="U8" s="12">
+        <v>53</v>
+      </c>
       <c r="V8">
         <f>SUM(N8:U8)/40</f>
-        <v>0</v>
+        <v>7.8</v>
+      </c>
+      <c r="W8" s="44">
+        <v>7</v>
       </c>
       <c r="Y8" t="s">
         <v>40</v>
@@ -13009,16 +13023,31 @@
         <v>Salman</v>
       </c>
       <c r="N9" s="28"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+      <c r="O9" s="12">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>70</v>
+      </c>
+      <c r="S9" s="12">
+        <v>50</v>
+      </c>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
+      <c r="U9" s="12">
+        <v>120</v>
+      </c>
       <c r="V9">
         <f t="shared" ref="V9:V13" si="0">SUM(N9:U9)/40</f>
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="W9" s="44">
+        <v>2</v>
       </c>
       <c r="Y9">
         <v>300</v>
@@ -13068,17 +13097,34 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="28"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="N10" s="28">
+        <v>144</v>
+      </c>
+      <c r="O10" s="12">
+        <v>40</v>
+      </c>
+      <c r="P10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>95</v>
+      </c>
+      <c r="S10" s="12">
+        <v>50</v>
+      </c>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
+      <c r="U10" s="12">
+        <v>15</v>
+      </c>
       <c r="V10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.6</v>
+      </c>
+      <c r="W10" s="44">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
@@ -13119,17 +13165,34 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="28"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+      <c r="N11" s="28">
+        <v>158</v>
+      </c>
+      <c r="O11" s="12">
+        <v>10</v>
+      </c>
+      <c r="P11" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>20</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
+      <c r="U11" s="12">
+        <v>20</v>
+      </c>
       <c r="V11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.45</v>
+      </c>
+      <c r="W11" s="41">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
@@ -13158,7 +13221,7 @@
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>148</v>
       </c>
-      <c r="K12" s="75">
+      <c r="K12" s="44">
         <v>7</v>
       </c>
       <c r="L12" s="11"/>
@@ -13243,15 +13306,15 @@
       <c r="M14" s="10"/>
       <c r="N14" s="14">
         <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="2"/>
@@ -13259,11 +13322,11 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="2"/>
@@ -13271,7 +13334,7 @@
       </c>
       <c r="U14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -13315,20 +13378,20 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="4">P14/20</f>
-        <v>0</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="5">R14/20</f>
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="5"/>
@@ -13375,24 +13438,24 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="7">O15+O14</f>
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>51.45</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>0</v>
+        <v>239.4</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>155.4</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="8"/>
@@ -13443,24 +13506,24 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>9.9250000000000007</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="10">O14/40</f>
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="11">R14/40</f>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="11"/>
@@ -13469,7 +13532,7 @@
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -13738,19 +13801,33 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
+      <c r="C8" s="28">
+        <v>70</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>10</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>82</v>
+      </c>
+      <c r="H8" s="12">
+        <v>65</v>
+      </c>
+      <c r="I8" s="12">
+        <v>130</v>
+      </c>
       <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
+        <v>8.9250000000000007</v>
       </c>
       <c r="K8" s="46">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="10" t="str">
@@ -13786,9 +13863,7 @@
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
         <v>0</v>
       </c>
-      <c r="K9" s="46">
-        <v>8</v>
-      </c>
+      <c r="K9" s="46"/>
       <c r="L9" s="27"/>
       <c r="M9" s="10" t="str">
         <f>B9</f>
@@ -13823,9 +13898,7 @@
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
         <v>0</v>
       </c>
-      <c r="K10" s="46">
-        <v>3</v>
-      </c>
+      <c r="K10" s="46"/>
       <c r="L10" s="27"/>
       <c r="M10" s="10" t="str">
         <f>B10</f>
@@ -13849,19 +13922,33 @@
       <c r="B11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="C11" s="28">
+        <v>212</v>
+      </c>
+      <c r="D11" s="12">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12">
+        <v>10</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>38</v>
+      </c>
+      <c r="H11" s="12">
+        <v>66</v>
+      </c>
+      <c r="I11" s="12">
+        <v>58</v>
+      </c>
       <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="K11" s="46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
@@ -13897,9 +13984,7 @@
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>0</v>
       </c>
-      <c r="K12" s="46">
-        <v>4</v>
-      </c>
+      <c r="K12" s="46"/>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
         <f>B12</f>
@@ -13948,15 +14033,15 @@
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="1"/>
@@ -13964,19 +14049,19 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
@@ -14025,11 +14110,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="3">E14/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="3"/>
@@ -14037,15 +14122,15 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -14082,15 +14167,15 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="6">D15+D14</f>
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="6"/>
@@ -14098,15 +14183,15 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>137.55000000000001</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>197.4</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -14146,15 +14231,15 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="9">D14/40</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="9"/>
@@ -14162,19 +14247,19 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
+        <v>18.775000000000002</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8083F8D1-497D-4C5F-8BB4-335A99E6BA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F026D4-1658-43ED-AF4C-528F397AF69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="22" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="24" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="48">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -188,6 +188,18 @@
   </si>
   <si>
     <t>No EXC</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -13801,34 +13813,18 @@
       <c r="B8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="28">
-        <v>70</v>
-      </c>
-      <c r="D8" s="12">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12">
-        <v>10</v>
-      </c>
-      <c r="F8" s="12">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
-        <v>82</v>
-      </c>
-      <c r="H8" s="12">
-        <v>65</v>
-      </c>
-      <c r="I8" s="12">
-        <v>130</v>
-      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
       <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>8.9250000000000007</v>
-      </c>
-      <c r="K8" s="46">
-        <v>17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" s="46"/>
       <c r="L8" s="27"/>
       <c r="M8" s="10" t="str">
         <f>B8</f>
@@ -13887,34 +13883,67 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="C10" s="28">
+        <v>70</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>10</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>82</v>
+      </c>
+      <c r="H10" s="12">
+        <v>65</v>
+      </c>
+      <c r="I10" s="12">
+        <v>130</v>
+      </c>
       <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="46"/>
+        <v>8.9250000000000007</v>
+      </c>
+      <c r="K10" s="46">
+        <v>17</v>
+      </c>
       <c r="L10" s="27"/>
       <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="28"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="N10" s="28">
+        <v>70</v>
+      </c>
+      <c r="O10" s="12">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>96</v>
+      </c>
+      <c r="S10" s="12">
+        <v>85</v>
+      </c>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
+      <c r="U10" s="12">
+        <v>130</v>
+      </c>
       <c r="V10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.7750000000000004</v>
+      </c>
+      <c r="W10" s="44">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
@@ -13955,17 +13984,34 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="28"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+      <c r="N11" s="28">
+        <v>126</v>
+      </c>
+      <c r="O11" s="12">
+        <v>10</v>
+      </c>
+      <c r="P11" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>32</v>
+      </c>
+      <c r="S11" s="12">
+        <v>60</v>
+      </c>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
+      <c r="U11" s="12">
+        <v>52</v>
+      </c>
       <c r="V11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.25</v>
+      </c>
+      <c r="W11" s="44">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
@@ -14067,15 +14113,15 @@
       <c r="M14" s="10"/>
       <c r="N14" s="14">
         <f t="shared" ref="N14:U14" si="2">SUM(N8:N13)</f>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="2"/>
@@ -14083,11 +14129,11 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="2"/>
@@ -14095,7 +14141,7 @@
       </c>
       <c r="U14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -14139,20 +14185,20 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="4">P14/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="5">R14/20</f>
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="5"/>
@@ -14199,24 +14245,24 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="7">O15+O14</f>
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>0</v>
+        <v>134.4</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>152.25</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="8"/>
@@ -14267,24 +14313,24 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="10">O14/40</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="11">R14/40</f>
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3.625</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="11"/>
@@ -14293,7 +14339,7 @@
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>12.475000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -14337,7 +14383,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48CA099E-5370-4419-9FCD-0778E6459525}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:AE25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -14356,7 +14402,7 @@
     <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14378,7 +14424,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -14404,7 +14450,7 @@
       <c r="U2" s="62"/>
       <c r="V2" s="63"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -14426,7 +14472,7 @@
       <c r="U3" s="65"/>
       <c r="V3" s="66"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -14448,7 +14494,7 @@
       <c r="U4" s="65"/>
       <c r="V4" s="66"/>
     </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -14470,7 +14516,7 @@
       <c r="U5" s="68"/>
       <c r="V5" s="69"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -14504,7 +14550,7 @@
       <c r="U6" s="71"/>
       <c r="V6" s="72"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -14557,7 +14603,7 @@
         <v>11</v>
       </c>
       <c r="R7" s="45" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S7" s="45" t="s">
         <v>13</v>
@@ -14569,7 +14615,7 @@
         <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>27</v>
@@ -14578,7 +14624,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -14598,9 +14644,7 @@
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="L8" s="44">
-        <v>4</v>
-      </c>
+      <c r="L8" s="44"/>
       <c r="M8" s="27"/>
       <c r="N8" s="10" t="str">
         <f>B8</f>
@@ -14609,91 +14653,118 @@
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="R8" s="28"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
       <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="V8" s="28"/>
       <c r="W8" s="47">
         <f>SUM(O8:Q8,S8,T8,U8)/40</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="C9" s="12">
+        <v>125</v>
+      </c>
+      <c r="D9" s="12">
+        <v>61</v>
+      </c>
+      <c r="E9" s="12">
+        <v>41</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>55</v>
+      </c>
+      <c r="H9" s="12">
+        <v>30</v>
+      </c>
+      <c r="I9" s="12">
+        <v>45</v>
+      </c>
       <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
+        <f t="shared" ref="J9:J13" si="0">SUM(G9:I9)/20</f>
+        <v>6.5</v>
       </c>
       <c r="K9" s="47">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
+        <v>8.9250000000000007</v>
       </c>
       <c r="L9" s="44">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
+      <c r="O9" s="12">
+        <v>85</v>
+      </c>
+      <c r="P9" s="12">
+        <v>41</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>41</v>
+      </c>
       <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="12">
+        <v>10</v>
+      </c>
+      <c r="T9" s="12">
+        <v>10</v>
+      </c>
       <c r="U9" s="12"/>
       <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W9" s="47">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+        <f>SUM(O9:V9)/40</f>
+        <v>5.1749999999999998</v>
+      </c>
+      <c r="X9" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="12">
+        <v>116</v>
+      </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="G10" s="12">
+        <v>77</v>
+      </c>
+      <c r="H10" s="12">
+        <v>105</v>
+      </c>
+      <c r="I10" s="12">
+        <v>46</v>
+      </c>
       <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>11.4</v>
       </c>
       <c r="K10" s="47">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="L10" s="44">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="10" t="str">
@@ -14703,117 +14774,172 @@
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R10" s="28"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
       <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="V10" s="28"/>
       <c r="W10" s="47">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" ref="W10:W11" si="1">SUM(O10:V10)/40</f>
+        <v>0</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="C11" s="12">
+        <v>360</v>
+      </c>
+      <c r="D11" s="12">
+        <v>80</v>
+      </c>
+      <c r="E11" s="12">
+        <v>80</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>155</v>
+      </c>
+      <c r="H11" s="12">
+        <v>155</v>
+      </c>
+      <c r="I11" s="12">
+        <v>190</v>
+      </c>
       <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="K11" s="47">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="L11" s="41">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
+      <c r="O11" s="12">
+        <v>280</v>
+      </c>
+      <c r="P11" s="12">
+        <v>80</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>80</v>
+      </c>
       <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="12">
+        <v>155</v>
+      </c>
+      <c r="T11" s="12">
+        <v>145</v>
+      </c>
       <c r="U11" s="12"/>
       <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="W11" s="47">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="X11" s="44">
+        <v>5</v>
+      </c>
+      <c r="AB11">
+        <v>12</v>
+      </c>
+      <c r="AC11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>580</v>
+      </c>
+      <c r="E12" s="12">
+        <v>480</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="12">
+        <v>350</v>
+      </c>
+      <c r="H12" s="12">
+        <v>560</v>
+      </c>
+      <c r="I12" s="12">
+        <v>940</v>
+      </c>
       <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>92.5</v>
       </c>
       <c r="K12" s="47">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
+        <v>72.75</v>
       </c>
       <c r="L12" s="41">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
+        <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R12" s="28"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="V12" s="28"/>
       <c r="W12" s="47">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="X12">
+        <v>50</v>
+      </c>
+      <c r="AC12">
+        <v>6</v>
+      </c>
+      <c r="AD12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -14824,7 +14950,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M13" s="11"/>
@@ -14832,97 +14958,109 @@
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R13" s="28"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V13" s="28"/>
+      <c r="AB13">
+        <v>15</v>
+      </c>
+      <c r="AC13">
+        <v>15</v>
+      </c>
+      <c r="AD13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:J14" si="2">SUM(C8:C13)</f>
+        <v>601</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>721</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>601</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>637</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>850</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1221</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>135.4</v>
       </c>
       <c r="K14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
+        <v>4631</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="10"/>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
+        <f t="shared" ref="O14:V14" si="3">SUM(O8:O13)</f>
+        <v>365</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>121</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>121</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>165</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>155</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>200</v>
       </c>
       <c r="W14" s="35" t="e">
         <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AB14">
+        <v>15</v>
+      </c>
+      <c r="AC14">
+        <v>15</v>
+      </c>
+      <c r="AD14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -14930,27 +15068,27 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>30.05</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>31.85</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>42.5</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>61.05</v>
       </c>
       <c r="J15" s="13"/>
       <c r="M15" s="13"/>
@@ -14960,59 +15098,62 @@
       <c r="O15" s="13"/>
       <c r="P15" s="13">
         <f>P14/20</f>
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
+        <f t="shared" ref="Q15" si="5">Q14/20</f>
+        <v>6.05</v>
       </c>
       <c r="R15" s="13"/>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
+        <f t="shared" ref="S15:U15" si="6">S14/20</f>
+        <v>8.25</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>7.75</v>
       </c>
       <c r="U15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AC15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>757.05</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>631.04999999999995</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>668.85</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>892.5</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1282.05</v>
       </c>
       <c r="J16" s="36"/>
       <c r="M16" s="13"/>
@@ -15021,68 +15162,71 @@
       </c>
       <c r="O16" s="36">
         <f>O15+O14</f>
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
+        <f t="shared" ref="P16:Q16" si="8">P15+P14</f>
+        <v>127.05</v>
       </c>
       <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>127.05</v>
       </c>
       <c r="R16" s="36"/>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
+        <f t="shared" ref="S16:U16" si="9">S15+S14</f>
+        <v>173.25</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>162.75</v>
       </c>
       <c r="U16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="AE16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>15.025</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>18.024999999999999</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>15.025</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>15.925000000000001</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>21.25</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>30.524999999999999</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
+        <v>115.77500000000001</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="39" t="s">
@@ -15090,39 +15234,51 @@
       </c>
       <c r="O17" s="36">
         <f>O14/40</f>
-        <v>0</v>
+        <v>9.125</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
+        <f t="shared" ref="P17:Q17" si="11">P14/40</f>
+        <v>3.0249999999999999</v>
       </c>
       <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>3.0249999999999999</v>
       </c>
       <c r="R17" s="36"/>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
+        <f t="shared" ref="S17:U17" si="12">S14/40</f>
+        <v>4.125</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>3.875</v>
       </c>
       <c r="U17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="V17" s="36"/>
       <c r="W17" s="35">
         <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <v>23.175000000000001</v>
+      </c>
+      <c r="AE17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="AC18">
+        <v>10</v>
+      </c>
+      <c r="AD18">
+        <v>10</v>
+      </c>
+      <c r="AE18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -15133,6 +15289,45 @@
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
+      <c r="AC19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AB20">
+        <v>15</v>
+      </c>
+      <c r="AC20">
+        <v>15</v>
+      </c>
+      <c r="AD20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AE21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AE22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AE23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AE24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AB25">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -15423,9 +15618,7 @@
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="L8" s="45">
-        <v>6</v>
-      </c>
+      <c r="L8" s="45"/>
       <c r="M8" s="27"/>
       <c r="N8" s="10" t="str">
         <f>B8</f>
@@ -15453,32 +15646,44 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y8" s="44">
-        <v>3</v>
-      </c>
+      <c r="Y8" s="44"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="C9" s="12">
+        <v>208</v>
+      </c>
+      <c r="D9" s="12">
+        <v>64</v>
+      </c>
+      <c r="E9" s="12">
+        <v>24</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>154</v>
+      </c>
+      <c r="H9" s="12">
+        <v>109</v>
+      </c>
+      <c r="I9" s="12">
+        <v>101</v>
+      </c>
       <c r="J9" s="28">
         <f t="shared" ref="J9:J13" si="2">SUM(G9:I9)/20</f>
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="K9" s="48">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="L9" s="45">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="10" t="str">
@@ -15507,32 +15712,44 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y9" s="44">
-        <v>0</v>
-      </c>
+      <c r="Y9" s="44"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="C10" s="12">
+        <v>240</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>40</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>120</v>
+      </c>
       <c r="J10" s="28">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K10" s="48">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L10" s="45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="10" t="str">
@@ -15561,32 +15778,44 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y10" s="44">
-        <v>5</v>
-      </c>
+      <c r="Y10" s="44"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="C11" s="12">
+        <v>112</v>
+      </c>
+      <c r="D11" s="12">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12">
+        <v>20</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>133</v>
+      </c>
+      <c r="H11" s="12">
+        <v>139</v>
+      </c>
+      <c r="I11" s="12">
+        <v>218</v>
+      </c>
       <c r="J11" s="28">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="K11" s="48">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
+        <v>16.05</v>
       </c>
       <c r="L11" s="45">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="10" t="str">
@@ -15615,37 +15844,45 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y11" s="41">
-        <v>3</v>
-      </c>
+      <c r="Y11" s="41"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>510</v>
+      </c>
+      <c r="E12" s="12">
+        <v>590</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="12">
+        <v>510</v>
+      </c>
+      <c r="H12" s="12">
+        <v>510</v>
+      </c>
+      <c r="I12" s="12">
+        <v>540</v>
+      </c>
       <c r="J12" s="28">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K12" s="48">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="L12" s="45">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
+        <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
@@ -15669,9 +15906,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y12" s="41">
-        <v>9</v>
-      </c>
+      <c r="Y12" s="41"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -15709,15 +15944,15 @@
       <c r="B14" s="10"/>
       <c r="C14" s="14">
         <f t="shared" ref="C14:J14" si="4">SUM(C8:C13)</f>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="4"/>
@@ -15725,23 +15960,23 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>837</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>979</v>
       </c>
       <c r="J14" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="K14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
+        <v>4362</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="10"/>
@@ -15790,11 +16025,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="6">E14/20</f>
-        <v>0</v>
+        <v>31.7</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="6"/>
@@ -15802,15 +16037,15 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>41.85</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>37.9</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>48.95</v>
       </c>
       <c r="J15" s="13"/>
       <c r="M15" s="13"/>
@@ -15848,15 +16083,15 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="9">D15+D14</f>
-        <v>0</v>
+        <v>623.70000000000005</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>665.7</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="9"/>
@@ -15864,15 +16099,15 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>878.85</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>795.9</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1027.95</v>
       </c>
       <c r="J16" s="36"/>
       <c r="M16" s="13"/>
@@ -15913,15 +16148,15 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="12">D14/40</f>
-        <v>0</v>
+        <v>14.85</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>15.85</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="12"/>
@@ -15929,20 +16164,20 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>20.925000000000001</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>18.95</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24.475000000000001</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
+        <v>109.05000000000001</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="39" t="s">

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F026D4-1658-43ED-AF4C-528F397AF69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14EF40B-328D-4227-885A-B8531CE003CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="24" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="25" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="49">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -682,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -863,6 +866,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -15344,7 +15359,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DA99B6-9D4E-4476-9E64-5E442631703E}">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -15361,15 +15376,13 @@
     <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.6328125" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.90625" customWidth="1"/>
+    <col min="22" max="23" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15393,9 +15406,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -15419,898 +15431,6 @@
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
       <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y7" s="44" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="48">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="45"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
-        <f>B8</f>
-        <v>Furqan</v>
-      </c>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="48">
-        <f t="shared" ref="W8:X12" si="1">SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="44"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
-      <c r="B9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="12">
-        <v>208</v>
-      </c>
-      <c r="D9" s="12">
-        <v>64</v>
-      </c>
-      <c r="E9" s="12">
-        <v>24</v>
-      </c>
-      <c r="F9" s="12">
-        <v>0</v>
-      </c>
-      <c r="G9" s="12">
-        <v>154</v>
-      </c>
-      <c r="H9" s="12">
-        <v>109</v>
-      </c>
-      <c r="I9" s="12">
-        <v>101</v>
-      </c>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="2">SUM(G9:I9)/20</f>
-        <v>18.2</v>
-      </c>
-      <c r="K9" s="48">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>16.5</v>
-      </c>
-      <c r="L9" s="45">
-        <v>11</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
-        <f>B9</f>
-        <v>Salman</v>
-      </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="3">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="44"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
-      <c r="B10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="12">
-        <v>240</v>
-      </c>
-      <c r="D10" s="12">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0</v>
-      </c>
-      <c r="F10" s="12">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>40</v>
-      </c>
-      <c r="H10" s="12">
-        <v>0</v>
-      </c>
-      <c r="I10" s="12">
-        <v>120</v>
-      </c>
-      <c r="J10" s="28">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="K10" s="48">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>10</v>
-      </c>
-      <c r="L10" s="45">
-        <v>8</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
-        <f>B10</f>
-        <v>Zesahn</v>
-      </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="44"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="12">
-        <v>112</v>
-      </c>
-      <c r="D11" s="12">
-        <v>20</v>
-      </c>
-      <c r="E11" s="12">
-        <v>20</v>
-      </c>
-      <c r="F11" s="12">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12">
-        <v>133</v>
-      </c>
-      <c r="H11" s="12">
-        <v>139</v>
-      </c>
-      <c r="I11" s="12">
-        <v>218</v>
-      </c>
-      <c r="J11" s="28">
-        <f t="shared" si="2"/>
-        <v>24.5</v>
-      </c>
-      <c r="K11" s="48">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>16.05</v>
-      </c>
-      <c r="L11" s="45">
-        <v>12</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
-        <f>B11</f>
-        <v>Umair</v>
-      </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="41"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12">
-        <v>510</v>
-      </c>
-      <c r="E12" s="12">
-        <v>590</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12">
-        <v>510</v>
-      </c>
-      <c r="H12" s="12">
-        <v>510</v>
-      </c>
-      <c r="I12" s="12">
-        <v>540</v>
-      </c>
-      <c r="J12" s="28">
-        <f t="shared" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="K12" s="48">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>66.5</v>
-      </c>
-      <c r="L12" s="45">
-        <v>6</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
-        <f>B12</f>
-        <v xml:space="preserve">Shakoor </v>
-      </c>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="41"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="4">SUM(C8:C13)</f>
-        <v>560</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="4"/>
-        <v>594</v>
-      </c>
-      <c r="E14" s="14">
-        <f t="shared" si="4"/>
-        <v>634</v>
-      </c>
-      <c r="F14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" si="4"/>
-        <v>837</v>
-      </c>
-      <c r="H14" s="14">
-        <f t="shared" si="4"/>
-        <v>758</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" si="4"/>
-        <v>979</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="4"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>4362</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="5">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13">
-        <f>D14/20</f>
-        <v>29.7</v>
-      </c>
-      <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="6">E14/20</f>
-        <v>31.7</v>
-      </c>
-      <c r="F15" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <f t="shared" si="6"/>
-        <v>41.85</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="6"/>
-        <v>37.9</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="6"/>
-        <v>48.95</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="7">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="8">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="36">
-        <f>C15+C14</f>
-        <v>560</v>
-      </c>
-      <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="9">D15+D14</f>
-        <v>623.70000000000005</v>
-      </c>
-      <c r="E16" s="36">
-        <f t="shared" si="9"/>
-        <v>665.7</v>
-      </c>
-      <c r="F16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="9"/>
-        <v>878.85</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="9"/>
-        <v>795.9</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="9"/>
-        <v>1027.95</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="10">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="11">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="36">
-        <f>C14/40</f>
-        <v>14</v>
-      </c>
-      <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="12">D14/40</f>
-        <v>14.85</v>
-      </c>
-      <c r="E17" s="36">
-        <f t="shared" si="12"/>
-        <v>15.85</v>
-      </c>
-      <c r="F17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="12"/>
-        <v>20.925000000000001</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="12"/>
-        <v>18.95</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="12"/>
-        <v>24.475000000000001</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>109.05000000000001</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="13">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="14">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2820B7-C470-4A6A-BA78-91C06063F4E3}">
-  <dimension ref="A1:X19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08984375" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
@@ -16332,7 +15452,6 @@
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
       <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
@@ -16354,7 +15473,6 @@
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
       <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
@@ -16376,7 +15494,6 @@
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
       <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -16410,7 +15527,6 @@
       </c>
       <c r="T6" s="71"/>
       <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -16455,7 +15571,7 @@
       <c r="N7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O7" s="58" t="s">
+      <c r="O7" s="75" t="s">
         <v>6</v>
       </c>
       <c r="P7" s="56" t="s">
@@ -16464,7 +15580,7 @@
       <c r="Q7" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="45" t="s">
+      <c r="R7" s="56" t="s">
         <v>8</v>
       </c>
       <c r="S7" s="45" t="s">
@@ -16473,16 +15589,16 @@
       <c r="T7" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="U7" s="12" t="s">
+      <c r="U7" s="45" t="s">
         <v>12</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="X7" s="44" t="s">
         <v>26</v>
       </c>
     </row>
@@ -16502,10 +15618,11 @@
         <f>SUM(G8:I8)/20</f>
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="48">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
+      <c r="L8" s="45"/>
       <c r="M8" s="27"/>
       <c r="N8" s="10" t="str">
         <f>B8</f>
@@ -16514,41 +15631,52 @@
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="R8" s="28"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
       <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
+      <c r="V8" s="48">
+        <f>SUM(O8:U8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="44"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="C9" s="12">
+        <v>208</v>
+      </c>
+      <c r="D9" s="12">
+        <v>64</v>
+      </c>
+      <c r="E9" s="12">
+        <v>24</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>154</v>
+      </c>
+      <c r="H9" s="12">
+        <v>109</v>
+      </c>
+      <c r="I9" s="12">
+        <v>101</v>
+      </c>
       <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+        <f t="shared" ref="J9:J13" si="0">SUM(G9:I9)/20</f>
+        <v>18.2</v>
+      </c>
+      <c r="K9" s="48">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
+        <v>16.5</v>
+      </c>
+      <c r="L9" s="45">
+        <v>11</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="10" t="str">
@@ -16558,20 +15686,16 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
       <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R9" s="28"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
       <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
+      <c r="V9" s="48">
+        <f t="shared" ref="V9:V12" si="1">SUM(O9:U9)/40</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="44" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
@@ -16579,20 +15703,37 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="C10" s="12">
+        <v>240</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>40</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>120</v>
+      </c>
       <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K10" s="48">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="L10" s="45">
+        <v>8</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="10" t="str">
@@ -16602,109 +15743,147 @@
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
       <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
+      <c r="R10" s="28"/>
+      <c r="S10" s="12">
+        <v>40</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="12">
+        <v>120</v>
+      </c>
+      <c r="V10" s="48">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="W10" s="78">
+        <v>7</v>
+      </c>
+      <c r="X10" s="44"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
+      <c r="C11" s="12">
+        <v>112</v>
+      </c>
+      <c r="D11" s="12">
+        <v>20</v>
+      </c>
+      <c r="E11" s="12">
+        <v>20</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>133</v>
+      </c>
+      <c r="H11" s="12">
+        <v>139</v>
+      </c>
+      <c r="I11" s="12">
+        <v>218</v>
+      </c>
       <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>24.5</v>
+      </c>
+      <c r="K11" s="48">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
+        <v>16.05</v>
+      </c>
+      <c r="L11" s="45">
+        <v>12</v>
       </c>
       <c r="M11" s="11"/>
       <c r="N11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
+      <c r="O11" s="12">
+        <v>112</v>
+      </c>
+      <c r="P11" s="12">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>20</v>
+      </c>
       <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S11" s="12">
+        <v>93</v>
+      </c>
+      <c r="T11" s="12">
+        <v>139</v>
+      </c>
+      <c r="U11" s="12">
+        <v>178</v>
+      </c>
+      <c r="V11" s="48">
+        <f t="shared" si="1"/>
+        <v>14.05</v>
+      </c>
+      <c r="W11" s="78">
+        <v>10</v>
+      </c>
+      <c r="X11" s="41"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>510</v>
+      </c>
+      <c r="E12" s="12">
+        <v>590</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="12">
+        <v>510</v>
+      </c>
+      <c r="H12" s="12">
+        <v>510</v>
+      </c>
+      <c r="I12" s="12">
+        <v>540</v>
+      </c>
       <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="K12" s="48">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
+        <v>66.5</v>
+      </c>
+      <c r="L12" s="45">
+        <v>6</v>
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
+        <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R12" s="28"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
+      <c r="V12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="41"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
@@ -16717,7 +15896,7 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M13" s="11"/>
@@ -16725,92 +15904,81 @@
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="R13" s="28"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:J14" si="2">SUM(C8:C13)</f>
+        <v>560</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>594</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>634</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>837</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>758</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>979</v>
       </c>
       <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>128.69999999999999</v>
       </c>
       <c r="K14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
+        <v>4362</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="10"/>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
+        <f t="shared" ref="O14:U14" si="3">SUM(O8:O13)</f>
+        <v>112</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>133</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>139</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
+        <f t="shared" si="3"/>
+        <v>298</v>
+      </c>
+      <c r="V14" s="35" t="e">
         <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
         <v>#REF!</v>
       </c>
@@ -16823,27 +15991,27 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>31.7</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>41.85</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>37.9</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>48.95</v>
       </c>
       <c r="J15" s="13"/>
       <c r="M15" s="13"/>
@@ -16853,26 +16021,25 @@
       <c r="O15" s="13"/>
       <c r="P15" s="13">
         <f>P14/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
+        <f t="shared" ref="Q15" si="5">Q14/20</f>
+        <v>1</v>
       </c>
       <c r="R15" s="13"/>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
+        <f t="shared" ref="S15:U15" si="6">S14/20</f>
+        <v>6.65</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>6.95</v>
       </c>
       <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
+        <f t="shared" si="6"/>
+        <v>14.9</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
@@ -16881,31 +16048,31 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>623.70000000000005</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>665.7</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>878.85</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>795.9</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1027.95</v>
       </c>
       <c r="J16" s="36"/>
       <c r="M16" s="13"/>
@@ -16914,68 +16081,67 @@
       </c>
       <c r="O16" s="36">
         <f>O15+O14</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
+        <f t="shared" ref="P16:Q16" si="8">P15+P14</f>
+        <v>21</v>
       </c>
       <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>21</v>
       </c>
       <c r="R16" s="36"/>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
+        <f t="shared" ref="S16:U16" si="9">S15+S14</f>
+        <v>139.65</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>145.94999999999999</v>
       </c>
       <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>312.89999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>14.85</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>15.85</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>20.925000000000001</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>18.95</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>24.475000000000001</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
+        <v>109.05000000000001</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="39" t="s">
@@ -16983,39 +16149,38 @@
       </c>
       <c r="O17" s="36">
         <f>O14/40</f>
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
+        <f t="shared" ref="P17:Q17" si="11">P14/40</f>
+        <v>0.5</v>
       </c>
       <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>0.5</v>
       </c>
       <c r="R17" s="36"/>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
+        <f t="shared" ref="S17:U17" si="12">S14/40</f>
+        <v>3.3250000000000002</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>3.4750000000000001</v>
       </c>
       <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
+        <f t="shared" si="12"/>
+        <v>7.45</v>
+      </c>
+      <c r="V17" s="35">
         <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <v>18.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -17032,9 +16197,770 @@
     <mergeCell ref="B2:J5"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
+    <mergeCell ref="N2:U5"/>
     <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="S6:U6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2820B7-C470-4A6A-BA78-91C06063F4E3}">
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8" s="27"/>
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8">
+        <f>SUM(C8:I8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
+        <f>B8</f>
+        <v>Furqan</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="77"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="77"/>
+      <c r="T8" s="77"/>
+      <c r="U8" s="77"/>
+      <c r="V8">
+        <f>SUM(N8:U8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A9" s="27"/>
+      <c r="B9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12">
+        <v>40</v>
+      </c>
+      <c r="E9" s="12">
+        <v>40</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>120</v>
+      </c>
+      <c r="H9" s="12">
+        <v>120</v>
+      </c>
+      <c r="I9" s="12">
+        <v>120</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
+        <v>11</v>
+      </c>
+      <c r="K9" s="76">
+        <v>2</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
+        <f>B9</f>
+        <v>Salman</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="77"/>
+      <c r="R9" s="77"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="77"/>
+      <c r="U9" s="77"/>
+      <c r="V9">
+        <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A10" s="27"/>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
+        <f>B10</f>
+        <v>Zesahn</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="77"/>
+      <c r="S10" s="77"/>
+      <c r="T10" s="77"/>
+      <c r="U10" s="77"/>
+      <c r="V10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="12">
+        <v>80</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12">
+        <v>40</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>40</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="K11" s="76">
+        <v>4</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
+        <f>B11</f>
+        <v>Umair</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="77"/>
+      <c r="S11" s="77"/>
+      <c r="T11" s="77"/>
+      <c r="U11" s="77"/>
+      <c r="V11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="12">
+        <v>200</v>
+      </c>
+      <c r="D12" s="12">
+        <v>440</v>
+      </c>
+      <c r="E12" s="12">
+        <v>400</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12">
+        <v>800</v>
+      </c>
+      <c r="H12" s="12">
+        <v>800</v>
+      </c>
+      <c r="I12" s="12">
+        <v>760</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="K12" s="76">
+        <v>5</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
+        <f>B12</f>
+        <v>Shakoor</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="77"/>
+      <c r="R12" s="77"/>
+      <c r="S12" s="77"/>
+      <c r="T12" s="77"/>
+      <c r="U12" s="77"/>
+      <c r="V12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="77"/>
+      <c r="S13" s="77"/>
+      <c r="T13" s="77"/>
+      <c r="U13" s="77"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="14">
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <v>280</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>480</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="2"/>
+        <v>440</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="2"/>
+        <v>960</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>920</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="2"/>
+        <v>920</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>4000</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13">
+        <f>D14/20</f>
+        <v>24</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>22</v>
+      </c>
+      <c r="F15" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="36">
+        <f>C15+C14</f>
+        <v>280</v>
+      </c>
+      <c r="D16" s="36">
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>504</v>
+      </c>
+      <c r="E16" s="36">
+        <f t="shared" si="7"/>
+        <v>462</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="7"/>
+        <v>1008</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="7"/>
+        <v>966</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="7"/>
+        <v>966</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="13"/>
+      <c r="B17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="36">
+        <f>C14/40</f>
+        <v>7</v>
+      </c>
+      <c r="D17" s="36">
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>12</v>
+      </c>
+      <c r="E17" s="36">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="10"/>
+        <v>23</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="10"/>
+        <v>23</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>100</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="36">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="C18" s="32"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:I5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14EF40B-328D-4227-885A-B8531CE003CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B6FD97-A86A-4B94-B437-544530DDD56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="25" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="24" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -685,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -866,15 +866,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -15571,7 +15562,7 @@
       <c r="N7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O7" s="75" t="s">
+      <c r="O7" s="37" t="s">
         <v>6</v>
       </c>
       <c r="P7" s="56" t="s">
@@ -15757,7 +15748,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="W10" s="78">
+      <c r="W10" s="59">
         <v>7</v>
       </c>
       <c r="X10" s="44"/>
@@ -15829,7 +15820,7 @@
         <f t="shared" si="1"/>
         <v>14.05</v>
       </c>
-      <c r="W11" s="78">
+      <c r="W11" s="59">
         <v>10</v>
       </c>
       <c r="X11" s="41"/>
@@ -15873,15 +15864,28 @@
         <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
+      <c r="P12" s="12">
+        <v>400</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>480</v>
+      </c>
       <c r="R12" s="28"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
+      <c r="S12" s="12">
+        <v>360</v>
+      </c>
+      <c r="T12" s="12">
+        <v>360</v>
+      </c>
+      <c r="U12" s="12">
+        <v>360</v>
+      </c>
       <c r="V12" s="48">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="W12" s="75">
+        <v>4</v>
       </c>
       <c r="X12" s="41"/>
     </row>
@@ -15956,11 +15960,11 @@
       </c>
       <c r="P14" s="14">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="R14" s="14">
         <f t="shared" si="3"/>
@@ -15968,15 +15972,15 @@
       </c>
       <c r="S14" s="14">
         <f t="shared" si="3"/>
-        <v>133</v>
+        <v>493</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="3"/>
-        <v>139</v>
+        <v>499</v>
       </c>
       <c r="U14" s="14">
         <f t="shared" si="3"/>
-        <v>298</v>
+        <v>658</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
@@ -16021,24 +16025,24 @@
       <c r="O15" s="13"/>
       <c r="P15" s="13">
         <f>P14/20</f>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Q15" s="13">
         <f t="shared" ref="Q15" si="5">Q14/20</f>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="R15" s="13"/>
       <c r="S15" s="13">
         <f t="shared" ref="S15:U15" si="6">S14/20</f>
-        <v>6.65</v>
+        <v>24.65</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="6"/>
-        <v>6.95</v>
+        <v>24.95</v>
       </c>
       <c r="U15" s="13">
         <f t="shared" si="6"/>
-        <v>14.9</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
@@ -16085,24 +16089,24 @@
       </c>
       <c r="P16" s="36">
         <f t="shared" ref="P16:Q16" si="8">P15+P14</f>
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="Q16" s="36">
         <f t="shared" si="8"/>
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="R16" s="36"/>
       <c r="S16" s="36">
         <f t="shared" ref="S16:U16" si="9">S15+S14</f>
-        <v>139.65</v>
+        <v>517.65</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="9"/>
-        <v>145.94999999999999</v>
+        <v>523.95000000000005</v>
       </c>
       <c r="U16" s="36">
         <f t="shared" si="9"/>
-        <v>312.89999999999998</v>
+        <v>690.9</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
@@ -16153,28 +16157,28 @@
       </c>
       <c r="P17" s="36">
         <f t="shared" ref="P17:Q17" si="11">P14/40</f>
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" s="36">
         <f t="shared" si="11"/>
-        <v>0.5</v>
+        <v>12.5</v>
       </c>
       <c r="R17" s="36"/>
       <c r="S17" s="36">
         <f t="shared" ref="S17:U17" si="12">S14/40</f>
-        <v>3.3250000000000002</v>
+        <v>12.324999999999999</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="12"/>
-        <v>3.4750000000000001</v>
+        <v>12.475</v>
       </c>
       <c r="U17" s="36">
         <f t="shared" si="12"/>
-        <v>7.45</v>
+        <v>16.45</v>
       </c>
       <c r="V17" s="35">
         <f>SUM(O17:U17)</f>
-        <v>18.05</v>
+        <v>67.05</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -16408,7 +16412,7 @@
       <c r="M7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N7" s="75" t="s">
+      <c r="N7" s="37" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="56" t="s">
@@ -16463,11 +16467,11 @@
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="77"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
       <c r="V8">
         <f>SUM(N8:U8)/40</f>
         <v>0</v>
@@ -16501,7 +16505,7 @@
         <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>11</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="44">
         <v>2</v>
       </c>
       <c r="L9" s="27"/>
@@ -16512,11 +16516,11 @@
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="77"/>
-      <c r="R9" s="77"/>
-      <c r="S9" s="77"/>
-      <c r="T9" s="77"/>
-      <c r="U9" s="77"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
       <c r="V9">
         <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
         <v>0</v>
@@ -16546,11 +16550,11 @@
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="77"/>
-      <c r="R10" s="77"/>
-      <c r="S10" s="77"/>
-      <c r="T10" s="77"/>
-      <c r="U10" s="77"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
       <c r="V10">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16580,7 +16584,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="44">
         <v>4</v>
       </c>
       <c r="L11" s="11"/>
@@ -16591,11 +16595,11 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="77"/>
-      <c r="S11" s="77"/>
-      <c r="T11" s="77"/>
-      <c r="U11" s="77"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
       <c r="V11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16629,7 +16633,7 @@
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="K12" s="76">
+      <c r="K12" s="44">
         <v>5</v>
       </c>
       <c r="L12" s="11"/>
@@ -16640,11 +16644,11 @@
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
-      <c r="U12" s="77"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
       <c r="V12">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16665,11 +16669,11 @@
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="77"/>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="77"/>
-      <c r="U13" s="77"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B6FD97-A86A-4B94-B437-544530DDD56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415140DE-01E4-4598-9176-1BF79C5E5F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="24" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="26" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="49">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -867,7 +867,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -15884,7 +15884,7 @@
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="W12" s="75">
+      <c r="W12" s="59">
         <v>4</v>
       </c>
       <c r="X12" s="41"/>
@@ -16514,16 +16514,31 @@
         <v>Salman</v>
       </c>
       <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+      <c r="O9" s="12">
+        <v>40</v>
+      </c>
+      <c r="P9" s="12">
+        <v>40</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>40</v>
+      </c>
+      <c r="S9" s="12">
+        <v>40</v>
+      </c>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
+      <c r="U9" s="12">
+        <v>40</v>
+      </c>
       <c r="V9">
         <f t="shared" ref="V9:V12" si="1">SUM(N9:U9)/40</f>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="W9" s="44">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
@@ -16718,11 +16733,11 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="3"/>
@@ -16730,11 +16745,11 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="3"/>
@@ -16742,7 +16757,7 @@
       </c>
       <c r="U14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -16786,20 +16801,20 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="5">P14/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="6">R14/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="6"/>
@@ -16850,20 +16865,20 @@
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="8">O15+O14</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="9">R15+R14</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="9"/>
@@ -16918,20 +16933,20 @@
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="11">O14/40</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="12">R14/40</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="12"/>
@@ -16940,7 +16955,7 @@
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -16972,7 +16987,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926CCD18-ABE2-4456-81B6-7B523C02EA6C}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -16983,16 +16998,15 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17002,7 +17016,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -17012,9 +17026,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -17026,21 +17039,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -17050,19 +17062,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -17072,19 +17083,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -17094,19 +17104,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -17122,25 +17131,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -17169,52 +17177,49 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -17226,39 +17231,35 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -17270,39 +17271,35 @@
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
         <v>0</v>
       </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="Q9" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U13" si="1">SUM(R9:T9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
@@ -17314,39 +17311,35 @@
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
         <v>0</v>
       </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
@@ -17358,83 +17351,90 @@
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
         <v>0</v>
       </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="D12" s="12">
+        <v>360</v>
+      </c>
+      <c r="E12" s="12">
+        <v>360</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>320</v>
+      </c>
+      <c r="H12" s="12">
+        <v>400</v>
+      </c>
+      <c r="I12" s="12">
+        <v>320</v>
+      </c>
+      <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+        <v>44</v>
+      </c>
+      <c r="K12" s="75">
+        <v>7</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
-      </c>
+        <v xml:space="preserve">Shakoor </v>
+      </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -17444,106 +17444,98 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U13" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
         <v>0</v>
       </c>
       <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="2"/>
+        <v>320</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="2"/>
+        <v>320</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>1760</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E14" s="14">
+      <c r="P14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F14" s="14">
+      <c r="Q14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="R14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="S14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="T14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J14" s="14">
+      <c r="U14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -17551,58 +17543,57 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>18</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>16</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>20</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -17612,62 +17603,61 @@
         <v>0</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>378</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="7"/>
+        <v>378</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="7"/>
+        <v>336</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="7"/>
+        <v>420</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="7"/>
+        <v>336</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
@@ -17677,73 +17667,72 @@
         <v>0</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>9</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>44</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -17753,16 +17742,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415140DE-01E4-4598-9176-1BF79C5E5F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8077A627-056B-4DC1-84B6-413965618DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" activeTab="26" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="27" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="49">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -685,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -866,9 +866,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16656,17 +16653,32 @@
         <f>B12</f>
         <v>Shakoor</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
+      <c r="N12" s="12">
+        <v>200</v>
+      </c>
+      <c r="O12" s="12">
+        <v>200</v>
+      </c>
+      <c r="P12" s="12">
+        <v>200</v>
+      </c>
       <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
+      <c r="R12" s="12">
+        <v>320</v>
+      </c>
+      <c r="S12" s="12">
+        <v>400</v>
+      </c>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
+      <c r="U12" s="12">
+        <v>280</v>
+      </c>
       <c r="V12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="W12" s="44">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
@@ -16729,15 +16741,15 @@
       <c r="M14" s="10"/>
       <c r="N14" s="14">
         <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O14" s="14">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="3"/>
@@ -16745,11 +16757,11 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>360</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>440</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="3"/>
@@ -16757,7 +16769,7 @@
       </c>
       <c r="U14" s="14">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -16801,20 +16813,20 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="5">P14/20</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="6">R14/20</f>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="6"/>
@@ -16861,24 +16873,24 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="8">O15+O14</f>
-        <v>42</v>
+        <v>252</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="8"/>
-        <v>42</v>
+        <v>252</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="9">R15+R14</f>
-        <v>42</v>
+        <v>378</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="9"/>
-        <v>42</v>
+        <v>462</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="9"/>
@@ -16929,24 +16941,24 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="11">O14/40</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="12">R14/40</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="12"/>
@@ -16955,7 +16967,7 @@
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -17385,31 +17397,17 @@
         <v>32</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12">
-        <v>360</v>
-      </c>
-      <c r="E12" s="12">
-        <v>360</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>320</v>
-      </c>
-      <c r="H12" s="12">
-        <v>400</v>
-      </c>
-      <c r="I12" s="12">
-        <v>320</v>
-      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
       <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>44</v>
-      </c>
-      <c r="K12" s="75">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" s="44"/>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
         <f>B12</f>
@@ -17470,11 +17468,11 @@
       </c>
       <c r="D14" s="14">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="2"/>
@@ -17482,19 +17480,19 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="2"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="2"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="2"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>1760</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
@@ -17543,11 +17541,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="4">E14/20</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="4"/>
@@ -17555,15 +17553,15 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -17604,11 +17602,11 @@
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="7">D15+D14</f>
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="7"/>
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="7"/>
@@ -17616,15 +17614,15 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="7"/>
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="7"/>
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="7"/>
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -17668,11 +17666,11 @@
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="10">D14/40</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="10"/>
@@ -17680,19 +17678,19 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">
@@ -17758,7 +17756,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C349645-DD2F-49D3-B3AF-0E6F627D58A3}">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -17769,19 +17767,18 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.1796875" customWidth="1"/>
+    <col min="17" max="17" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.81640625" customWidth="1"/>
+    <col min="19" max="19" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17791,7 +17788,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -17800,10 +17797,8 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -17815,21 +17810,19 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -17839,19 +17832,17 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:25" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -17861,19 +17852,17 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -17883,19 +17872,17 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -17911,25 +17898,23 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -17958,55 +17943,49 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="V7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
+      <c r="W7" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="Y7" s="44" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -18018,257 +17997,282 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="L8" s="44">
-        <v>7</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="K8" s="44"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f t="shared" ref="W8:X12" si="1">SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="U8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="44"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="C9" s="12">
+        <v>208</v>
+      </c>
+      <c r="D9" s="12">
+        <v>64</v>
+      </c>
+      <c r="E9" s="12">
+        <v>24</v>
+      </c>
       <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="2">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="44">
-        <v>8</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="G9" s="12">
+        <v>154</v>
+      </c>
+      <c r="H9" s="12">
+        <v>104</v>
+      </c>
+      <c r="I9" s="12">
+        <v>106</v>
+      </c>
+      <c r="J9">
+        <f>SUM(C9:I9)/40</f>
+        <v>16.5</v>
+      </c>
+      <c r="K9" s="44">
+        <v>11</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="3">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="N9" s="12">
+        <v>124</v>
+      </c>
+      <c r="O9" s="12">
+        <v>64</v>
+      </c>
+      <c r="P9" s="12">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>82</v>
+      </c>
+      <c r="S9" s="12">
+        <v>72</v>
+      </c>
+      <c r="T9" s="12">
+        <v>42</v>
+      </c>
+      <c r="U9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="V9" s="44">
+        <v>7</v>
+      </c>
+      <c r="W9" s="44"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="44">
-        <v>4</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+      <c r="C10" s="12">
+        <v>240</v>
+      </c>
+      <c r="D10" s="12">
+        <v>60</v>
+      </c>
+      <c r="E10" s="12">
+        <v>60</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>50</v>
+      </c>
+      <c r="H10" s="12">
+        <v>60</v>
+      </c>
+      <c r="I10" s="12">
+        <v>90</v>
+      </c>
+      <c r="J10">
+        <f t="shared" ref="J10:J12" si="0">SUM(C10:I10)/40</f>
+        <v>14</v>
+      </c>
+      <c r="K10" s="44">
+        <v>9</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="44"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="N10" s="12">
+        <v>160</v>
+      </c>
+      <c r="O10" s="12">
+        <v>60</v>
+      </c>
+      <c r="P10" s="12">
+        <v>60</v>
+      </c>
+      <c r="Q10" s="28">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>50</v>
+      </c>
+      <c r="S10" s="12">
+        <v>60</v>
+      </c>
+      <c r="T10" s="12">
+        <v>90</v>
+      </c>
+      <c r="U10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>12</v>
+      </c>
+      <c r="V10" s="44">
+        <v>8</v>
+      </c>
+      <c r="W10" s="44"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="41">
-        <v>5</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+      <c r="C11" s="12">
+        <v>160</v>
+      </c>
+      <c r="D11" s="12">
+        <v>12</v>
+      </c>
+      <c r="E11" s="12">
+        <v>12</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>106</v>
+      </c>
+      <c r="H11" s="12">
+        <v>96</v>
+      </c>
+      <c r="I11" s="12">
+        <v>96</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>12.05</v>
+      </c>
+      <c r="K11" s="41">
+        <v>6</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="N11" s="12">
+        <f>80+40</f>
+        <v>120</v>
+      </c>
+      <c r="O11" s="12">
+        <v>12</v>
+      </c>
+      <c r="P11" s="12">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="28">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>91</v>
+      </c>
+      <c r="S11" s="12">
+        <v>86</v>
+      </c>
+      <c r="T11" s="12">
+        <f>81+40</f>
+        <v>121</v>
+      </c>
+      <c r="U11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>11.05</v>
+      </c>
+      <c r="V11" s="44">
+        <v>5</v>
+      </c>
+      <c r="W11" s="41"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="C12" s="12">
+        <v>360</v>
+      </c>
+      <c r="D12" s="12">
+        <v>360</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>320</v>
+      </c>
+      <c r="G12" s="12">
+        <v>400</v>
+      </c>
+      <c r="H12" s="12">
+        <v>320</v>
+      </c>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="K12" s="41">
+        <v>7</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
-      </c>
+        <v xml:space="preserve">Shakoor </v>
+      </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="U12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -18278,110 +18282,91 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="4">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>968</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>496</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>96</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>320</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>710</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>580</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="1"/>
+        <v>292</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>3462</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:T14" si="2">SUM(N8:N13)</f>
+        <v>404</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="5">SUM(O8:O13)</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>136</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>96</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>223</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>218</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="2"/>
+        <v>253</v>
+      </c>
+      <c r="U14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
-      <c r="X14" s="35" t="e">
-        <f>P14+Q14+#REF!+R14+T14+U14+V14</f>
+      <c r="V14" s="35" t="e">
+        <f>O14+P14+#REF!+Q14+S14+T14+#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -18389,203 +18374,197 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="6">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>4.8</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>35.5</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <f t="shared" si="3"/>
+        <v>14.6</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>6.8</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="7">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>4.8</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>11.15</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="8">S14/20</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>10.9</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v>12.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="9">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>520.79999999999995</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>100.8</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>336</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>745.5</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>609</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
+        <f t="shared" si="6"/>
+        <v>306.60000000000002</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>404</v>
+      </c>
       <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>142.80000000000001</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="10">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
+        <f t="shared" si="7"/>
+        <v>100.8</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>234.15</v>
+      </c>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="11">S15+S14</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>228.9</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>265.64999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="12">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>12.4</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>2.4</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>8</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>17.75</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>14.5</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
+        <f t="shared" si="9"/>
+        <v>7.3</v>
+      </c>
+      <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
+        <v>86.55</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
         <v>23</v>
       </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>10.1</v>
+      </c>
       <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>3.4</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="13">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
+        <f t="shared" si="10"/>
+        <v>2.4</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>5.5750000000000002</v>
+      </c>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="14">S14/40</f>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>5.45</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-      <c r="X17" s="35">
-        <f>SUM(P17:V17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="11"/>
+        <v>6.3250000000000002</v>
+      </c>
+      <c r="U17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>33.25</v>
+      </c>
+      <c r="V17" s="35">
+        <f>SUM(O17:T17)</f>
+        <v>23.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -18595,16 +18574,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:T5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:T6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18612,7 +18590,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2852D254-6817-4C2C-AE7A-E9C5892E76B5}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -18623,15 +18601,14 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18641,7 +18618,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -18651,9 +18628,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -18665,21 +18641,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -18689,19 +18664,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -18711,19 +18685,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -18733,19 +18706,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -18761,25 +18733,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -18808,52 +18779,49 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -18865,183 +18833,183 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="47">
+      <c r="J8" s="47">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="L8" s="47">
-        <v>4</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="K8" s="47"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="47">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28"/>
+      <c r="V8" s="47">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
+      <c r="C9" s="12">
+        <v>92</v>
+      </c>
+      <c r="D9" s="12">
+        <v>52</v>
+      </c>
+      <c r="E9" s="12">
+        <v>12</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>62</v>
+      </c>
+      <c r="H9" s="12">
+        <v>16</v>
+      </c>
+      <c r="I9" s="12">
+        <v>60</v>
+      </c>
+      <c r="J9" s="47">
+        <f>SUM(C9:F9,G9,H9,I9)/40</f>
+        <v>7.35</v>
       </c>
       <c r="K9" s="47">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="47">
-        <v>8</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+        <v>3</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="47">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28"/>
+      <c r="V9" s="47">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="C10" s="12">
+        <v>80</v>
+      </c>
+      <c r="D10" s="12">
+        <v>50</v>
+      </c>
+      <c r="E10" s="12">
+        <v>40</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>95</v>
+      </c>
+      <c r="H10" s="12">
+        <v>125</v>
+      </c>
+      <c r="I10" s="12">
+        <v>105</v>
+      </c>
+      <c r="J10" s="47">
+        <f>SUM(C10:F10,G10,H10,I10)/40</f>
+        <v>12.375</v>
       </c>
       <c r="K10" s="47">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="47">
-        <v>10</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>6</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10" s="47">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10" s="28"/>
+      <c r="V10" s="47">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="C11" s="12">
+        <v>124</v>
+      </c>
+      <c r="D11" s="12">
+        <v>40</v>
+      </c>
+      <c r="E11" s="12">
+        <v>80</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>92</v>
+      </c>
+      <c r="H11" s="12">
+        <v>92</v>
+      </c>
+      <c r="I11" s="12">
+        <v>100</v>
+      </c>
+      <c r="J11" s="47">
+        <f>SUM(C11:F11,G11,H11,I11)/40</f>
+        <v>13.2</v>
       </c>
       <c r="K11" s="47">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="47">
-        <v>20</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>5</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="47">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11" s="28"/>
+      <c r="V11" s="47">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -19053,42 +19021,30 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="47">
+      <c r="J12" s="47">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>0</v>
       </c>
-      <c r="L12" s="47">
-        <v>5</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="K12" s="47"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12" s="47">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12" s="28"/>
+      <c r="V12" s="47">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -19098,106 +19054,92 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U13" s="28"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="0">SUM(C8:C13)</f>
+        <v>296</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>142</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>132</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>249</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>233</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <f t="shared" si="0"/>
+        <v>265</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>1317</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="1">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -19205,199 +19147,196 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="2">E14/20</f>
+        <v>6.6</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>12.45</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>11.65</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <f t="shared" si="2"/>
+        <v>13.25</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="3">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="4">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="5">D15+D14</f>
+        <v>149.1</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>138.6</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>261.45</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>244.65</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
+        <f t="shared" si="5"/>
+        <v>278.25</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
       <c r="O16" s="36">
-        <f>O15+O14</f>
+        <f t="shared" ref="O16:P16" si="6">O15+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="7">R15+R14</f>
+        <v>0</v>
+      </c>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="8">D14/40</f>
+        <v>3.55</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>3.3</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>6.2249999999999996</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>5.8250000000000002</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
+        <f t="shared" si="8"/>
+        <v>6.625</v>
+      </c>
+      <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
+        <v>32.924999999999997</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
         <v>23</v>
       </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
       <c r="O17" s="36">
-        <f>O14/40</f>
+        <f t="shared" ref="O17:P17" si="9">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="10">R14/40</f>
+        <v>0</v>
+      </c>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -19407,16 +19346,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8077A627-056B-4DC1-84B6-413965618DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C25C4-76A4-4538-B185-B0DC553E9FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="27" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="29" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="49">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -685,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -866,6 +866,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -17756,7 +17759,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C349645-DD2F-49D3-B3AF-0E6F627D58A3}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -17778,7 +17781,7 @@
     <col min="20" max="20" width="4.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17798,7 +17801,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -17822,7 +17825,7 @@
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
     </row>
-    <row r="3" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -17842,7 +17845,7 @@
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
     </row>
-    <row r="4" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -17862,7 +17865,7 @@
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
     </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -17882,7 +17885,7 @@
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -17914,7 +17917,7 @@
       <c r="S6" s="71"/>
       <c r="T6" s="71"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -17981,11 +17984,8 @@
       <c r="V7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="W7" s="44" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -18018,9 +18018,8 @@
         <f>SUM(N8:P8,R8,S8,T8)/40</f>
         <v>0</v>
       </c>
-      <c r="W8" s="44"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -18084,9 +18083,8 @@
       <c r="V9" s="44">
         <v>7</v>
       </c>
-      <c r="W9" s="44"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
@@ -18152,9 +18150,8 @@
       <c r="V10" s="44">
         <v>8</v>
       </c>
-      <c r="W10" s="44"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
@@ -18222,9 +18219,8 @@
       <c r="V11" s="44">
         <v>5</v>
       </c>
-      <c r="W11" s="41"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>32</v>
@@ -18261,18 +18257,31 @@
         <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
+      <c r="O12" s="12">
+        <v>120</v>
+      </c>
+      <c r="P12" s="12">
+        <v>40</v>
+      </c>
       <c r="Q12" s="28"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
+      <c r="R12" s="12">
+        <v>77</v>
+      </c>
+      <c r="S12" s="12">
+        <v>80</v>
+      </c>
+      <c r="T12" s="12">
+        <v>159</v>
+      </c>
       <c r="U12">
         <f>SUM(N12:P12,R12,S12,T12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+        <v>11.9</v>
+      </c>
+      <c r="V12" s="41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -18292,7 +18301,7 @@
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
@@ -18335,11 +18344,11 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="2"/>
-        <v>136</v>
+        <v>256</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="2"/>
@@ -18347,15 +18356,15 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="2"/>
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="2"/>
-        <v>218</v>
+        <v>298</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="2"/>
-        <v>253</v>
+        <v>412</v>
       </c>
       <c r="U14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -18366,7 +18375,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -18403,27 +18412,27 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>6.8</v>
+        <v>12.8</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="4">P14/20</f>
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="5">R14/20</f>
-        <v>11.15</v>
+        <v>15</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>10.9</v>
+        <v>14.9</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="5"/>
-        <v>12.65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -18466,24 +18475,24 @@
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="7">O15+O14</f>
-        <v>142.80000000000001</v>
+        <v>268.8</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="7"/>
-        <v>100.8</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>234.15</v>
+        <v>315</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="8"/>
-        <v>228.9</v>
+        <v>312.89999999999998</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="8"/>
-        <v>265.64999999999998</v>
+        <v>432.6</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.35">
@@ -18533,32 +18542,32 @@
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="10">O14/40</f>
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="10"/>
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="11">R14/40</f>
-        <v>5.5750000000000002</v>
+        <v>7.5</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="11"/>
-        <v>5.45</v>
+        <v>7.45</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="11"/>
-        <v>6.3250000000000002</v>
+        <v>10.3</v>
       </c>
       <c r="U17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>33.25</v>
+        <v>45.150000000000006</v>
       </c>
       <c r="V17" s="35">
         <f>SUM(O17:T17)</f>
-        <v>23.15</v>
+        <v>35.049999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -18590,7 +18599,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2852D254-6817-4C2C-AE7A-E9C5892E76B5}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -18605,10 +18614,10 @@
     <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -18627,9 +18636,8 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -18652,9 +18660,8 @@
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -18673,9 +18680,8 @@
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -18694,9 +18700,8 @@
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
-    </row>
-    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -18715,9 +18720,8 @@
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -18748,9 +18752,8 @@
       </c>
       <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -18812,16 +18815,13 @@
         <v>12</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -18850,13 +18850,12 @@
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="47">
-        <f>SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U8" s="47">
+        <f>SUM(N8:T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -18894,20 +18893,36 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="47">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="N9" s="12">
+        <v>112</v>
+      </c>
+      <c r="O9" s="12">
+        <v>72</v>
+      </c>
+      <c r="P9" s="12">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>82</v>
+      </c>
+      <c r="S9" s="12">
+        <v>26</v>
+      </c>
+      <c r="T9" s="12">
+        <v>70</v>
+      </c>
+      <c r="U9" s="47">
+        <f t="shared" ref="U9:U12" si="0">SUM(N9:T9)/40</f>
+        <v>9.35</v>
+      </c>
+      <c r="V9" s="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
@@ -18945,20 +18960,36 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="47">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="N10" s="12">
+        <v>80</v>
+      </c>
+      <c r="O10" s="12">
+        <v>50</v>
+      </c>
+      <c r="P10" s="12">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="28">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>95</v>
+      </c>
+      <c r="S10" s="12">
+        <v>125</v>
+      </c>
+      <c r="T10" s="12">
+        <v>105</v>
+      </c>
+      <c r="U10" s="47">
+        <f t="shared" si="0"/>
+        <v>12.375</v>
+      </c>
+      <c r="V10" s="75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
@@ -18996,20 +19027,36 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="28"/>
-      <c r="V11" s="47">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="N11" s="12">
+        <v>112</v>
+      </c>
+      <c r="O11" s="12">
+        <v>40</v>
+      </c>
+      <c r="P11" s="12">
+        <v>80</v>
+      </c>
+      <c r="Q11" s="28">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>92</v>
+      </c>
+      <c r="S11" s="12">
+        <v>92</v>
+      </c>
+      <c r="T11" s="12">
+        <v>100</v>
+      </c>
+      <c r="U11" s="47">
+        <f t="shared" si="0"/>
+        <v>12.9</v>
+      </c>
+      <c r="V11" s="75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -19038,13 +19085,12 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="47">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U12" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -19063,37 +19109,36 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="28"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="0">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
         <v>296</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>142</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>132</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>249</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>233</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>265</v>
       </c>
       <c r="J14" s="35">
@@ -19103,43 +19148,39 @@
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="1">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:T14" si="2">SUM(N8:N13)</f>
+        <v>304</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>162</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>132</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>269</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>243</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="35" t="e">
+        <f t="shared" si="2"/>
+        <v>275</v>
+      </c>
+      <c r="U14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -19150,23 +19191,23 @@
         <v>7.1</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="2">E14/20</f>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
         <v>6.6</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12.45</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.65</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13.25</v>
       </c>
       <c r="L15" s="13"/>
@@ -19176,28 +19217,27 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="3">P14/20</f>
-        <v>0</v>
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>6.6</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="4">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>13.45</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>12.15</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -19207,27 +19247,27 @@
         <v>296</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="5">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
         <v>149.1</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>138.6</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>261.45</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>244.65</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>278.25</v>
       </c>
       <c r="L16" s="13"/>
@@ -19236,32 +19276,31 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="6">O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>170.1</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>138.6</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="7">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>282.45</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>255.15</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>288.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
@@ -19271,27 +19310,27 @@
         <v>7.4</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="8">D14/40</f>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
         <v>3.55</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.3</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.2249999999999996</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5.8250000000000002</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.625</v>
       </c>
       <c r="J17" s="35">
@@ -19304,39 +19343,38 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="9">O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>4.05</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>3.3</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="10">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>6.7249999999999996</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>6.0750000000000002</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36"/>
-      <c r="V17" s="35">
+        <f t="shared" si="11"/>
+        <v>6.875</v>
+      </c>
+      <c r="U17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+        <v>34.625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -19352,9 +19390,9 @@
     <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:I6"/>
-    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="M2:T5"/>
     <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="R6:T6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20449,7 +20487,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E53001-FEFC-449D-A8A3-82DAE50447EF}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -20460,16 +20498,15 @@
     <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20479,7 +20516,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -20489,9 +20526,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="61" t="s">
         <v>34</v>
@@ -20503,21 +20539,20 @@
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="61" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="62"/>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="63"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="64"/>
       <c r="C3" s="65"/>
@@ -20527,19 +20562,18 @@
       <c r="G3" s="65"/>
       <c r="H3" s="65"/>
       <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
       <c r="O3" s="65"/>
       <c r="P3" s="65"/>
       <c r="Q3" s="65"/>
       <c r="R3" s="65"/>
       <c r="S3" s="65"/>
       <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="66"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="64"/>
       <c r="C4" s="65"/>
@@ -20549,19 +20583,18 @@
       <c r="G4" s="65"/>
       <c r="H4" s="65"/>
       <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="65"/>
       <c r="S4" s="65"/>
       <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="66"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="67"/>
       <c r="C5" s="68"/>
@@ -20571,19 +20604,18 @@
       <c r="G5" s="68"/>
       <c r="H5" s="68"/>
       <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
       <c r="O5" s="68"/>
       <c r="P5" s="68"/>
       <c r="Q5" s="68"/>
       <c r="R5" s="68"/>
       <c r="S5" s="68"/>
       <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="69"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -20599,25 +20631,24 @@
       </c>
       <c r="H6" s="71"/>
       <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="71" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="71"/>
       <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="72"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -20646,52 +20677,49 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -20703,171 +20731,206 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="J8">
         <f>SUM(C8:F8,G8,H8,I8)/40</f>
         <v>0</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="C9" s="12">
+        <v>139</v>
+      </c>
+      <c r="D9" s="12">
+        <v>64</v>
+      </c>
+      <c r="E9" s="12">
+        <v>12</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>70</v>
+      </c>
+      <c r="H9" s="12">
+        <v>40</v>
+      </c>
+      <c r="I9" s="12">
+        <v>66</v>
+      </c>
+      <c r="J9">
         <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+        <v>9.7750000000000004</v>
+      </c>
+      <c r="K9" s="75">
+        <v>8</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="Q9" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U13" si="1">SUM(R9:T9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
+      <c r="C10" s="12">
+        <v>204</v>
+      </c>
+      <c r="D10" s="12">
+        <v>46</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>45</v>
+      </c>
+      <c r="H10" s="12">
+        <v>56</v>
+      </c>
+      <c r="I10" s="12">
+        <v>51</v>
+      </c>
+      <c r="J10">
         <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>11.2</v>
+      </c>
+      <c r="K10" s="75">
+        <v>15</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U10" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="C11" s="12">
+        <v>216</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>80</v>
+      </c>
+      <c r="H11" s="12">
+        <v>80</v>
+      </c>
+      <c r="I11" s="12">
+        <v>160</v>
+      </c>
+      <c r="J11">
         <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>15.7</v>
+      </c>
+      <c r="K11" s="75">
+        <v>5</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U11" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -20879,39 +20942,35 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="J12">
         <f>SUM(C12:F12,G12,H12,I12)/40</f>
         <v>0</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U12" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -20921,106 +20980,98 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U13" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
+        <v>559</v>
       </c>
       <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>156</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="2"/>
+        <v>104</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="2"/>
+        <v>195</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="2"/>
+        <v>277</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>1467</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E14" s="14">
+      <c r="P14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F14" s="14">
+      <c r="Q14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="R14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="S14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I14" s="14">
+      <c r="T14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J14" s="14">
+      <c r="U14" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -21028,199 +21079,196 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
+        <v>5.2</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>9.75</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <f t="shared" si="4"/>
+        <v>13.85</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
+        <v>163.80000000000001</v>
       </c>
       <c r="E16" s="36">
+        <f t="shared" si="7"/>
+        <v>109.2</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="7"/>
+        <v>204.75</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="7"/>
+        <v>184.8</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="7"/>
+        <v>290.85000000000002</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="36">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>13.975</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
+        <v>3.9</v>
       </c>
       <c r="E17" s="36">
+        <f t="shared" si="10"/>
+        <v>2.6</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="10"/>
+        <v>4.875</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="10"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="10"/>
+        <v>6.9249999999999998</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>36.674999999999997</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="36">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="36">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -21230,16 +21278,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C25C4-76A4-4538-B185-B0DC553E9FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6C36CD-AE45-4B17-B170-83AAB74031D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="29" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="30" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="49">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -685,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -825,6 +825,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -868,6 +871,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1215,57 +1221,57 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="B2" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
     </row>
     <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
     </row>
     <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1273,18 +1279,18 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
@@ -1634,95 +1640,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="N2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="64"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="67"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="67"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="70"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="70"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -1730,33 +1736,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="73"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="P6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="72"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="73"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -2524,87 +2530,87 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -2612,32 +2618,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="73" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="74"/>
-      <c r="T6" s="74"/>
-      <c r="U6" s="74"/>
+      <c r="S6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -3303,91 +3309,91 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -3395,32 +3401,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4172,95 +4178,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="N2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="64"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="67"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="67"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="70"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="70"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -4268,33 +4274,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="73"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="P6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="72"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="73"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -4970,87 +4976,87 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="64"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="67"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="67"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="70"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5058,31 +5064,31 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -5815,87 +5821,87 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="64"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="67"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="67"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="70"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -5903,31 +5909,31 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -6636,91 +6642,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6728,32 +6734,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -7518,91 +7524,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -7610,32 +7616,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -8335,91 +8341,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -8427,32 +8433,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -9206,91 +9212,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -9298,32 +9304,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -10076,58 +10082,58 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="64"/>
       <c r="AB2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
       <c r="AB3">
         <v>14</v>
       </c>
@@ -10140,51 +10146,51 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="66"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="69"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -10192,35 +10198,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71" t="s">
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11113,95 +11119,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="N2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="64"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="67"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="67"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="70"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="70"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -11209,33 +11215,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="73"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="P6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="72"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="73"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -11916,87 +11922,87 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="64"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="67"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="67"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="70"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12004,31 +12010,31 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -12735,91 +12741,91 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -12827,32 +12833,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -13624,91 +13630,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -13716,32 +13722,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -14432,95 +14438,95 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="N2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="64"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="67"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="67"/>
     </row>
     <row r="5" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="70"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="70"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -14528,33 +14534,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="73"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="P6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="72"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="73"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -15400,91 +15406,91 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="N2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="70"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -15492,32 +15498,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="73"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="P6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="72"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -16253,91 +16259,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -16345,32 +16351,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -17044,91 +17050,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -17136,32 +17142,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -17803,87 +17809,87 @@
     </row>
     <row r="2" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
     </row>
     <row r="3" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
     </row>
     <row r="4" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
     </row>
     <row r="5" spans="1:22" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -17891,31 +17897,31 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -18639,87 +18645,87 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -18727,31 +18733,31 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -18902,9 +18908,7 @@
       <c r="P9" s="12">
         <v>12</v>
       </c>
-      <c r="Q9" s="28">
-        <v>0</v>
-      </c>
+      <c r="Q9" s="28"/>
       <c r="R9" s="12">
         <v>82</v>
       </c>
@@ -18969,9 +18973,7 @@
       <c r="P10" s="12">
         <v>40</v>
       </c>
-      <c r="Q10" s="28">
-        <v>0</v>
-      </c>
+      <c r="Q10" s="28"/>
       <c r="R10" s="12">
         <v>95</v>
       </c>
@@ -18985,7 +18987,7 @@
         <f t="shared" si="0"/>
         <v>12.375</v>
       </c>
-      <c r="V10" s="75">
+      <c r="V10" s="44">
         <v>6</v>
       </c>
     </row>
@@ -19036,9 +19038,7 @@
       <c r="P11" s="12">
         <v>80</v>
       </c>
-      <c r="Q11" s="28">
-        <v>0</v>
-      </c>
+      <c r="Q11" s="28"/>
       <c r="R11" s="12">
         <v>92</v>
       </c>
@@ -19052,7 +19052,7 @@
         <f t="shared" si="0"/>
         <v>12.9</v>
       </c>
-      <c r="V11" s="75">
+      <c r="V11" s="44">
         <v>4</v>
       </c>
     </row>
@@ -19074,20 +19074,32 @@
       </c>
       <c r="K12" s="47"/>
       <c r="L12" s="11"/>
-      <c r="M12" s="10" t="str">
-        <f>B12</f>
-        <v>Mubeen</v>
+      <c r="M12" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
+      <c r="O12" s="12">
+        <v>320</v>
+      </c>
+      <c r="P12" s="12">
+        <v>320</v>
+      </c>
       <c r="Q12" s="28"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
+      <c r="R12" s="12">
+        <v>480</v>
+      </c>
+      <c r="S12" s="12">
+        <v>560</v>
+      </c>
+      <c r="T12" s="12">
+        <v>480</v>
+      </c>
       <c r="U12" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="V12" s="41">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
@@ -19153,11 +19165,11 @@
       </c>
       <c r="O14" s="14">
         <f t="shared" si="2"/>
-        <v>162</v>
+        <v>482</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="2"/>
-        <v>132</v>
+        <v>452</v>
       </c>
       <c r="Q14" s="14">
         <f t="shared" si="2"/>
@@ -19165,15 +19177,15 @@
       </c>
       <c r="R14" s="14">
         <f t="shared" si="2"/>
-        <v>269</v>
+        <v>749</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="2"/>
-        <v>243</v>
+        <v>803</v>
       </c>
       <c r="T14" s="14">
         <f t="shared" si="2"/>
-        <v>275</v>
+        <v>755</v>
       </c>
       <c r="U14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -19217,24 +19229,24 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>8.1</v>
+        <v>24.1</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" ref="P15" si="4">P14/20</f>
-        <v>6.6</v>
+        <v>22.6</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
         <f t="shared" ref="R15:T15" si="5">R14/20</f>
-        <v>13.45</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>12.15</v>
+        <v>40.15</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="5"/>
-        <v>13.75</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
@@ -19280,24 +19292,24 @@
       </c>
       <c r="O16" s="36">
         <f t="shared" ref="O16:P16" si="7">O15+O14</f>
-        <v>170.1</v>
+        <v>506.1</v>
       </c>
       <c r="P16" s="36">
         <f t="shared" si="7"/>
-        <v>138.6</v>
+        <v>474.6</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
         <f t="shared" ref="R16:T16" si="8">R15+R14</f>
-        <v>282.45</v>
+        <v>786.45</v>
       </c>
       <c r="S16" s="36">
         <f t="shared" si="8"/>
-        <v>255.15</v>
+        <v>843.15</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="8"/>
-        <v>288.75</v>
+        <v>792.75</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
@@ -19347,28 +19359,28 @@
       </c>
       <c r="O17" s="36">
         <f t="shared" ref="O17:P17" si="10">O14/40</f>
-        <v>4.05</v>
+        <v>12.05</v>
       </c>
       <c r="P17" s="36">
         <f t="shared" si="10"/>
-        <v>3.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
         <f t="shared" ref="R17:T17" si="11">R14/40</f>
-        <v>6.7249999999999996</v>
+        <v>18.725000000000001</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="11"/>
-        <v>6.0750000000000002</v>
+        <v>20.074999999999999</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="11"/>
-        <v>6.875</v>
+        <v>18.875</v>
       </c>
       <c r="U17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>34.625</v>
+        <v>88.625</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
@@ -19446,103 +19458,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="64"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="66"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="69"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -19550,35 +19562,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71" t="s">
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -20487,6 +20499,825 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E53001-FEFC-449D-A8A3-82DAE50447EF}">
+  <dimension ref="A1:Y19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.08984375" customWidth="1"/>
+    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+    </row>
+    <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
+        <v>3</v>
+      </c>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="27"/>
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8">
+        <f>SUM(C8:F8,G8,H8,I8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
+        <f>B8</f>
+        <v>Furqan</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8">
+        <f>SUM(N8:T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="27"/>
+      <c r="B9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="12">
+        <v>139</v>
+      </c>
+      <c r="D9" s="12">
+        <v>64</v>
+      </c>
+      <c r="E9" s="12">
+        <v>12</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>70</v>
+      </c>
+      <c r="H9" s="12">
+        <v>40</v>
+      </c>
+      <c r="I9" s="12">
+        <v>66</v>
+      </c>
+      <c r="J9">
+        <f>SUM(C9:F9,G9,H9,I9)/40</f>
+        <v>9.7750000000000004</v>
+      </c>
+      <c r="K9" s="44">
+        <v>8</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
+        <f>B9</f>
+        <v>Salman</v>
+      </c>
+      <c r="N9" s="12">
+        <v>119</v>
+      </c>
+      <c r="O9" s="12">
+        <v>12</v>
+      </c>
+      <c r="P9" s="12">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="28">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>58</v>
+      </c>
+      <c r="S9" s="12">
+        <v>40</v>
+      </c>
+      <c r="T9" s="12">
+        <v>54</v>
+      </c>
+      <c r="U9">
+        <f t="shared" ref="U9:U12" si="0">SUM(N9:T9)/40</f>
+        <v>7.375</v>
+      </c>
+      <c r="V9" s="44">
+        <v>6</v>
+      </c>
+      <c r="X9" s="61">
+        <v>51</v>
+      </c>
+      <c r="Y9">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="27"/>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12">
+        <v>204</v>
+      </c>
+      <c r="D10" s="12">
+        <v>46</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>45</v>
+      </c>
+      <c r="H10" s="12">
+        <v>56</v>
+      </c>
+      <c r="I10" s="12">
+        <v>51</v>
+      </c>
+      <c r="J10">
+        <f>SUM(C10:F10,G10,H10,I10)/40</f>
+        <v>11.2</v>
+      </c>
+      <c r="K10" s="44">
+        <v>15</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
+        <f>B10</f>
+        <v>Zesahn</v>
+      </c>
+      <c r="N10" s="12">
+        <v>60</v>
+      </c>
+      <c r="O10" s="12">
+        <v>40</v>
+      </c>
+      <c r="P10" s="12">
+        <v>40</v>
+      </c>
+      <c r="Q10" s="28">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>39</v>
+      </c>
+      <c r="S10" s="12">
+        <v>50</v>
+      </c>
+      <c r="T10" s="12">
+        <v>51</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="V10" s="44">
+        <v>9</v>
+      </c>
+      <c r="X10" s="61">
+        <v>160</v>
+      </c>
+      <c r="Y10">
+        <f>Y9-X13</f>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="12">
+        <v>216</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>80</v>
+      </c>
+      <c r="H11" s="12">
+        <v>80</v>
+      </c>
+      <c r="I11" s="12">
+        <v>160</v>
+      </c>
+      <c r="J11">
+        <f>SUM(C11:F11,G11,H11,I11)/40</f>
+        <v>15.7</v>
+      </c>
+      <c r="K11" s="44">
+        <v>5</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
+        <f>B11</f>
+        <v>Umair</v>
+      </c>
+      <c r="N11" s="12">
+        <v>216</v>
+      </c>
+      <c r="O11" s="12">
+        <v>46</v>
+      </c>
+      <c r="P11" s="12">
+        <v>46</v>
+      </c>
+      <c r="Q11" s="28">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>80</v>
+      </c>
+      <c r="S11" s="12">
+        <v>80</v>
+      </c>
+      <c r="T11" s="12">
+        <v>160</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="0"/>
+        <v>15.7</v>
+      </c>
+      <c r="V11" s="44">
+        <v>5</v>
+      </c>
+      <c r="X11" s="61">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12">
+        <f>SUM(C12:F12,G12,H12,I12)/40</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
+        <f>B12</f>
+        <v>Mubeen</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="X13" s="61">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="14">
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
+        <v>559</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+      <c r="E14" s="14">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="F14" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <f t="shared" si="1"/>
+        <v>195</v>
+      </c>
+      <c r="H14" s="14">
+        <f t="shared" si="1"/>
+        <v>176</v>
+      </c>
+      <c r="I14" s="14">
+        <f t="shared" si="1"/>
+        <v>277</v>
+      </c>
+      <c r="J14" s="35">
+        <f>C14+D14+E14+F14+G14+H14+I14</f>
+        <v>1467</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f>SUM(N8:N12)</f>
+        <v>395</v>
+      </c>
+      <c r="O14" s="14">
+        <f t="shared" ref="O14:T14" si="2">SUM(O8:O12)</f>
+        <v>98</v>
+      </c>
+      <c r="P14" s="14">
+        <f t="shared" si="2"/>
+        <v>98</v>
+      </c>
+      <c r="Q14" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="14">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="T14" s="14">
+        <f t="shared" si="2"/>
+        <v>265</v>
+      </c>
+      <c r="U14" s="35">
+        <f>SUM(N14:T14)/40</f>
+        <v>30.074999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13">
+        <f>D14/20</f>
+        <v>7.8</v>
+      </c>
+      <c r="E15" s="13">
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
+        <v>5.2</v>
+      </c>
+      <c r="F15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" si="3"/>
+        <v>9.75</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="3"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="3"/>
+        <v>13.85</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P15" s="13">
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>8.85</v>
+      </c>
+      <c r="S15" s="13">
+        <f t="shared" si="5"/>
+        <v>8.5</v>
+      </c>
+      <c r="T15" s="13">
+        <f t="shared" si="5"/>
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="36">
+        <f>C15+C14</f>
+        <v>559</v>
+      </c>
+      <c r="D16" s="36">
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
+        <v>163.80000000000001</v>
+      </c>
+      <c r="E16" s="36">
+        <f t="shared" si="6"/>
+        <v>109.2</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="6"/>
+        <v>204.75</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="6"/>
+        <v>184.8</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="6"/>
+        <v>290.85000000000002</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>395</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>102.9</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="7"/>
+        <v>102.9</v>
+      </c>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>185.85</v>
+      </c>
+      <c r="S16" s="36">
+        <f t="shared" si="8"/>
+        <v>178.5</v>
+      </c>
+      <c r="T16" s="36">
+        <f t="shared" si="8"/>
+        <v>278.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A17" s="13"/>
+      <c r="B17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="36">
+        <f>C14/40</f>
+        <v>13.975</v>
+      </c>
+      <c r="D17" s="36">
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
+        <v>3.9</v>
+      </c>
+      <c r="E17" s="36">
+        <f t="shared" si="9"/>
+        <v>2.6</v>
+      </c>
+      <c r="F17" s="36">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="9"/>
+        <v>4.875</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="9"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="I17" s="36">
+        <f t="shared" si="9"/>
+        <v>6.9249999999999998</v>
+      </c>
+      <c r="J17" s="35">
+        <f>SUM(C17:I17)</f>
+        <v>36.674999999999997</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>9.875</v>
+      </c>
+      <c r="O17" s="36">
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="P17" s="36">
+        <f t="shared" si="10"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>4.4249999999999998</v>
+      </c>
+      <c r="S17" s="36">
+        <f t="shared" si="11"/>
+        <v>4.25</v>
+      </c>
+      <c r="T17" s="36">
+        <f t="shared" si="11"/>
+        <v>6.625</v>
+      </c>
+      <c r="U17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>30.074999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="C18" s="32"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:I5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:T5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:T6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E2FD71-4BFE-4078-B64C-19DAB7732322}">
   <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -20529,91 +21360,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -20621,32 +21452,32 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -20765,31 +21596,31 @@
         <v>14</v>
       </c>
       <c r="C9" s="12">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D9" s="12">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E9" s="12">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F9" s="12">
         <v>0</v>
       </c>
       <c r="G9" s="12">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H9" s="12">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="I9" s="12">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="J9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>9.7750000000000004</v>
-      </c>
-      <c r="K9" s="75">
+        <f t="shared" ref="J9:J12" si="1">SUM(C9:F9,G9,H9,I9)/40</f>
+        <v>11.65</v>
+      </c>
+      <c r="K9" s="76">
         <v>8</v>
       </c>
       <c r="L9" s="27"/>
@@ -20808,7 +21639,7 @@
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
       <c r="U9" s="28">
-        <f t="shared" ref="U9:U13" si="1">SUM(R9:T9)/20</f>
+        <f t="shared" ref="U9:U13" si="2">SUM(R9:T9)/20</f>
         <v>0</v>
       </c>
       <c r="V9">
@@ -20822,32 +21653,32 @@
         <v>37</v>
       </c>
       <c r="C10" s="12">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="D10" s="12">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E10" s="12">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F10" s="12">
         <v>0</v>
       </c>
       <c r="G10" s="12">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="H10" s="12">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I10" s="12">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="J10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>11.2</v>
-      </c>
-      <c r="K10" s="75">
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="K10" s="76">
+        <v>11</v>
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="10" t="str">
@@ -20865,7 +21696,7 @@
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
       <c r="U10" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V10">
@@ -20879,32 +21710,26 @@
         <v>31</v>
       </c>
       <c r="C11" s="12">
-        <v>216</v>
-      </c>
-      <c r="D11" s="12">
-        <v>46</v>
-      </c>
-      <c r="E11" s="12">
-        <v>46</v>
-      </c>
-      <c r="F11" s="12">
-        <v>0</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
       <c r="G11" s="12">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="H11" s="12">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I11" s="12">
-        <v>160</v>
+        <v>52</v>
       </c>
       <c r="J11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>15.7</v>
-      </c>
-      <c r="K11" s="75">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>14.1</v>
+      </c>
+      <c r="K11" s="76">
+        <v>12</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="10" t="str">
@@ -20922,7 +21747,7 @@
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
       <c r="U11" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V11">
@@ -20933,23 +21758,36 @@
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="12">
+        <v>2160</v>
+      </c>
+      <c r="E12" s="12">
+        <v>2720</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
+      <c r="G12" s="12">
+        <v>4360</v>
+      </c>
+      <c r="H12" s="12">
+        <v>4640</v>
+      </c>
+      <c r="I12" s="12">
+        <v>7040</v>
+      </c>
       <c r="J12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>523</v>
+      </c>
+      <c r="K12" s="77">
+        <v>6</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="10" t="str">
         <f>B12</f>
-        <v>Mubeen</v>
+        <v xml:space="preserve">Shakoor </v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
@@ -20962,7 +21800,7 @@
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
       <c r="U12" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="V12">
@@ -20993,7 +21831,7 @@
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -21001,69 +21839,69 @@
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
-        <v>559</v>
+        <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
+        <v>572</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="2"/>
-        <v>156</v>
+        <f t="shared" si="3"/>
+        <v>2290</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="2"/>
-        <v>104</v>
+        <f t="shared" si="3"/>
+        <v>2815</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="2"/>
-        <v>195</v>
+        <f t="shared" si="3"/>
+        <v>4672</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="2"/>
-        <v>176</v>
+        <f t="shared" si="3"/>
+        <v>4832</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="2"/>
-        <v>277</v>
+        <f t="shared" si="3"/>
+        <v>7269</v>
       </c>
       <c r="J14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>1467</v>
+        <f>SUM(C14:I14)/40</f>
+        <v>561.25</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <f t="shared" ref="N14:U14" si="4">SUM(N8:N13)</f>
         <v>0</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="V14" s="35" t="e">
@@ -21079,27 +21917,27 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>7.8</v>
+        <v>114.5</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="4">E14/20</f>
-        <v>5.2</v>
+        <f t="shared" ref="E15:I15" si="5">E14/20</f>
+        <v>140.75</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="4"/>
-        <v>9.75</v>
+        <f t="shared" si="5"/>
+        <v>233.6</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="4"/>
-        <v>8.8000000000000007</v>
+        <f t="shared" si="5"/>
+        <v>241.6</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="4"/>
-        <v>13.85</v>
+        <f t="shared" si="5"/>
+        <v>363.45</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="10" t="s">
@@ -21111,20 +21949,20 @@
         <v>0</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="5">P14/20</f>
+        <f t="shared" ref="P15" si="6">P14/20</f>
         <v>0</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <f t="shared" ref="R15:T15" si="7">R14/20</f>
         <v>0</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -21136,31 +21974,31 @@
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
-        <v>163.80000000000001</v>
+        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
+        <v>2404.5</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="7"/>
-        <v>109.2</v>
+        <f t="shared" si="8"/>
+        <v>2955.75</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="7"/>
-        <v>204.75</v>
+        <f t="shared" si="8"/>
+        <v>4905.6000000000004</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="7"/>
-        <v>184.8</v>
+        <f t="shared" si="8"/>
+        <v>5073.6000000000004</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="7"/>
-        <v>290.85000000000002</v>
+        <f t="shared" si="8"/>
+        <v>7632.45</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="10" t="s">
@@ -21171,24 +22009,24 @@
         <v>0</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <f t="shared" ref="O16:P16" si="9">O15+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <f t="shared" ref="R16:T16" si="10">R15+R14</f>
         <v>0</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -21200,35 +22038,35 @@
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>13.975</v>
+        <v>14.3</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="10">D14/40</f>
-        <v>3.9</v>
+        <f t="shared" ref="D17:I17" si="11">D14/40</f>
+        <v>57.25</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="10"/>
-        <v>2.6</v>
+        <f t="shared" si="11"/>
+        <v>70.375</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="10"/>
-        <v>4.875</v>
+        <f t="shared" si="11"/>
+        <v>116.8</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="10"/>
-        <v>4.4000000000000004</v>
+        <f t="shared" si="11"/>
+        <v>120.8</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="10"/>
-        <v>6.9249999999999998</v>
+        <f t="shared" si="11"/>
+        <v>181.72499999999999</v>
       </c>
       <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>36.674999999999997</v>
+        <v>561.25</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="39" t="s">
@@ -21239,24 +22077,24 @@
         <v>0</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <f t="shared" ref="O17:P17" si="12">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <f t="shared" ref="R17:T17" si="13">R14/40</f>
         <v>0</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
@@ -21287,804 +22125,6 @@
     <mergeCell ref="M2:U5"/>
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="R6:U6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E2FD71-4BFE-4078-B64C-19DAB7732322}">
-  <dimension ref="A1:X19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.08984375" customWidth="1"/>
-    <col min="5" max="5" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="4.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P6" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="56" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
-        <f>B8</f>
-        <v>Furqan</v>
-      </c>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
-      <c r="B9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
-        <f>B9</f>
-        <v>Salman</v>
-      </c>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
-      <c r="B10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
-        <f>B10</f>
-        <v>Zesahn</v>
-      </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
-        <f>B11</f>
-        <v>Umair</v>
-      </c>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
-        <f>B12</f>
-        <v>Mubeen</v>
-      </c>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
-        <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13">
-        <f>D14/20</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="36">
-        <f>C15+C14</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="36">
-        <f>O15+O14</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="36">
-        <f>C14/40</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
-        <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="36">
-        <f>O14/40</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22137,95 +22177,95 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="64"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="61" t="s">
+      <c r="N2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="64"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="66"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="67"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="66"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="67"/>
     </row>
     <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="70"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="69"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="70"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -22233,33 +22273,33 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="73"/>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="70" t="s">
+      <c r="P6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="71" t="s">
+      <c r="Q6" s="72"/>
+      <c r="R6" s="73"/>
+      <c r="S6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="73"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -22937,103 +22977,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="64"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="66"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="69"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -23041,35 +23081,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71" t="s">
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -23981,103 +24021,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="64"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="66"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="69"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -24085,35 +24125,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71" t="s">
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -25048,103 +25088,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="64"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
     </row>
     <row r="4" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="66"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:26" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="69"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -25152,35 +25192,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71" t="s">
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -25818,103 +25858,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="64"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="66"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="69"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -25922,35 +25962,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71" t="s">
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -26691,103 +26731,103 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="64"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="64"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="67"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="67"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="66"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="70"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="69"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="70"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -26795,35 +26835,35 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="71" t="s">
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="73"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="70" t="s">
+      <c r="Q6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="71" t="s">
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="72"/>
+      <c r="V6" s="72"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
@@ -27666,91 +27706,91 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="64"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="66"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="67"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="66"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="66"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="67"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="66"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66"/>
+      <c r="U4" s="67"/>
     </row>
     <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="69"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="70"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="69"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -27758,30 +27798,30 @@
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="73"/>
       <c r="L6" s="1"/>
       <c r="M6" s="2"/>
       <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="O6" s="70" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="73"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6C36CD-AE45-4B17-B170-83AAB74031D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0FDCCF-D741-48D7-B99B-31B88DEBD772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="1" activeTab="30" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="2" activeTab="31" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
   <sheets>
     <sheet name="last month" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="49">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -685,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -871,9 +871,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -20499,7 +20496,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E53001-FEFC-449D-A8A3-82DAE50447EF}">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.90625" bestFit="1" customWidth="1"/>
@@ -20518,7 +20515,7 @@
     <col min="20" max="20" width="4.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -20538,7 +20535,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="62" t="s">
         <v>34</v>
@@ -20562,7 +20559,7 @@
       <c r="S2" s="63"/>
       <c r="T2" s="63"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -20582,7 +20579,7 @@
       <c r="S3" s="66"/>
       <c r="T3" s="66"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="65"/>
       <c r="C4" s="66"/>
@@ -20602,7 +20599,7 @@
       <c r="S4" s="66"/>
       <c r="T4" s="66"/>
     </row>
-    <row r="5" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="68"/>
       <c r="C5" s="69"/>
@@ -20622,7 +20619,7 @@
       <c r="S5" s="69"/>
       <c r="T5" s="69"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -20654,7 +20651,7 @@
       <c r="S6" s="72"/>
       <c r="T6" s="72"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -20722,7 +20719,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -20755,7 +20752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -20828,7 +20825,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
@@ -20902,7 +20899,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
@@ -20972,7 +20969,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -21005,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -21028,7 +21025,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
@@ -21098,7 +21095,7 @@
         <v>30.074999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -21155,7 +21152,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -21217,8 +21214,17 @@
         <f t="shared" si="8"/>
         <v>278.25</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="X16">
+        <v>98</v>
+      </c>
+      <c r="Y16">
+        <v>1163</v>
+      </c>
+      <c r="Z16">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
@@ -21288,11 +21294,21 @@
         <f>SUM(N17:T17)</f>
         <v>30.074999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="X17">
+        <v>99</v>
+      </c>
+      <c r="Z17">
+        <f>Z16-Y16</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="X18">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -21302,6 +21318,19 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
+      <c r="X19">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="X20">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="X21">
+        <v>395</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -21620,7 +21649,7 @@
         <f t="shared" ref="J9:J12" si="1">SUM(C9:F9,G9,H9,I9)/40</f>
         <v>11.65</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="44">
         <v>8</v>
       </c>
       <c r="L9" s="27"/>
@@ -21677,7 +21706,7 @@
         <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="44">
         <v>11</v>
       </c>
       <c r="L10" s="27"/>
@@ -21728,7 +21757,7 @@
         <f t="shared" si="1"/>
         <v>14.1</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="44">
         <v>12</v>
       </c>
       <c r="L11" s="11"/>
@@ -21781,7 +21810,7 @@
         <f t="shared" si="1"/>
         <v>523</v>
       </c>
-      <c r="K12" s="77">
+      <c r="K12" s="41">
         <v>6</v>
       </c>
       <c r="L12" s="11"/>
@@ -22132,7 +22161,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F06847A-2E50-4E41-94F1-9E0FF672B727}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -22144,16 +22173,15 @@
     <col min="7" max="7" width="3.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.6328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22163,7 +22191,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -22173,9 +22201,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="62" t="s">
         <v>34</v>
@@ -22187,21 +22214,20 @@
       <c r="G2" s="63"/>
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
-      <c r="J2" s="64"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="62" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="62" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="63"/>
       <c r="O2" s="63"/>
       <c r="P2" s="63"/>
       <c r="Q2" s="63"/>
       <c r="R2" s="63"/>
       <c r="S2" s="63"/>
       <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="64"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U2" s="64"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -22211,19 +22237,18 @@
       <c r="G3" s="66"/>
       <c r="H3" s="66"/>
       <c r="I3" s="66"/>
-      <c r="J3" s="67"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="65"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="66"/>
       <c r="O3" s="66"/>
       <c r="P3" s="66"/>
       <c r="Q3" s="66"/>
       <c r="R3" s="66"/>
       <c r="S3" s="66"/>
       <c r="T3" s="66"/>
-      <c r="U3" s="66"/>
-      <c r="V3" s="67"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U3" s="67"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="65"/>
       <c r="C4" s="66"/>
@@ -22233,19 +22258,18 @@
       <c r="G4" s="66"/>
       <c r="H4" s="66"/>
       <c r="I4" s="66"/>
-      <c r="J4" s="67"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="65"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
       <c r="O4" s="66"/>
       <c r="P4" s="66"/>
       <c r="Q4" s="66"/>
       <c r="R4" s="66"/>
       <c r="S4" s="66"/>
       <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="67"/>
-    </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U4" s="67"/>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="68"/>
       <c r="C5" s="69"/>
@@ -22255,19 +22279,18 @@
       <c r="G5" s="69"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
-      <c r="J5" s="70"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="68"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
       <c r="O5" s="69"/>
       <c r="P5" s="69"/>
       <c r="Q5" s="69"/>
       <c r="R5" s="69"/>
       <c r="S5" s="69"/>
       <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
-      <c r="V5" s="70"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U5" s="70"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -22283,25 +22306,24 @@
       </c>
       <c r="H6" s="72"/>
       <c r="I6" s="72"/>
-      <c r="J6" s="73"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="71" t="s">
+      <c r="O6" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="73"/>
-      <c r="S6" s="72" t="s">
+      <c r="P6" s="72"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="72" t="s">
         <v>3</v>
       </c>
+      <c r="S6" s="72"/>
       <c r="T6" s="72"/>
-      <c r="U6" s="72"/>
-      <c r="V6" s="73"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U6" s="73"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -22330,52 +22352,49 @@
         <v>12</v>
       </c>
       <c r="J7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="N7" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="R7" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="T7" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -22387,215 +22406,248 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="28">
-        <f>SUM(G8:I8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f>SUM(C8:F8,G8,H8,I8)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="10" t="str">
+      <c r="J8">
+        <f>SUM(C8:I8)/40</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="10" t="str">
         <f>B8</f>
         <v>Furqan</v>
       </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="28">
-        <f t="shared" ref="R8:R13" si="0">SUM(P8:Q8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28">
+        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="28">
-        <f>SUM(S8:U8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f>SUM(O8:Q8,S8,T8,U8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U8" s="28">
+        <f>SUM(R8:T8)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f>SUM(N8:P8,R8,S8,T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="28">
-        <f t="shared" ref="J9:J13" si="1">SUM(G9:I9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <f>SUM(C9:F9,G9,H9,I9)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="10" t="str">
+      <c r="C9" s="12">
+        <v>52</v>
+      </c>
+      <c r="D9" s="12">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12">
+        <v>12</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>79</v>
+      </c>
+      <c r="H9" s="12">
+        <v>58</v>
+      </c>
+      <c r="I9" s="12">
+        <v>171</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9:J12" si="1">SUM(C9:I9)/40</f>
+        <v>9.6</v>
+      </c>
+      <c r="K9" s="76">
+        <v>6</v>
+      </c>
+      <c r="L9" s="27"/>
+      <c r="M9" s="10" t="str">
         <f>B9</f>
         <v>Salman</v>
       </c>
+      <c r="N9" s="12"/>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="28">
+      <c r="Q9" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="28">
-        <f t="shared" ref="V9:V13" si="2">SUM(S9:U9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f>SUM(O9:Q9,S9,T9,U9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U9" s="28">
+        <f t="shared" ref="U9:U13" si="2">SUM(R9:T9)/20</f>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f>SUM(N9:P9,R9,S9,T9)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="28">
+      <c r="C10" s="12">
+        <v>184</v>
+      </c>
+      <c r="D10" s="12">
+        <v>32</v>
+      </c>
+      <c r="E10" s="12">
+        <v>32</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>155</v>
+      </c>
+      <c r="H10" s="12">
+        <v>92</v>
+      </c>
+      <c r="I10" s="12">
+        <v>177</v>
+      </c>
+      <c r="J10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <f>SUM(C10:F10,G10,H10,I10)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="10" t="str">
+        <v>16.8</v>
+      </c>
+      <c r="K10" s="76">
+        <v>10</v>
+      </c>
+      <c r="L10" s="27"/>
+      <c r="M10" s="10" t="str">
         <f>B10</f>
         <v>Zesahn</v>
       </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="28">
+      <c r="Q10" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R10" s="12"/>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="28">
+      <c r="U10" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W10">
-        <f>SUM(O10:Q10,S10,T10,U10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V10">
+        <f>SUM(N10:P10,R10,S10,T10)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="28">
+      <c r="C11" s="12">
+        <v>80</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>81</v>
+      </c>
+      <c r="H11" s="12">
+        <v>75</v>
+      </c>
+      <c r="I11" s="12">
+        <v>56</v>
+      </c>
+      <c r="J11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(C11:F11,G11,H11,I11)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="str">
+        <v>7.3</v>
+      </c>
+      <c r="K11" s="76">
+        <v>7</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="10" t="str">
         <f>B11</f>
         <v>Umair</v>
       </c>
+      <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="28">
+      <c r="Q11" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="28">
+      <c r="U11" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W11">
-        <f>SUM(O11:Q11,S11,T11,U11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V11">
+        <f>SUM(N11:P11,R11,S11,T11)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
-      <c r="J12" s="28">
+      <c r="J12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12">
-        <f>SUM(C12:F12,G12,H12,I12)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="str">
+      <c r="L12" s="11"/>
+      <c r="M12" s="10" t="str">
         <f>B12</f>
         <v>Mubeen</v>
       </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="28">
+      <c r="Q12" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R12" s="12"/>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="28">
+      <c r="U12" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W12">
-        <f>SUM(O12:Q12,S12,T12,U12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="V12">
+        <f>SUM(N12:P12,R12,S12,T12)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -22605,41 +22657,37 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
-      <c r="J13" s="28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="28">
+      <c r="Q13" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="28">
+      <c r="U13" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:J14" si="3">SUM(C8:C13)</f>
-        <v>0</v>
+        <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
+        <v>316</v>
       </c>
       <c r="D14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="3"/>
@@ -22647,28 +22695,28 @@
       </c>
       <c r="G14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="I14" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="14">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="35">
+        <v>404</v>
+      </c>
+      <c r="J14" s="35">
         <f>C14+D14+E14+F14+G14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10"/>
+        <v>1348</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="14">
+        <f t="shared" ref="N14:U14" si="4">SUM(N8:N13)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="14">
-        <f t="shared" ref="O14:V14" si="4">SUM(O8:O13)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P14" s="14">
@@ -22695,16 +22743,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W14" s="35" t="e">
-        <f>O14+P14+Q14+#REF!+S14+T14+U14</f>
+      <c r="V14" s="35" t="e">
+        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -22712,11 +22756,11 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13">
         <f>D14/20</f>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" ref="E15:I15" si="5">E14/20</f>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="5"/>
@@ -22724,61 +22768,60 @@
       </c>
       <c r="G15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="10" t="s">
+        <v>20.2</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13">
+        <f>O14/20</f>
+        <v>0</v>
+      </c>
       <c r="P15" s="13">
-        <f>P14/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <f t="shared" ref="Q15" si="6">Q14/20</f>
-        <v>0</v>
-      </c>
-      <c r="R15" s="13"/>
+        <f t="shared" ref="P15" si="6">P14/20</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13">
+        <f t="shared" ref="R15:T15" si="7">R14/20</f>
+        <v>0</v>
+      </c>
       <c r="S15" s="13">
-        <f t="shared" ref="S15:U15" si="7">S14/20</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T15" s="13">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="13"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="36">
         <f>C15+C14</f>
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ref="D16:I16" si="8">D15+D14</f>
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="8"/>
@@ -22786,64 +22829,63 @@
       </c>
       <c r="G16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>330.75</v>
       </c>
       <c r="H16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>236.25</v>
       </c>
       <c r="I16" s="36">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="10" t="s">
+        <v>424.2</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="N16" s="36">
+        <f>N15+N14</f>
+        <v>0</v>
+      </c>
       <c r="O16" s="36">
-        <f>O15+O14</f>
+        <f t="shared" ref="O16:P16" si="9">O15+O14</f>
         <v>0</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" ref="P16:Q16" si="9">P15+P14</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36">
+        <f t="shared" ref="R16:T16" si="10">R15+R14</f>
+        <v>0</v>
+      </c>
       <c r="S16" s="36">
-        <f t="shared" ref="S16:U16" si="10">S15+S14</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T16" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="U16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="36"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="36">
         <f>C14/40</f>
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="D17" s="36">
         <f t="shared" ref="D17:I17" si="11">D14/40</f>
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F17" s="36">
         <f t="shared" si="11"/>
@@ -22851,60 +22893,59 @@
       </c>
       <c r="G17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>7.875</v>
       </c>
       <c r="H17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5.625</v>
       </c>
       <c r="I17" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="35">
+        <v>10.1</v>
+      </c>
+      <c r="J17" s="35">
         <f>SUM(C17:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="39" t="s">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="39" t="s">
         <v>23</v>
       </c>
+      <c r="N17" s="36">
+        <f>N14/40</f>
+        <v>0</v>
+      </c>
       <c r="O17" s="36">
-        <f>O14/40</f>
+        <f t="shared" ref="O17:P17" si="12">O14/40</f>
         <v>0</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" ref="P17:Q17" si="12">P14/40</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36">
+        <f t="shared" ref="R17:T17" si="13">R14/40</f>
+        <v>0</v>
+      </c>
       <c r="S17" s="36">
-        <f t="shared" ref="S17:U17" si="13">S14/40</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T17" s="36">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="35">
-        <f>SUM(O17:U17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U17" s="36"/>
+      <c r="V17" s="35">
+        <f>SUM(N17:T17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -22914,16 +22955,15 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:J5"/>
+    <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="N2:V5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="R6:U6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
+++ b/july 2026/Daily Reports/Final Execution SKU wise  july.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0FDCCF-D741-48D7-B99B-31B88DEBD772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02781797-74F9-4FF4-9CDA-BBB363B7AB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="887" firstSheet="2" activeTab="31" xr2:uid="{6D56E189-8B51-44FA-B14F-5373D35B2784}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="51">
   <si>
     <t>Gate Pass</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shabaz </t>
+  </si>
+  <si>
+    <t>LMT</t>
   </si>
 </sst>
 </file>
@@ -870,7 +876,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -21362,7 +21368,7 @@
     <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.54296875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21596,27 +21602,24 @@
         <v>0</v>
       </c>
       <c r="L8" s="27"/>
-      <c r="M8" s="10" t="str">
-        <f>B8</f>
-        <v>Furqan</v>
+      <c r="M8" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="28">
-        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="O8" s="12">
+        <v>20</v>
+      </c>
+      <c r="P8" s="12">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="28"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="28">
-        <f>SUM(R8:T8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="U8" s="28"/>
       <c r="V8">
-        <f>SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
+        <f>SUM(N8:U8)/40</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
@@ -21646,7 +21649,7 @@
         <v>92</v>
       </c>
       <c r="J9">
-        <f t="shared" ref="J9:J12" si="1">SUM(C9:F9,G9,H9,I9)/40</f>
+        <f t="shared" ref="J9:J12" si="0">SUM(C9:F9,G9,H9,I9)/40</f>
         <v>11.65</v>
       </c>
       <c r="K9" s="44">
@@ -21657,23 +21660,34 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="N9" s="12">
+        <v>100</v>
+      </c>
+      <c r="O9" s="12">
+        <v>60</v>
+      </c>
+      <c r="P9" s="12">
+        <v>17</v>
+      </c>
       <c r="Q9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>72</v>
+      </c>
+      <c r="S9" s="12">
+        <v>47</v>
+      </c>
       <c r="T9" s="12"/>
       <c r="U9" s="28">
-        <f t="shared" ref="U9:U13" si="2">SUM(R9:T9)/20</f>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="V9">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
+        <f t="shared" ref="V9:V13" si="1">SUM(N9:U9)/40</f>
+        <v>9.6</v>
+      </c>
+      <c r="W9" s="44">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
@@ -21703,7 +21717,7 @@
         <v>85</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="K10" s="44">
@@ -21714,23 +21728,32 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
+      <c r="N10" s="12">
+        <v>120</v>
+      </c>
+      <c r="O10" s="12">
+        <v>50</v>
+      </c>
+      <c r="P10" s="12">
+        <v>60</v>
+      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="12">
+        <v>80</v>
+      </c>
+      <c r="S10" s="12">
+        <v>65</v>
+      </c>
       <c r="T10" s="12"/>
       <c r="U10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V10">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
+      <c r="W10" s="44">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
@@ -21754,7 +21777,7 @@
         <v>52</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14.1</v>
       </c>
       <c r="K11" s="44">
@@ -21765,23 +21788,34 @@
         <f>B11</f>
         <v>Umair</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="N11" s="12">
+        <v>272</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0</v>
+      </c>
       <c r="Q11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>60</v>
+      </c>
+      <c r="S11" s="12">
+        <v>20</v>
+      </c>
       <c r="T11" s="12"/>
       <c r="U11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V11">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>9.1</v>
+      </c>
+      <c r="W11" s="44">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
@@ -21807,7 +21841,7 @@
         <v>7040</v>
       </c>
       <c r="J12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>523</v>
       </c>
       <c r="K12" s="41">
@@ -21818,23 +21852,23 @@
         <f>B12</f>
         <v xml:space="preserve">Shakoor </v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
+      <c r="N12" s="12">
+        <v>2</v>
+      </c>
+      <c r="O12" s="12">
+        <v>2</v>
+      </c>
       <c r="P12" s="12"/>
-      <c r="Q12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="12"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="12">
+        <v>2</v>
+      </c>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
-      <c r="U12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="U12" s="28"/>
       <c r="V12">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
@@ -21848,51 +21882,66 @@
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
+      <c r="M13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" s="12">
+        <v>5600</v>
+      </c>
+      <c r="O13" s="12">
+        <v>1400</v>
+      </c>
+      <c r="P13" s="12">
+        <v>1800</v>
+      </c>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="12">
+        <v>2400</v>
+      </c>
+      <c r="S13" s="12">
+        <v>3000</v>
+      </c>
       <c r="T13" s="12"/>
       <c r="U13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="W13" s="41">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="2">SUM(C8:C13)</f>
         <v>572</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2290</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2815</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4672</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4832</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7269</v>
       </c>
       <c r="J14" s="35">
@@ -21902,36 +21951,36 @@
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="4">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:U14" si="3">SUM(N8:N13)</f>
+        <v>6094</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1532</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>1897</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>2614</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>3132</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>3185</v>
       </c>
       <c r="V14" s="35" t="e">
         <f>N14+O14+P14+#REF!+R14+S14+T14</f>
@@ -21949,23 +21998,23 @@
         <v>114.5</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
+        <f t="shared" ref="E15:I15" si="4">E14/20</f>
         <v>140.75</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>233.6</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>241.6</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>363.45</v>
       </c>
       <c r="L15" s="13"/>
@@ -21975,23 +22024,23 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="6">P14/20</f>
-        <v>0</v>
+        <f t="shared" ref="P15" si="5">P14/20</f>
+        <v>94.85</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="7">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:T15" si="6">R14/20</f>
+        <v>130.69999999999999</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>156.6</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U15" s="13"/>
@@ -22006,27 +22055,27 @@
         <v>572</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="7">D15+D14</f>
         <v>2404.5</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2955.75</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4905.6000000000004</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5073.6000000000004</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7632.45</v>
       </c>
       <c r="L16" s="13"/>
@@ -22035,27 +22084,27 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>6094</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="9">O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="8">O15+O14</f>
+        <v>1608.6</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1991.85</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="10">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:T16" si="9">R15+R14</f>
+        <v>2744.7</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>3288.6</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U16" s="36"/>
@@ -22070,27 +22119,27 @@
         <v>14.3</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
+        <f t="shared" ref="D17:I17" si="10">D14/40</f>
         <v>57.25</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>70.375</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>116.8</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>120.8</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>181.72499999999999</v>
       </c>
       <c r="J17" s="35">
@@ -22103,33 +22152,33 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>152.35</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="12">O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="11">O14/40</f>
+        <v>38.299999999999997</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>47.424999999999997</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="13">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:T17" si="12">R14/40</f>
+        <v>65.349999999999994</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>78.3</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U17" s="36"/>
       <c r="V17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
+        <v>381.72499999999997</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.35">
@@ -22161,7 +22210,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F06847A-2E50-4E41-94F1-9E0FF672B727}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.54296875" bestFit="1" customWidth="1"/>
@@ -22177,11 +22226,12 @@
     <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="3.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.6328125" customWidth="1"/>
+    <col min="20" max="20" width="5.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -22200,9 +22250,8 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="62" t="s">
         <v>34</v>
@@ -22225,9 +22274,8 @@
       <c r="R2" s="63"/>
       <c r="S2" s="63"/>
       <c r="T2" s="63"/>
-      <c r="U2" s="64"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -22246,9 +22294,8 @@
       <c r="R3" s="66"/>
       <c r="S3" s="66"/>
       <c r="T3" s="66"/>
-      <c r="U3" s="67"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="65"/>
       <c r="C4" s="66"/>
@@ -22267,9 +22314,8 @@
       <c r="R4" s="66"/>
       <c r="S4" s="66"/>
       <c r="T4" s="66"/>
-      <c r="U4" s="67"/>
-    </row>
-    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1"/>
       <c r="B5" s="68"/>
       <c r="C5" s="69"/>
@@ -22288,9 +22334,8 @@
       <c r="R5" s="69"/>
       <c r="S5" s="69"/>
       <c r="T5" s="69"/>
-      <c r="U5" s="70"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
@@ -22321,9 +22366,8 @@
       </c>
       <c r="S6" s="72"/>
       <c r="T6" s="72"/>
-      <c r="U6" s="73"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
@@ -22385,16 +22429,13 @@
         <v>12</v>
       </c>
       <c r="U7" s="12" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="27"/>
       <c r="B8" s="10" t="s">
         <v>17</v>
@@ -22418,23 +22459,16 @@
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
-      <c r="Q8" s="28">
-        <f t="shared" ref="Q8:Q13" si="0">SUM(O8:P8)/20</f>
-        <v>0</v>
-      </c>
+      <c r="Q8" s="28"/>
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
-      <c r="U8" s="28">
-        <f>SUM(R8:T8)/20</f>
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <f>SUM(N8:P8,R8,S8,T8)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U8">
+        <f>SUM(N8:T8)/40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="10" t="s">
         <v>14</v>
@@ -22461,10 +22495,10 @@
         <v>171</v>
       </c>
       <c r="J9">
-        <f t="shared" ref="J9:J12" si="1">SUM(C9:I9)/40</f>
+        <f t="shared" ref="J9:J12" si="0">SUM(C9:I9)/40</f>
         <v>9.6</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="44">
         <v>6</v>
       </c>
       <c r="L9" s="27"/>
@@ -22472,26 +22506,36 @@
         <f>B9</f>
         <v>Salman</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="N9" s="12">
+        <v>52</v>
+      </c>
+      <c r="O9" s="12">
+        <v>12</v>
+      </c>
+      <c r="P9" s="12">
+        <v>12</v>
+      </c>
       <c r="Q9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="28">
-        <f t="shared" ref="U9:U13" si="2">SUM(R9:T9)/20</f>
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <f>SUM(N9:P9,R9,S9,T9)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>63</v>
+      </c>
+      <c r="S9" s="12">
+        <v>48</v>
+      </c>
+      <c r="T9" s="12">
+        <v>155</v>
+      </c>
+      <c r="U9">
+        <f>SUM(N9:T9)/40</f>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="V9" s="44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="27"/>
       <c r="B10" s="10" t="s">
         <v>37</v>
@@ -22518,10 +22562,10 @@
         <v>177</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16.8</v>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="44">
         <v>10</v>
       </c>
       <c r="L10" s="27"/>
@@ -22529,26 +22573,36 @@
         <f>B10</f>
         <v>Zesahn</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
+      <c r="N10" s="12">
+        <v>132</v>
+      </c>
+      <c r="O10" s="12">
+        <v>20</v>
+      </c>
+      <c r="P10" s="12">
+        <v>20</v>
+      </c>
       <c r="Q10" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <f>SUM(N10:P10,R10,S10,T10)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>85</v>
+      </c>
+      <c r="S10" s="12">
+        <v>44</v>
+      </c>
+      <c r="T10" s="12">
+        <v>165</v>
+      </c>
+      <c r="U10">
+        <f>SUM(N10:T10)/40</f>
+        <v>11.65</v>
+      </c>
+      <c r="V10" s="44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="11"/>
       <c r="B11" s="11" t="s">
         <v>31</v>
@@ -22575,10 +22629,10 @@
         <v>56</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7.3</v>
       </c>
-      <c r="K11" s="76">
+      <c r="K11" s="44">
         <v>7</v>
       </c>
       <c r="L11" s="11"/>
@@ -22589,23 +22643,17 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
-      <c r="Q11" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="Q11" s="28"/>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
-      <c r="U11" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <f>SUM(N11:P11,R11,S11,T11)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="U11">
+        <f>SUM(N11:T11)/40</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="44"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="11"/>
       <c r="B12" s="11" t="s">
         <v>19</v>
@@ -22620,34 +22668,41 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L12" s="11"/>
-      <c r="M12" s="10" t="str">
-        <f>B12</f>
-        <v>Mubeen</v>
-      </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
+      <c r="M12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" s="12">
+        <v>5760</v>
+      </c>
+      <c r="O12" s="12">
+        <v>1080</v>
+      </c>
+      <c r="P12" s="12">
+        <v>1118</v>
+      </c>
       <c r="Q12" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <f>SUM(N12:P12,R12,S12,T12)/40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+        <v>960</v>
+      </c>
+      <c r="R12" s="12">
+        <v>1840</v>
+      </c>
+      <c r="S12" s="12">
+        <v>1837</v>
+      </c>
+      <c r="T12" s="12">
+        <v>2199</v>
+      </c>
+      <c r="U12">
+        <f>SUM(N12:T12)/40</f>
+        <v>369.85</v>
+      </c>
+      <c r="W12" s="76"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
@@ -22659,50 +22714,59 @@
       <c r="I13" s="12"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+      <c r="N13" s="12">
+        <v>4000</v>
+      </c>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+        <v>2000</v>
+      </c>
+      <c r="R13" s="12">
+        <v>2800</v>
+      </c>
+      <c r="S13" s="12">
+        <v>2400</v>
+      </c>
+      <c r="T13" s="12">
+        <v>2800</v>
+      </c>
+      <c r="U13">
+        <f>SUM(N13:T13)/40</f>
+        <v>350</v>
+      </c>
+      <c r="W13" s="76"/>
+      <c r="X13" s="76"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="10"/>
       <c r="C14" s="14">
-        <f t="shared" ref="C14:I14" si="3">SUM(C8:C13)</f>
+        <f t="shared" ref="C14:I14" si="1">SUM(C8:C13)</f>
         <v>316</v>
       </c>
       <c r="D14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="E14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="F14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>315</v>
       </c>
       <c r="H14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>225</v>
       </c>
       <c r="I14" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>404</v>
       </c>
       <c r="J14" s="35">
@@ -22712,43 +22776,39 @@
       <c r="L14" s="13"/>
       <c r="M14" s="10"/>
       <c r="N14" s="14">
-        <f t="shared" ref="N14:U14" si="4">SUM(N8:N13)</f>
-        <v>0</v>
+        <f t="shared" ref="N14:T14" si="2">SUM(N8:N13)</f>
+        <v>9944</v>
       </c>
       <c r="O14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1112</v>
       </c>
       <c r="P14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1150</v>
       </c>
       <c r="Q14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2960</v>
       </c>
       <c r="R14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4788</v>
       </c>
       <c r="S14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4329</v>
       </c>
       <c r="T14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="35" t="e">
-        <f>N14+O14+P14+#REF!+R14+S14+T14</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>5319</v>
+      </c>
+      <c r="U14" s="35">
+        <f>SUM(N14:T14)/40</f>
+        <v>740.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -22759,23 +22819,23 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="13">
-        <f t="shared" ref="E15:I15" si="5">E14/20</f>
+        <f t="shared" ref="E15:I15" si="3">E14/20</f>
         <v>2.2000000000000002</v>
       </c>
       <c r="F15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>15.75</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>11.25</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>20.2</v>
       </c>
       <c r="L15" s="13"/>
@@ -22785,28 +22845,27 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13">
         <f>O14/20</f>
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" ref="P15" si="6">P14/20</f>
-        <v>0</v>
+        <f t="shared" ref="P15" si="4">P14/20</f>
+        <v>57.5</v>
       </c>
       <c r="Q15" s="13"/>
       <c r="R15" s="13">
-        <f t="shared" ref="R15:T15" si="7">R14/20</f>
-        <v>0</v>
+        <f t="shared" ref="R15:T15" si="5">R14/20</f>
+        <v>239.4</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>216.45</v>
       </c>
       <c r="T15" s="13">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="13"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v>265.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>21</v>
@@ -22816,27 +22875,27 @@
         <v>316</v>
       </c>
       <c r="D16" s="36">
-        <f t="shared" ref="D16:I16" si="8">D15+D14</f>
+        <f t="shared" ref="D16:I16" si="6">D15+D14</f>
         <v>46.2</v>
       </c>
       <c r="E16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>46.2</v>
       </c>
       <c r="F16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>330.75</v>
       </c>
       <c r="H16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>236.25</v>
       </c>
       <c r="I16" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>424.2</v>
       </c>
       <c r="L16" s="13"/>
@@ -22845,32 +22904,31 @@
       </c>
       <c r="N16" s="36">
         <f>N15+N14</f>
-        <v>0</v>
+        <v>9944</v>
       </c>
       <c r="O16" s="36">
-        <f t="shared" ref="O16:P16" si="9">O15+O14</f>
-        <v>0</v>
+        <f t="shared" ref="O16:P16" si="7">O15+O14</f>
+        <v>1167.5999999999999</v>
       </c>
       <c r="P16" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1207.5</v>
       </c>
       <c r="Q16" s="36"/>
       <c r="R16" s="36">
-        <f t="shared" ref="R16:T16" si="10">R15+R14</f>
-        <v>0</v>
+        <f t="shared" ref="R16:T16" si="8">R15+R14</f>
+        <v>5027.3999999999996</v>
       </c>
       <c r="S16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>4545.45</v>
       </c>
       <c r="T16" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="36"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>5584.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="39" t="s">
         <v>23</v>
@@ -22880,27 +22938,27 @@
         <v>7.9</v>
       </c>
       <c r="D17" s="36">
-        <f t="shared" ref="D17:I17" si="11">D14/40</f>
+        <f t="shared" ref="D17:I17" si="9">D14/40</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="F17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>7.875</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>5.625</v>
       </c>
       <c r="I17" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>10.1</v>
       </c>
       <c r="J17" s="35">
@@ -22913,39 +22971,38 @@
       </c>
       <c r="N17" s="36">
         <f>N14/40</f>
-        <v>0</v>
+        <v>248.6</v>
       </c>
       <c r="O17" s="36">
-        <f t="shared" ref="O17:P17" si="12">O14/40</f>
-        <v>0</v>
+        <f t="shared" ref="O17:P17" si="10">O14/40</f>
+        <v>27.8</v>
       </c>
       <c r="P17" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>28.75</v>
       </c>
       <c r="Q17" s="36"/>
       <c r="R17" s="36">
-        <f t="shared" ref="R17:T17" si="13">R14/40</f>
-        <v>0</v>
+        <f t="shared" ref="R17:T17" si="11">R14/40</f>
+        <v>119.7</v>
       </c>
       <c r="S17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>108.22499999999999</v>
       </c>
       <c r="T17" s="36">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="36"/>
-      <c r="V17" s="35">
+        <f t="shared" si="11"/>
+        <v>132.97499999999999</v>
+      </c>
+      <c r="U17" s="35">
         <f>SUM(N17:T17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+        <v>666.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C18" s="32"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="26"/>
@@ -22961,9 +23018,9 @@
     <mergeCell ref="B2:I5"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:I6"/>
-    <mergeCell ref="M2:U5"/>
+    <mergeCell ref="M2:T5"/>
     <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="R6:T6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
